--- a/workspaces/btc_daily_14days/drawdown/drawdown_120.xlsx
+++ b/workspaces/btc_daily_14days/drawdown/drawdown_120.xlsx
@@ -575,46 +575,46 @@
         <v>22</v>
       </c>
       <c r="C6" s="4" t="n">
-        <v>-2.493438320207908</v>
+        <v>-2.48522726838592</v>
       </c>
       <c r="D6" s="4" t="n">
-        <v>-8.65265183156658</v>
+        <v>-8.624242243366872</v>
       </c>
       <c r="E6" s="4" t="n">
-        <v>-22.69310584787808</v>
+        <v>-22.61896017701461</v>
       </c>
       <c r="F6" s="4" t="n">
-        <v>-8.92183275544128</v>
+        <v>-8.892579709866965</v>
       </c>
       <c r="G6" s="4" t="n">
-        <v>-14.01296657226461</v>
+        <v>-13.96743810511781</v>
       </c>
       <c r="H6" s="4" t="n">
-        <v>-9.167510913769476</v>
+        <v>-9.137741995898494</v>
       </c>
       <c r="I6" s="4" t="n">
-        <v>-9.254672778352642</v>
+        <v>-9.224604360955652</v>
       </c>
       <c r="J6" s="4" t="n">
-        <v>-9.724774255013486</v>
+        <v>-9.693582038326738</v>
       </c>
       <c r="K6" s="4" t="n">
-        <v>-5.233924123627162</v>
+        <v>-5.217023576212931</v>
       </c>
       <c r="L6" s="4" t="n">
-        <v>3.024592763140234</v>
+        <v>3.014001166228319</v>
       </c>
       <c r="M6" s="4" t="n">
-        <v>2.820112926897352</v>
+        <v>2.810224955180978</v>
       </c>
       <c r="N6" s="4" t="n">
-        <v>2.855010040287858</v>
+        <v>2.845413572493932</v>
       </c>
       <c r="O6" s="4" t="n">
-        <v>6.993399293565382</v>
+        <v>6.97031410275126</v>
       </c>
       <c r="P6" s="4" t="n">
-        <v>7.245764604277774</v>
+        <v>7.221811218939031</v>
       </c>
     </row>
     <row r="7">
@@ -627,46 +627,46 @@
         <v>20</v>
       </c>
       <c r="C7" s="4" t="n">
-        <v>-12.49343832021225</v>
+        <v>-12.45221185192861</v>
       </c>
       <c r="D7" s="4" t="n">
-        <v>-4.106068917803263</v>
+        <v>-4.092328117644051</v>
       </c>
       <c r="E7" s="4" t="n">
-        <v>5.502874660669811</v>
+        <v>5.48496520781589</v>
       </c>
       <c r="F7" s="4" t="n">
-        <v>-4.372993461161904</v>
+        <v>-4.358407660502898</v>
       </c>
       <c r="G7" s="4" t="n">
-        <v>5.097155314907411</v>
+        <v>5.080242194183882</v>
       </c>
       <c r="H7" s="4" t="n">
-        <v>5.396266327652512</v>
+        <v>5.378396235998963</v>
       </c>
       <c r="I7" s="4" t="n">
-        <v>5.312773107172667</v>
+        <v>5.295193621081566</v>
       </c>
       <c r="J7" s="4" t="n">
-        <v>-0.162544079555289</v>
+        <v>-0.1625066043013277</v>
       </c>
       <c r="K7" s="4" t="n">
-        <v>9.796421862633771</v>
+        <v>9.764010182377525</v>
       </c>
       <c r="L7" s="4" t="n">
-        <v>8.947263207450234</v>
+        <v>8.917056726333087</v>
       </c>
       <c r="M7" s="4" t="n">
-        <v>13.7569870677416</v>
+        <v>13.71098089474658</v>
       </c>
       <c r="N7" s="4" t="n">
-        <v>8.780697607666667</v>
+        <v>8.751486907348777</v>
       </c>
       <c r="O7" s="4" t="n">
-        <v>-1.669067332771633</v>
+        <v>-1.663874284441583</v>
       </c>
       <c r="P7" s="4" t="n">
-        <v>3.597643233459166</v>
+        <v>3.585447582575398</v>
       </c>
     </row>
     <row r="8">
@@ -679,46 +679,46 @@
         <v>39</v>
       </c>
       <c r="C8" s="4" t="n">
-        <v>9.04502321825273</v>
+        <v>9.015242360267649</v>
       </c>
       <c r="D8" s="4" t="n">
-        <v>-0.258946854720044</v>
+        <v>-0.2577928746162854</v>
       </c>
       <c r="E8" s="4" t="n">
-        <v>12.17299561350296</v>
+        <v>12.1326333005573</v>
       </c>
       <c r="F8" s="4" t="n">
-        <v>7.174279340312651</v>
+        <v>7.150683001250492</v>
       </c>
       <c r="G8" s="4" t="n">
-        <v>14.33745850601662</v>
+        <v>14.28956001420016</v>
       </c>
       <c r="H8" s="4" t="n">
-        <v>17.20634813087469</v>
+        <v>17.14893201751656</v>
       </c>
       <c r="I8" s="4" t="n">
-        <v>17.12589956094811</v>
+        <v>17.06876831390026</v>
       </c>
       <c r="J8" s="4" t="n">
-        <v>14.09375416045233</v>
+        <v>14.04638061854768</v>
       </c>
       <c r="K8" s="4" t="n">
-        <v>19.1748908609765</v>
+        <v>19.11080039174468</v>
       </c>
       <c r="L8" s="4" t="n">
-        <v>23.46819101103073</v>
+        <v>23.38923696177967</v>
       </c>
       <c r="M8" s="4" t="n">
-        <v>23.26903441009627</v>
+        <v>23.1907000253732</v>
       </c>
       <c r="N8" s="4" t="n">
-        <v>20.73779508852019</v>
+        <v>20.66837827446631</v>
       </c>
       <c r="O8" s="4" t="n">
-        <v>25.46544093437144</v>
+        <v>25.38047224884836</v>
       </c>
       <c r="P8" s="4" t="n">
-        <v>25.72268971237548</v>
+        <v>25.63672963385744</v>
       </c>
     </row>
     <row r="9">
@@ -731,46 +731,46 @@
         <v>56</v>
       </c>
       <c r="C9" s="4" t="n">
-        <v>8.220847394074923</v>
+        <v>8.193113020442652</v>
       </c>
       <c r="D9" s="4" t="n">
-        <v>1.252432227940467</v>
+        <v>1.248515276311387</v>
       </c>
       <c r="E9" s="4" t="n">
-        <v>8.004318190510944</v>
+        <v>7.977025793673789</v>
       </c>
       <c r="F9" s="4" t="n">
-        <v>11.7109129201521</v>
+        <v>11.67142821131178</v>
       </c>
       <c r="G9" s="4" t="n">
-        <v>5.812488155469808</v>
+        <v>5.792171874354324</v>
       </c>
       <c r="H9" s="4" t="n">
-        <v>-2.828263611935398</v>
+        <v>-2.819498717796151</v>
       </c>
       <c r="I9" s="4" t="n">
-        <v>6.028682721060299</v>
+        <v>6.007584785833011</v>
       </c>
       <c r="J9" s="4" t="n">
-        <v>-1.593457545622975</v>
+        <v>-1.589070572165106</v>
       </c>
       <c r="K9" s="4" t="n">
-        <v>-1.654931529656388</v>
+        <v>-1.650322518871981</v>
       </c>
       <c r="L9" s="4" t="n">
-        <v>1.072904526747109</v>
+        <v>1.067565346329658</v>
       </c>
       <c r="M9" s="4" t="n">
-        <v>4.448780631498934</v>
+        <v>4.432014254189738</v>
       </c>
       <c r="N9" s="4" t="n">
-        <v>0.9023950965113414</v>
+        <v>0.8981912600264224</v>
       </c>
       <c r="O9" s="4" t="n">
-        <v>0.4811373488338049</v>
+        <v>0.4783705635167266</v>
       </c>
       <c r="P9" s="4" t="n">
-        <v>-2.851453321588295</v>
+        <v>-2.843123845996033</v>
       </c>
     </row>
     <row r="10">
@@ -783,46 +783,46 @@
         <v>60</v>
       </c>
       <c r="C10" s="4" t="n">
-        <v>0.8398950131229768</v>
+        <v>0.8366096755069492</v>
       </c>
       <c r="D10" s="4" t="n">
-        <v>-0.7719017838084952</v>
+        <v>-0.769000392235867</v>
       </c>
       <c r="E10" s="4" t="n">
-        <v>-11.17233166502771</v>
+        <v>-11.13473333418563</v>
       </c>
       <c r="F10" s="4" t="n">
-        <v>-14.38087378067933</v>
+        <v>-14.33213992877891</v>
       </c>
       <c r="G10" s="4" t="n">
-        <v>-4.912917117511121</v>
+        <v>-4.897094832863992</v>
       </c>
       <c r="H10" s="4" t="n">
-        <v>-6.285304795014753</v>
+        <v>-6.26442330106174</v>
       </c>
       <c r="I10" s="4" t="n">
-        <v>-11.37950920657706</v>
+        <v>-11.34158812398757</v>
       </c>
       <c r="J10" s="4" t="n">
-        <v>-15.19005093931933</v>
+        <v>-15.13892929593312</v>
       </c>
       <c r="K10" s="4" t="n">
-        <v>-10.24456365221657</v>
+        <v>-10.21037387084348</v>
       </c>
       <c r="L10" s="4" t="n">
-        <v>-17.78124320905309</v>
+        <v>-17.7221256070715</v>
       </c>
       <c r="M10" s="4" t="n">
-        <v>-16.31986584948046</v>
+        <v>-16.26596323008839</v>
       </c>
       <c r="N10" s="4" t="n">
-        <v>-16.29021318485662</v>
+        <v>-16.23562022128356</v>
       </c>
       <c r="O10" s="4" t="n">
-        <v>-18.38800508720487</v>
+        <v>-18.32618502713117</v>
       </c>
       <c r="P10" s="4" t="n">
-        <v>-18.14221032086334</v>
+        <v>-18.08121908409127</v>
       </c>
     </row>
     <row r="11">
@@ -835,46 +835,46 @@
         <v>64</v>
       </c>
       <c r="C11" s="4" t="n">
-        <v>-2.49343832020962</v>
+        <v>-2.485212273683004</v>
       </c>
       <c r="D11" s="4" t="n">
-        <v>-0.9802984240472128</v>
+        <v>-0.9765740426974006</v>
       </c>
       <c r="E11" s="4" t="n">
-        <v>-7.62895690261027</v>
+        <v>-7.602461194155993</v>
       </c>
       <c r="F11" s="4" t="n">
-        <v>-2.809438471477101</v>
+        <v>-2.799424292782639</v>
       </c>
       <c r="G11" s="4" t="n">
-        <v>-6.477257031878025</v>
+        <v>-6.455455025540502</v>
       </c>
       <c r="H11" s="4" t="n">
-        <v>-4.616667815057028</v>
+        <v>-4.600909135660601</v>
       </c>
       <c r="I11" s="4" t="n">
-        <v>-4.70268144743725</v>
+        <v>-4.686776065205699</v>
       </c>
       <c r="J11" s="4" t="n">
-        <v>-3.606722312991771</v>
+        <v>-3.594282404215797</v>
       </c>
       <c r="K11" s="4" t="n">
-        <v>-0.5369370581053019</v>
+        <v>-0.5354529921620994</v>
       </c>
       <c r="L11" s="4" t="n">
-        <v>-4.521434746351915</v>
+        <v>-4.50657751641954</v>
       </c>
       <c r="M11" s="4" t="n">
-        <v>-7.861060789145839</v>
+        <v>-7.834854748188306</v>
       </c>
       <c r="N11" s="4" t="n">
-        <v>-10.96353635906777</v>
+        <v>-10.92569782597164</v>
       </c>
       <c r="O11" s="4" t="n">
-        <v>-16.09084367186673</v>
+        <v>-16.03497625618748</v>
       </c>
       <c r="P11" s="4" t="n">
-        <v>-12.7086292964722</v>
+        <v>-12.6645524174246</v>
       </c>
     </row>
     <row r="12">
@@ -887,46 +887,46 @@
         <v>57</v>
       </c>
       <c r="C12" s="4" t="n">
-        <v>-5.1250172675784</v>
+        <v>-5.107203563659141</v>
       </c>
       <c r="D12" s="4" t="n">
-        <v>-4.983591068279203</v>
+        <v>-4.965571083847976</v>
       </c>
       <c r="E12" s="4" t="n">
-        <v>3.396650851179402</v>
+        <v>3.384985633686767</v>
       </c>
       <c r="F12" s="4" t="n">
-        <v>0.01625886600198356</v>
+        <v>0.01659920216764021</v>
       </c>
       <c r="G12" s="4" t="n">
-        <v>-7.547723116993446</v>
+        <v>-7.521412912977461</v>
       </c>
       <c r="H12" s="4" t="n">
-        <v>-10.76559113268576</v>
+        <v>-10.72754410815515</v>
       </c>
       <c r="I12" s="4" t="n">
-        <v>-14.36783889473553</v>
+        <v>-14.31719179189692</v>
       </c>
       <c r="J12" s="4" t="n">
-        <v>-25.38640063065056</v>
+        <v>-25.29644409684942</v>
       </c>
       <c r="K12" s="4" t="n">
-        <v>-23.69597520466551</v>
+        <v>-23.61245217687796</v>
       </c>
       <c r="L12" s="4" t="n">
-        <v>-24.55442678617874</v>
+        <v>-24.46815707766716</v>
       </c>
       <c r="M12" s="4" t="n">
-        <v>-24.76631596140587</v>
+        <v>-24.67939661756191</v>
       </c>
       <c r="N12" s="4" t="n">
-        <v>-17.70078254704396</v>
+        <v>-17.63784524952892</v>
       </c>
       <c r="O12" s="4" t="n">
-        <v>-18.12770819949092</v>
+        <v>-18.0627887151423</v>
       </c>
       <c r="P12" s="4" t="n">
-        <v>-19.64252456185818</v>
+        <v>-19.57244715426671</v>
       </c>
     </row>
     <row r="13">
@@ -939,46 +939,46 @@
         <v>78</v>
       </c>
       <c r="C13" s="4" t="n">
-        <v>-1.211387038158698</v>
+        <v>-1.207060352312375</v>
       </c>
       <c r="D13" s="4" t="n">
-        <v>-4.106206028384996</v>
+        <v>-4.090682790647364</v>
       </c>
       <c r="E13" s="4" t="n">
-        <v>-0.6541189177110525</v>
+        <v>-0.651570111098863</v>
       </c>
       <c r="F13" s="4" t="n">
-        <v>-3.090250794211116</v>
+        <v>-3.078660994783171</v>
       </c>
       <c r="G13" s="4" t="n">
-        <v>-8.763955727475476</v>
+        <v>-8.732257960444286</v>
       </c>
       <c r="H13" s="4" t="n">
-        <v>-8.468748387918581</v>
+        <v>-8.43758021908323</v>
       </c>
       <c r="I13" s="4" t="n">
-        <v>-4.703459947042688</v>
+        <v>-4.685867815666818</v>
       </c>
       <c r="J13" s="4" t="n">
-        <v>-6.457966044627277</v>
+        <v>-6.433097300908315</v>
       </c>
       <c r="K13" s="4" t="n">
-        <v>-3.950850656580251</v>
+        <v>-3.935611159782624</v>
       </c>
       <c r="L13" s="4" t="n">
-        <v>-2.23356843714204</v>
+        <v>-2.224795876068761</v>
       </c>
       <c r="M13" s="4" t="n">
-        <v>1.41738681886595</v>
+        <v>1.412860969408378</v>
       </c>
       <c r="N13" s="4" t="n">
-        <v>2.737639809710309</v>
+        <v>2.729012567583283</v>
       </c>
       <c r="O13" s="4" t="n">
-        <v>-1.542870178672274</v>
+        <v>-1.535501825064578</v>
       </c>
       <c r="P13" s="4" t="n">
-        <v>-6.43950494884902</v>
+        <v>-6.414552417424311</v>
       </c>
     </row>
     <row r="14">
@@ -991,46 +991,46 @@
         <v>82</v>
       </c>
       <c r="C14" s="4" t="n">
-        <v>-0.05441392996607419</v>
+        <v>-0.0541727739232698</v>
       </c>
       <c r="D14" s="4" t="n">
-        <v>-0.4466818379628918</v>
+        <v>-0.4439974659538777</v>
       </c>
       <c r="E14" s="4" t="n">
-        <v>-0.8418609575241192</v>
+        <v>-0.8385010872514513</v>
       </c>
       <c r="F14" s="4" t="n">
-        <v>1.729253940107441</v>
+        <v>1.723531896244829</v>
       </c>
       <c r="G14" s="4" t="n">
-        <v>-0.03025016324797036</v>
+        <v>-0.02943694337238867</v>
       </c>
       <c r="H14" s="4" t="n">
-        <v>3.93109822497405</v>
+        <v>3.917787151510346</v>
       </c>
       <c r="I14" s="4" t="n">
-        <v>0.1825663523968615</v>
+        <v>0.1828738593781338</v>
       </c>
       <c r="J14" s="4" t="n">
-        <v>3.379668582910725</v>
+        <v>3.369255364453565</v>
       </c>
       <c r="K14" s="4" t="n">
-        <v>0.875225125234337</v>
+        <v>0.8732947286165924</v>
       </c>
       <c r="L14" s="4" t="n">
-        <v>-4.867235924515747</v>
+        <v>-4.848314933172027</v>
       </c>
       <c r="M14" s="4" t="n">
-        <v>-1.40474918075887</v>
+        <v>-1.399034816070035</v>
       </c>
       <c r="N14" s="4" t="n">
-        <v>-5.041238765788862</v>
+        <v>-5.021464794151136</v>
       </c>
       <c r="O14" s="4" t="n">
-        <v>-12.80743555174264</v>
+        <v>-12.75803465644127</v>
       </c>
       <c r="P14" s="4" t="n">
-        <v>-11.3368183875751</v>
+        <v>-11.29260119791268</v>
       </c>
     </row>
     <row r="15">
@@ -1043,46 +1043,46 @@
         <v>89</v>
       </c>
       <c r="C15" s="4" t="n">
-        <v>-5.302427084255179</v>
+        <v>-5.282242776389765</v>
       </c>
       <c r="D15" s="4" t="n">
-        <v>-10.28787904077988</v>
+        <v>-10.24768529358822</v>
       </c>
       <c r="E15" s="4" t="n">
-        <v>-11.81020276529599</v>
+        <v>-11.76501906174308</v>
       </c>
       <c r="F15" s="4" t="n">
-        <v>-15.05711034886892</v>
+        <v>-14.99936634941976</v>
       </c>
       <c r="G15" s="4" t="n">
-        <v>-13.35084372319621</v>
+        <v>-13.29940041951131</v>
       </c>
       <c r="H15" s="4" t="n">
-        <v>-13.0570123268786</v>
+        <v>-13.00647027629591</v>
       </c>
       <c r="I15" s="4" t="n">
-        <v>-17.64809227385616</v>
+        <v>-17.58005144936519</v>
       </c>
       <c r="J15" s="4" t="n">
-        <v>-12.49246581183419</v>
+        <v>-12.44311943731012</v>
       </c>
       <c r="K15" s="4" t="n">
-        <v>-11.43081261090303</v>
+        <v>-11.38610310312493</v>
       </c>
       <c r="L15" s="4" t="n">
-        <v>-11.1601280068145</v>
+        <v>-11.11636240939758</v>
       </c>
       <c r="M15" s="4" t="n">
-        <v>-14.74896783072248</v>
+        <v>-14.69228881549038</v>
       </c>
       <c r="N15" s="4" t="n">
-        <v>-15.84687312077135</v>
+        <v>-15.785073266643</v>
       </c>
       <c r="O15" s="4" t="n">
-        <v>-9.5095801020599</v>
+        <v>-9.470236048053103</v>
       </c>
       <c r="P15" s="4" t="n">
-        <v>-8.134208794442308</v>
+        <v>-8.099945675851309</v>
       </c>
     </row>
     <row r="16">
@@ -1095,46 +1095,46 @@
         <v>68</v>
       </c>
       <c r="C16" s="4" t="n">
-        <v>-11.31696773197434</v>
+        <v>-11.27253365816102</v>
       </c>
       <c r="D16" s="4" t="n">
-        <v>-15.87461952517859</v>
+        <v>-15.81089729971379</v>
       </c>
       <c r="E16" s="4" t="n">
-        <v>-20.68892068804804</v>
+        <v>-20.60721919777272</v>
       </c>
       <c r="F16" s="4" t="n">
-        <v>-14.67735469928321</v>
+        <v>-14.6183800040167</v>
       </c>
       <c r="G16" s="4" t="n">
-        <v>-7.85924726124437</v>
+        <v>-7.826675538879194</v>
       </c>
       <c r="H16" s="4" t="n">
-        <v>-13.45507836527997</v>
+        <v>-13.40062872589232</v>
       </c>
       <c r="I16" s="4" t="n">
-        <v>-9.124735252521674</v>
+        <v>-9.08653682201944</v>
       </c>
       <c r="J16" s="4" t="n">
-        <v>-11.06972291920187</v>
+        <v>-11.02358020393359</v>
       </c>
       <c r="K16" s="4" t="n">
-        <v>-9.659866733134429</v>
+        <v>-9.619927092328119</v>
       </c>
       <c r="L16" s="4" t="n">
-        <v>-17.88812025816273</v>
+        <v>-17.81623689679281</v>
       </c>
       <c r="M16" s="4" t="n">
-        <v>-13.67377823969685</v>
+        <v>-13.61861304243509</v>
       </c>
       <c r="N16" s="4" t="n">
-        <v>-16.59532998301717</v>
+        <v>-16.52773802268732</v>
       </c>
       <c r="O16" s="4" t="n">
-        <v>-14.07154905361665</v>
+        <v>-14.01268708221721</v>
       </c>
       <c r="P16" s="4" t="n">
-        <v>-13.8254124373671</v>
+        <v>-13.76749359389552</v>
       </c>
     </row>
     <row r="17">
@@ -1147,46 +1147,46 @@
         <v>60</v>
       </c>
       <c r="C17" s="4" t="n">
-        <v>-7.493438320210352</v>
+        <v>-7.462363372620189</v>
       </c>
       <c r="D17" s="4" t="n">
-        <v>-5.773705197051157</v>
+        <v>-5.747359433318152</v>
       </c>
       <c r="E17" s="4" t="n">
-        <v>-2.835435002042871</v>
+        <v>-2.820998313941764</v>
       </c>
       <c r="F17" s="4" t="n">
-        <v>-2.706199689575982</v>
+        <v>-2.692164676898393</v>
       </c>
       <c r="G17" s="4" t="n">
-        <v>-3.24619338324387</v>
+        <v>-3.230556568299313</v>
       </c>
       <c r="H17" s="4" t="n">
-        <v>-2.949754510933232</v>
+        <v>-2.934637088924674</v>
       </c>
       <c r="I17" s="4" t="n">
-        <v>0.303512865490255</v>
+        <v>0.3059972363779622</v>
       </c>
       <c r="J17" s="4" t="n">
-        <v>3.175260650322009</v>
+        <v>3.166994103420286</v>
       </c>
       <c r="K17" s="4" t="n">
-        <v>1.444570552464732</v>
+        <v>1.442250584564377</v>
       </c>
       <c r="L17" s="4" t="n">
-        <v>10.61918423888734</v>
+        <v>10.58138811977051</v>
       </c>
       <c r="M17" s="4" t="n">
-        <v>5.402074482661611</v>
+        <v>5.384121336936417</v>
       </c>
       <c r="N17" s="4" t="n">
-        <v>5.43678438497431</v>
+        <v>5.420077190263093</v>
       </c>
       <c r="O17" s="4" t="n">
-        <v>5.01546071635768</v>
+        <v>5.001303933683189</v>
       </c>
       <c r="P17" s="4" t="n">
-        <v>5.267273190656176</v>
+        <v>5.252114249242446</v>
       </c>
     </row>
     <row r="18">
@@ -1199,46 +1199,46 @@
         <v>80</v>
       </c>
       <c r="C18" s="4" t="n">
-        <v>6.256561679790593</v>
+        <v>6.233391057447186</v>
       </c>
       <c r="D18" s="4" t="n">
-        <v>7.146892067953054</v>
+        <v>7.122140053296633</v>
       </c>
       <c r="E18" s="4" t="n">
-        <v>5.502988814519142</v>
+        <v>5.484337361631681</v>
       </c>
       <c r="F18" s="4" t="n">
-        <v>3.13244079230288</v>
+        <v>3.123478161282101</v>
       </c>
       <c r="G18" s="4" t="n">
-        <v>6.348868304950486</v>
+        <v>6.326387966596769</v>
       </c>
       <c r="H18" s="4" t="n">
-        <v>4.144358464653557</v>
+        <v>4.131448816801566</v>
       </c>
       <c r="I18" s="4" t="n">
-        <v>5.312811547765449</v>
+        <v>5.295148773724449</v>
       </c>
       <c r="J18" s="4" t="n">
-        <v>4.845758313599035</v>
+        <v>4.830377058706574</v>
       </c>
       <c r="K18" s="4" t="n">
-        <v>9.798754070027236</v>
+        <v>9.762552552754336</v>
       </c>
       <c r="L18" s="4" t="n">
-        <v>6.441963397598315</v>
+        <v>6.419412197379735</v>
       </c>
       <c r="M18" s="4" t="n">
-        <v>7.492511325831984</v>
+        <v>7.465323617318816</v>
       </c>
       <c r="N18" s="4" t="n">
-        <v>12.545053993793</v>
+        <v>12.49887665532586</v>
       </c>
       <c r="O18" s="4" t="n">
-        <v>10.87121974182731</v>
+        <v>10.83276845933791</v>
       </c>
       <c r="P18" s="4" t="n">
-        <v>9.869877474998702</v>
+        <v>9.835447582575114</v>
       </c>
     </row>
     <row r="19">
@@ -1251,46 +1251,46 @@
         <v>82</v>
       </c>
       <c r="C19" s="4" t="n">
-        <v>-6.151974905576104</v>
+        <v>-6.124855922177822</v>
       </c>
       <c r="D19" s="4" t="n">
-        <v>-5.326502970084235</v>
+        <v>-5.300778026834891</v>
       </c>
       <c r="E19" s="4" t="n">
-        <v>-2.062668079050994</v>
+        <v>-2.050891187142561</v>
       </c>
       <c r="F19" s="4" t="n">
-        <v>-0.7125974867818172</v>
+        <v>-0.7060690385165813</v>
       </c>
       <c r="G19" s="4" t="n">
-        <v>-4.915155166317497</v>
+        <v>-4.892059223051881</v>
       </c>
       <c r="H19" s="4" t="n">
-        <v>-5.840832499844126</v>
+        <v>-5.812977347317364</v>
       </c>
       <c r="I19" s="4" t="n">
-        <v>-13.25891896684672</v>
+        <v>-13.20043391857822</v>
       </c>
       <c r="J19" s="4" t="n">
-        <v>-12.50966347949311</v>
+        <v>-12.45382586428682</v>
       </c>
       <c r="K19" s="4" t="n">
-        <v>-15.01956421660754</v>
+        <v>-14.95465705468308</v>
       </c>
       <c r="L19" s="4" t="n">
-        <v>-12.20836609431786</v>
+        <v>-12.15469610431614</v>
       </c>
       <c r="M19" s="4" t="n">
-        <v>-8.747266262346962</v>
+        <v>-8.708474813544882</v>
       </c>
       <c r="N19" s="4" t="n">
-        <v>-8.71659993547059</v>
+        <v>-8.676942364187163</v>
       </c>
       <c r="O19" s="4" t="n">
-        <v>-7.918425167396585</v>
+        <v>-7.880899342940999</v>
       </c>
       <c r="P19" s="4" t="n">
-        <v>-6.44604315238189</v>
+        <v>-6.414552417424325</v>
       </c>
     </row>
     <row r="20">
@@ -1303,46 +1303,46 @@
         <v>92</v>
       </c>
       <c r="C20" s="4" t="n">
-        <v>7.289170375442197</v>
+        <v>7.26038137280257</v>
       </c>
       <c r="D20" s="4" t="n">
-        <v>5.679123776748192</v>
+        <v>5.659272591229708</v>
       </c>
       <c r="E20" s="4" t="n">
-        <v>8.548660964132495</v>
+        <v>8.515749234413711</v>
       </c>
       <c r="F20" s="4" t="n">
-        <v>6.505465688887156</v>
+        <v>6.481511114697653</v>
       </c>
       <c r="G20" s="4" t="n">
-        <v>0.5263783838223546</v>
+        <v>0.527533767395397</v>
       </c>
       <c r="H20" s="4" t="n">
-        <v>-0.2649393630573158</v>
+        <v>-0.2593268327728993</v>
       </c>
       <c r="I20" s="4" t="n">
-        <v>-2.528794135374646</v>
+        <v>-2.512833001742841</v>
       </c>
       <c r="J20" s="4" t="n">
-        <v>-5.177432775086743</v>
+        <v>-5.149744865276851</v>
       </c>
       <c r="K20" s="4" t="n">
-        <v>-6.329848476043765</v>
+        <v>-6.298375203777987</v>
       </c>
       <c r="L20" s="4" t="n">
-        <v>-7.185020786054494</v>
+        <v>-7.14975425239853</v>
       </c>
       <c r="M20" s="4" t="n">
-        <v>-8.482993243774985</v>
+        <v>-8.443111968320821</v>
       </c>
       <c r="N20" s="4" t="n">
-        <v>-6.27064800279576</v>
+        <v>-6.239177527112261</v>
       </c>
       <c r="O20" s="4" t="n">
-        <v>-9.969859629987688</v>
+        <v>-9.92141695532937</v>
       </c>
       <c r="P20" s="4" t="n">
-        <v>-10.81434517296245</v>
+        <v>-10.76237850438137</v>
       </c>
     </row>
     <row r="21">
@@ -1352,49 +1352,49 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="C21" s="4" t="n">
-        <v>-0.8594513921053917</v>
+        <v>-0.8623522720673478</v>
       </c>
       <c r="D21" s="4" t="n">
-        <v>1.450736055895526</v>
+        <v>1.452067898375653</v>
       </c>
       <c r="E21" s="4" t="n">
-        <v>2.364074389215304</v>
+        <v>2.368261387097327</v>
       </c>
       <c r="F21" s="4" t="n">
-        <v>9.037692671052163</v>
+        <v>9.057596159827732</v>
       </c>
       <c r="G21" s="4" t="n">
-        <v>8.501304030334502</v>
+        <v>8.519748535437607</v>
       </c>
       <c r="H21" s="4" t="n">
-        <v>8.801440874342852</v>
+        <v>8.819926796082733</v>
       </c>
       <c r="I21" s="4" t="n">
-        <v>11.99350552732086</v>
+        <v>12.01908961645837</v>
       </c>
       <c r="J21" s="4" t="n">
-        <v>11.52846124056021</v>
+        <v>11.55250544651809</v>
       </c>
       <c r="K21" s="4" t="n">
-        <v>10.81603238080398</v>
+        <v>10.83894476097368</v>
       </c>
       <c r="L21" s="4" t="n">
-        <v>7.999472171243937</v>
+        <v>8.015493301738729</v>
       </c>
       <c r="M21" s="4" t="n">
-        <v>10.42043904127347</v>
+        <v>10.44270730021113</v>
       </c>
       <c r="N21" s="4" t="n">
-        <v>8.48919355563504</v>
+        <v>8.506389440327069</v>
       </c>
       <c r="O21" s="4" t="n">
-        <v>8.068048590613763</v>
+        <v>8.083297969296105</v>
       </c>
       <c r="P21" s="4" t="n">
-        <v>10.01291726959502</v>
+        <v>10.03281600362803</v>
       </c>
     </row>
     <row r="22">
@@ -1404,49 +1404,49 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>137</v>
+        <v>132</v>
       </c>
       <c r="C22" s="4" t="n">
-        <v>2.251087227235281</v>
+        <v>2.315781791075885</v>
       </c>
       <c r="D22" s="4" t="n">
-        <v>2.099816291375099</v>
+        <v>2.143309362727393</v>
       </c>
       <c r="E22" s="4" t="n">
-        <v>-4.465020911480643</v>
+        <v>-4.640836598908791</v>
       </c>
       <c r="F22" s="4" t="n">
-        <v>-3.608506978622771</v>
+        <v>-3.745967269406762</v>
       </c>
       <c r="G22" s="4" t="n">
-        <v>-4.469175850484341</v>
+        <v>-4.640652472628595</v>
       </c>
       <c r="H22" s="4" t="n">
-        <v>-3.768081569870951</v>
+        <v>-3.924788051896542</v>
       </c>
       <c r="I22" s="4" t="n">
-        <v>-3.120419059486878</v>
+        <v>-3.256884227568456</v>
       </c>
       <c r="J22" s="4" t="n">
-        <v>-3.575116035930172</v>
+        <v>-3.735058535705079</v>
       </c>
       <c r="K22" s="4" t="n">
-        <v>-2.178357153463892</v>
+        <v>-2.281500372227306</v>
       </c>
       <c r="L22" s="4" t="n">
-        <v>-5.20314156710284</v>
+        <v>-5.420319104017722</v>
       </c>
       <c r="M22" s="4" t="n">
-        <v>-6.876031262623073</v>
+        <v>-7.14074356844975</v>
       </c>
       <c r="N22" s="4" t="n">
-        <v>-5.686334825753384</v>
+        <v>-5.919607135512045</v>
       </c>
       <c r="O22" s="4" t="n">
-        <v>-5.659088369456889</v>
+        <v>-5.906697992125302</v>
       </c>
       <c r="P22" s="4" t="n">
-        <v>-5.421202375459735</v>
+        <v>-5.656976659848844</v>
       </c>
     </row>
     <row r="23">
@@ -1456,49 +1456,49 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>175</v>
+        <v>171</v>
       </c>
       <c r="C23" s="4" t="n">
-        <v>-2.207724034495563</v>
+        <v>-2.263922007208798</v>
       </c>
       <c r="D23" s="4" t="n">
-        <v>5.06589715773471</v>
+        <v>5.160509413010494</v>
       </c>
       <c r="E23" s="4" t="n">
-        <v>7.530249230359146</v>
+        <v>7.680263396208503</v>
       </c>
       <c r="F23" s="4" t="n">
-        <v>6.82873033724789</v>
+        <v>6.96952360737334</v>
       </c>
       <c r="G23" s="4" t="n">
-        <v>5.726779526998079</v>
+        <v>5.839718710644512</v>
       </c>
       <c r="H23" s="4" t="n">
-        <v>8.309520014835826</v>
+        <v>8.474000333652114</v>
       </c>
       <c r="I23" s="4" t="n">
-        <v>5.687067483235801</v>
+        <v>5.792338479323902</v>
       </c>
       <c r="J23" s="4" t="n">
-        <v>6.37695917186889</v>
+        <v>6.492112630080662</v>
       </c>
       <c r="K23" s="4" t="n">
-        <v>4.598517569153103</v>
+        <v>4.680747419440856</v>
       </c>
       <c r="L23" s="4" t="n">
-        <v>6.629864394213058</v>
+        <v>6.748920505947808</v>
       </c>
       <c r="M23" s="4" t="n">
-        <v>6.752024687861933</v>
+        <v>6.879492440740549</v>
       </c>
       <c r="N23" s="4" t="n">
-        <v>3.930682489160631</v>
+        <v>3.989898989898983</v>
       </c>
       <c r="O23" s="4" t="n">
-        <v>6.961992058382556</v>
+        <v>7.078416308778777</v>
       </c>
       <c r="P23" s="4" t="n">
-        <v>7.203798726264466</v>
+        <v>7.328137641055065</v>
       </c>
     </row>
     <row r="24">
@@ -1508,49 +1508,49 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>170</v>
+        <v>167</v>
       </c>
       <c r="C24" s="4" t="n">
-        <v>-1.31696773197482</v>
+        <v>-1.349530483709074</v>
       </c>
       <c r="D24" s="4" t="n">
-        <v>-4.693247227291742</v>
+        <v>-4.786800529893704</v>
       </c>
       <c r="E24" s="4" t="n">
-        <v>-2.146939463300228</v>
+        <v>-2.191144075632032</v>
       </c>
       <c r="F24" s="4" t="n">
-        <v>-2.016686330692863</v>
+        <v>-2.053917312645659</v>
       </c>
       <c r="G24" s="4" t="n">
-        <v>0.3860689248233342</v>
+        <v>0.3877261875720706</v>
       </c>
       <c r="H24" s="4" t="n">
-        <v>-2.257665608049237</v>
+        <v>-2.30535703557053</v>
       </c>
       <c r="I24" s="4" t="n">
-        <v>-3.51886991355682</v>
+        <v>-3.593274447565065</v>
       </c>
       <c r="J24" s="4" t="n">
-        <v>2.225711393544273</v>
+        <v>2.250649752121205</v>
       </c>
       <c r="K24" s="4" t="n">
-        <v>3.669021576377631</v>
+        <v>3.723384261948702</v>
       </c>
       <c r="L24" s="4" t="n">
-        <v>4.343579715260447</v>
+        <v>4.405392944383955</v>
       </c>
       <c r="M24" s="4" t="n">
-        <v>3.549219386073226</v>
+        <v>3.601837224856801</v>
       </c>
       <c r="N24" s="4" t="n">
-        <v>3.591146952554368</v>
+        <v>3.63622038220209</v>
       </c>
       <c r="O24" s="4" t="n">
-        <v>0.8302965619059037</v>
+        <v>0.8207561904187344</v>
       </c>
       <c r="P24" s="4" t="n">
-        <v>-1.279781836047981</v>
+        <v>-1.324732058143297</v>
       </c>
     </row>
     <row r="25">
@@ -2185,10 +2185,8 @@
           <t>X &gt; -0.5425</t>
         </is>
       </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>3977~3990</t>
-        </is>
+      <c r="B6" t="n">
+        <v>3977</v>
       </c>
       <c r="C6" s="4" t="n">
         <v>0.01282734395042695</v>
@@ -2239,10 +2237,8 @@
           <t>X &gt; -0.5238</t>
         </is>
       </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>3955~3968</t>
-        </is>
+      <c r="B7" t="n">
+        <v>3955</v>
       </c>
       <c r="C7" s="4" t="n">
         <v>0.02672297011260127</v>
@@ -2293,10 +2289,8 @@
           <t>X &gt; -0.5051</t>
         </is>
       </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>3935~3948</t>
-        </is>
+      <c r="B8" t="n">
+        <v>3935</v>
       </c>
       <c r="C8" s="4" t="n">
         <v>0.09014830592984424</v>
@@ -2347,10 +2341,8 @@
           <t>X &gt; -0.4864</t>
         </is>
       </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>3896~3909</t>
-        </is>
+      <c r="B9" t="n">
+        <v>3896</v>
       </c>
       <c r="C9" s="4" t="n">
         <v>0.0008057319772802884</v>
@@ -2401,10 +2393,8 @@
           <t>X &gt; -0.4677</t>
         </is>
       </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>3840~3853</t>
-        </is>
+      <c r="B10" t="n">
+        <v>3840</v>
       </c>
       <c r="C10" s="4" t="n">
         <v>-0.1186654159795069</v>
@@ -2455,10 +2445,8 @@
           <t>X &gt; -0.449</t>
         </is>
       </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>3780~3793</t>
-        </is>
+      <c r="B11" t="n">
+        <v>3780</v>
       </c>
       <c r="C11" s="4" t="n">
         <v>-0.1338285126697656</v>
@@ -2509,10 +2497,8 @@
           <t>X &gt; -0.4303</t>
         </is>
       </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>3716~3729</t>
-        </is>
+      <c r="B12" t="n">
+        <v>3716</v>
       </c>
       <c r="C12" s="4" t="n">
         <v>-0.09333105284606802</v>
@@ -2563,10 +2549,8 @@
           <t>X &gt; -0.4116</t>
         </is>
       </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>3659~3672</t>
-        </is>
+      <c r="B13" t="n">
+        <v>3659</v>
       </c>
       <c r="C13" s="4" t="n">
         <v>-0.01522481258470521</v>
@@ -2617,10 +2601,8 @@
           <t>X &gt; -0.3929</t>
         </is>
       </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>3581~3594</t>
-        </is>
+      <c r="B14" t="n">
+        <v>3581</v>
       </c>
       <c r="C14" s="4" t="n">
         <v>0.01073530249453114</v>
@@ -2671,10 +2653,8 @@
           <t>X &gt; -0.3742</t>
         </is>
       </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>3499~3512</t>
-        </is>
+      <c r="B15" t="n">
+        <v>3499</v>
       </c>
       <c r="C15" s="4" t="n">
         <v>0.01225644061006648</v>
@@ -2725,10 +2705,8 @@
           <t>X &gt; -0.3555</t>
         </is>
       </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>3410~3423</t>
-        </is>
+      <c r="B16" t="n">
+        <v>3410</v>
       </c>
       <c r="C16" s="4" t="n">
         <v>0.1504413175346997</v>
@@ -2779,10 +2757,8 @@
           <t>X &gt; -0.3368</t>
         </is>
       </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>3342~3355</t>
-        </is>
+      <c r="B17" t="n">
+        <v>3342</v>
       </c>
       <c r="C17" s="4" t="n">
         <v>0.3828657036350336</v>
@@ -2833,10 +2809,8 @@
           <t>X &gt; -0.318</t>
         </is>
       </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>3282~3295</t>
-        </is>
+      <c r="B18" t="n">
+        <v>3282</v>
       </c>
       <c r="C18" s="4" t="n">
         <v>0.5262885386671172</v>
@@ -2887,10 +2861,8 @@
           <t>X &gt; -0.2993</t>
         </is>
       </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>3202~3215</t>
-        </is>
+      <c r="B19" t="n">
+        <v>3202</v>
       </c>
       <c r="C19" s="4" t="n">
         <v>0.3837000934758663</v>
@@ -2941,10 +2913,8 @@
           <t>X &gt; -0.2806</t>
         </is>
       </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>3120~3133</t>
-        </is>
+      <c r="B20" t="n">
+        <v>3120</v>
       </c>
       <c r="C20" s="4" t="n">
         <v>0.5547582964513751</v>
@@ -2995,10 +2965,8 @@
           <t>X &gt; -0.2619</t>
         </is>
       </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>3028~3041</t>
-        </is>
+      <c r="B21" t="n">
+        <v>3028</v>
       </c>
       <c r="C21" s="4" t="n">
         <v>0.3510207393099236</v>
@@ -3049,10 +3017,8 @@
           <t>X &gt; -0.2432</t>
         </is>
       </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>2876~2888</t>
-        </is>
+      <c r="B22" t="n">
+        <v>2876</v>
       </c>
       <c r="C22" s="4" t="n">
         <v>0.415148937407757</v>
@@ -3103,10 +3069,8 @@
           <t>X &gt; -0.2245</t>
         </is>
       </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>2744~2751</t>
-        </is>
+      <c r="B23" t="n">
+        <v>2744</v>
       </c>
       <c r="C23" s="4" t="n">
         <v>0.323719077100094</v>
@@ -3157,10 +3121,8 @@
           <t>X &gt; -0.2058</t>
         </is>
       </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>2573~2576</t>
-        </is>
+      <c r="B24" t="n">
+        <v>2573</v>
       </c>
       <c r="C24" s="4" t="n">
         <v>0.495692114572627</v>
@@ -3211,10 +3173,8 @@
           <t>X &gt; -0.1871</t>
         </is>
       </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>2406~2406</t>
-        </is>
+      <c r="B25" t="n">
+        <v>2406</v>
       </c>
       <c r="C25" s="4" t="n">
         <v>0.6237686623336671</v>
@@ -3265,10 +3225,8 @@
           <t>X &gt; -0.1684</t>
         </is>
       </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>2253~2253</t>
-        </is>
+      <c r="B26" t="n">
+        <v>2253</v>
       </c>
       <c r="C26" s="4" t="n">
         <v>1.035190175129571</v>
@@ -3319,10 +3277,8 @@
           <t>X &gt; -0.1497</t>
         </is>
       </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>2087~2087</t>
-        </is>
+      <c r="B27" t="n">
+        <v>2087</v>
       </c>
       <c r="C27" s="4" t="n">
         <v>0.9804476404991789</v>
@@ -3373,10 +3329,8 @@
           <t>X &gt; -0.131</t>
         </is>
       </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>1926~1926</t>
-        </is>
+      <c r="B28" t="n">
+        <v>1926</v>
       </c>
       <c r="C28" s="4" t="n">
         <v>1.66024807646707</v>
@@ -3427,10 +3381,8 @@
           <t>X &gt; -0.1123</t>
         </is>
       </c>
-      <c r="B29" t="inlineStr">
-        <is>
-          <t>1750~1750</t>
-        </is>
+      <c r="B29" t="n">
+        <v>1750</v>
       </c>
       <c r="C29" s="4" t="n">
         <v>1.506561679790025</v>
@@ -3481,10 +3433,8 @@
           <t>X &gt; -0.09354</t>
         </is>
       </c>
-      <c r="B30" t="inlineStr">
-        <is>
-          <t>1511~1511</t>
-        </is>
+      <c r="B30" t="n">
+        <v>1511</v>
       </c>
       <c r="C30" s="4" t="n">
         <v>1.113444538823778</v>
@@ -3535,10 +3485,8 @@
           <t>X &gt; -0.07483</t>
         </is>
       </c>
-      <c r="B31" t="inlineStr">
-        <is>
-          <t>1286~1286</t>
-        </is>
+      <c r="B31" t="n">
+        <v>1286</v>
       </c>
       <c r="C31" s="4" t="n">
         <v>2.794275521158603</v>
@@ -3589,10 +3537,8 @@
           <t>X &gt; -0.05613</t>
         </is>
       </c>
-      <c r="B32" t="inlineStr">
-        <is>
-          <t>1065~1065</t>
-        </is>
+      <c r="B32" t="n">
+        <v>1065</v>
       </c>
       <c r="C32" s="4" t="n">
         <v>3.562899707959041</v>
@@ -3643,10 +3589,8 @@
           <t>X &gt; -0.03742</t>
         </is>
       </c>
-      <c r="B33" t="inlineStr">
-        <is>
-          <t>833~833</t>
-        </is>
+      <c r="B33" t="n">
+        <v>833</v>
       </c>
       <c r="C33" s="4" t="n">
         <v>3.809082688193385</v>
@@ -3697,10 +3641,8 @@
           <t>X &gt; -0.01871</t>
         </is>
       </c>
-      <c r="B34" t="inlineStr">
-        <is>
-          <t>608~608</t>
-        </is>
+      <c r="B34" t="n">
+        <v>608</v>
       </c>
       <c r="C34" s="4" t="n">
         <v>2.276298521895292</v>
@@ -3751,10 +3693,8 @@
           <t>X &gt; 0</t>
         </is>
       </c>
-      <c r="B35" t="inlineStr">
-        <is>
-          <t>0~0</t>
-        </is>
+      <c r="B35" t="n">
+        <v>0</v>
       </c>
       <c r="C35" s="4" t="inlineStr"/>
       <c r="D35" s="4" t="inlineStr"/>
@@ -3911,10 +3851,8 @@
           <t>X &lt; -0.5425</t>
         </is>
       </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>82~82</t>
-        </is>
+      <c r="B6" t="n">
+        <v>82</v>
       </c>
       <c r="C6" s="4" t="n">
         <v>4.823634850521728</v>
@@ -3965,10 +3903,8 @@
           <t>X &lt; -0.5238</t>
         </is>
       </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>104~104</t>
-        </is>
+      <c r="B7" t="n">
+        <v>104</v>
       </c>
       <c r="C7" s="4" t="n">
         <v>3.275792449020798</v>
@@ -4019,10 +3955,8 @@
           <t>X &lt; -0.5051</t>
         </is>
       </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>124~124</t>
-        </is>
+      <c r="B8" t="n">
+        <v>124</v>
       </c>
       <c r="C8" s="4" t="n">
         <v>0.7323681314029216</v>
@@ -4073,10 +4007,8 @@
           <t>X &lt; -0.4864</t>
         </is>
       </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>163~163</t>
-        </is>
+      <c r="B9" t="n">
+        <v>163</v>
       </c>
       <c r="C9" s="4" t="n">
         <v>2.721285606170397</v>
@@ -4127,10 +4059,8 @@
           <t>X &lt; -0.4677</t>
         </is>
       </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>219~219</t>
-        </is>
+      <c r="B10" t="n">
+        <v>219</v>
       </c>
       <c r="C10" s="4" t="n">
         <v>4.127566246000065</v>
@@ -4181,10 +4111,8 @@
           <t>X &lt; -0.449</t>
         </is>
       </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>279~279</t>
-        </is>
+      <c r="B11" t="n">
+        <v>279</v>
       </c>
       <c r="C11" s="4" t="n">
         <v>3.420540174413674</v>
@@ -4235,10 +4163,8 @@
           <t>X &lt; -0.4303</t>
         </is>
       </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>343~343</t>
-        </is>
+      <c r="B12" t="n">
+        <v>343</v>
       </c>
       <c r="C12" s="4" t="n">
         <v>2.317057306612178</v>
@@ -4289,10 +4215,8 @@
           <t>X &lt; -0.4116</t>
         </is>
       </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>400~400</t>
-        </is>
+      <c r="B13" t="n">
+        <v>400</v>
       </c>
       <c r="C13" s="4" t="n">
         <v>1.256561679790025</v>
@@ -4343,10 +4267,8 @@
           <t>X &lt; -0.3929</t>
         </is>
       </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>478~478</t>
-        </is>
+      <c r="B14" t="n">
+        <v>478</v>
       </c>
       <c r="C14" s="4" t="n">
         <v>0.8538420145180581</v>
@@ -4397,10 +4319,8 @@
           <t>X &lt; -0.3742</t>
         </is>
       </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>560~560</t>
-        </is>
+      <c r="B15" t="n">
+        <v>560</v>
       </c>
       <c r="C15" s="4" t="n">
         <v>0.7208473940757401</v>
@@ -4451,10 +4371,8 @@
           <t>X &lt; -0.3555</t>
         </is>
       </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>649~649</t>
-        </is>
+      <c r="B16" t="n">
+        <v>649</v>
       </c>
       <c r="C16" s="4" t="n">
         <v>-0.1051486437847018</v>
@@ -4505,10 +4423,8 @@
           <t>X &lt; -0.3368</t>
         </is>
       </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>717~717</t>
-        </is>
+      <c r="B17" t="n">
+        <v>717</v>
       </c>
       <c r="C17" s="4" t="n">
         <v>-1.16847318771346</v>
@@ -4559,10 +4475,8 @@
           <t>X &lt; -0.318</t>
         </is>
       </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>777~777</t>
-        </is>
+      <c r="B18" t="n">
+        <v>777</v>
       </c>
       <c r="C18" s="4" t="n">
         <v>-1.656887483659148</v>
@@ -4613,10 +4527,8 @@
           <t>X &lt; -0.2993</t>
         </is>
       </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>857~857</t>
-        </is>
+      <c r="B19" t="n">
+        <v>857</v>
       </c>
       <c r="C19" s="4" t="n">
         <v>-0.9181757764526779</v>
@@ -4667,10 +4579,8 @@
           <t>X &lt; -0.2806</t>
         </is>
       </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>939~939</t>
-        </is>
+      <c r="B20" t="n">
+        <v>939</v>
       </c>
       <c r="C20" s="4" t="n">
         <v>-1.375227457590171</v>
@@ -4721,10 +4631,8 @@
           <t>X &lt; -0.2619</t>
         </is>
       </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>1031~1031</t>
-        </is>
+      <c r="B21" t="n">
+        <v>1031</v>
       </c>
       <c r="C21" s="4" t="n">
         <v>-0.6020707159422756</v>
@@ -4775,10 +4683,8 @@
           <t>X &lt; -0.2432</t>
         </is>
       </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>1183~1184</t>
-        </is>
+      <c r="B22" t="n">
+        <v>1183</v>
       </c>
       <c r="C22" s="4" t="n">
         <v>-0.63533021210187</v>
@@ -4829,10 +4735,8 @@
           <t>X &lt; -0.2245</t>
         </is>
       </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>1315~1321</t>
-        </is>
+      <c r="B23" t="n">
+        <v>1315</v>
       </c>
       <c r="C23" s="4" t="n">
         <v>-0.3359818478405643</v>
@@ -4883,10 +4787,8 @@
           <t>X &lt; -0.2058</t>
         </is>
       </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>1486~1496</t>
-        </is>
+      <c r="B24" t="n">
+        <v>1486</v>
       </c>
       <c r="C24" s="4" t="n">
         <v>-0.5549356464131847</v>
@@ -4937,10 +4839,8 @@
           <t>X &lt; -0.1871</t>
         </is>
       </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>1653~1666</t>
-        </is>
+      <c r="B25" t="n">
+        <v>1653</v>
       </c>
       <c r="C25" s="4" t="n">
         <v>-0.6326940224908881</v>
@@ -4991,10 +4891,8 @@
           <t>X &lt; -0.1684</t>
         </is>
       </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>1806~1819</t>
-        </is>
+      <c r="B26" t="n">
+        <v>1806</v>
       </c>
       <c r="C26" s="4" t="n">
         <v>-1.03659390019898</v>
@@ -5045,10 +4943,8 @@
           <t>X &lt; -0.1497</t>
         </is>
       </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>1972~1985</t>
-        </is>
+      <c r="B27" t="n">
+        <v>1972</v>
       </c>
       <c r="C27" s="4" t="n">
         <v>-0.8057808894794931</v>
@@ -5099,10 +4995,8 @@
           <t>X &lt; -0.131</t>
         </is>
       </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>2133~2146</t>
-        </is>
+      <c r="B28" t="n">
+        <v>2133</v>
       </c>
       <c r="C28" s="4" t="n">
         <v>-1.281881936239792</v>
@@ -5153,10 +5047,8 @@
           <t>X &lt; -0.1123</t>
         </is>
       </c>
-      <c r="B29" t="inlineStr">
-        <is>
-          <t>2309~2322</t>
-        </is>
+      <c r="B29" t="n">
+        <v>2309</v>
       </c>
       <c r="C29" s="4" t="n">
         <v>-0.9430507233107477</v>
@@ -5207,10 +5099,8 @@
           <t>X &lt; -0.09354</t>
         </is>
       </c>
-      <c r="B30" t="inlineStr">
-        <is>
-          <t>2548~2561</t>
-        </is>
+      <c r="B30" t="n">
+        <v>2548</v>
       </c>
       <c r="C30" s="4" t="n">
         <v>-0.4825050910026292</v>
@@ -5261,10 +5151,8 @@
           <t>X &lt; -0.07483</t>
         </is>
       </c>
-      <c r="B31" t="inlineStr">
-        <is>
-          <t>2773~2786</t>
-        </is>
+      <c r="B31" t="n">
+        <v>2773</v>
       </c>
       <c r="C31" s="4" t="n">
         <v>-1.129475649714642</v>
@@ -5315,10 +5203,8 @@
           <t>X &lt; -0.05613</t>
         </is>
       </c>
-      <c r="B32" t="inlineStr">
-        <is>
-          <t>2994~3007</t>
-        </is>
+      <c r="B32" t="n">
+        <v>2994</v>
       </c>
       <c r="C32" s="4" t="n">
         <v>-1.113325250705493</v>
@@ -5369,10 +5255,8 @@
           <t>X &lt; -0.03742</t>
         </is>
       </c>
-      <c r="B33" t="inlineStr">
-        <is>
-          <t>3226~3239</t>
-        </is>
+      <c r="B33" t="n">
+        <v>3226</v>
       </c>
       <c r="C33" s="4" t="n">
         <v>-0.841693954665061</v>
@@ -5423,10 +5307,8 @@
           <t>X &lt; -0.01871</t>
         </is>
       </c>
-      <c r="B34" t="inlineStr">
-        <is>
-          <t>3451~3464</t>
-        </is>
+      <c r="B34" t="n">
+        <v>3451</v>
       </c>
       <c r="C34" s="4" t="n">
         <v>-0.2705745788704874</v>
@@ -5477,10 +5359,8 @@
           <t>X &lt; 0</t>
         </is>
       </c>
-      <c r="B35" t="inlineStr">
-        <is>
-          <t>3731~3744</t>
-        </is>
+      <c r="B35" t="n">
+        <v>3731</v>
       </c>
       <c r="C35" s="4" t="n">
         <v>-0.1430109697826225</v>

--- a/workspaces/btc_daily_14days/drawdown/drawdown_120.xlsx
+++ b/workspaces/btc_daily_14days/drawdown/drawdown_120.xlsx
@@ -479,7 +479,7 @@
     <row r="3" ht="22" customHeight="1">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>Measures the winrate at horizon h days, given that Drawdown-120 is approximately at value x, minus the unconditional baseline winrate.</t>
+          <t>Measures the winrate at horizon h, given that Drawdown-120 is approximately at value x, minus the unconditional baseline winrate.</t>
         </is>
       </c>
     </row>
@@ -575,46 +575,46 @@
         <v>22</v>
       </c>
       <c r="C6" s="4" t="n">
-        <v>-2.48522726838592</v>
+        <v>-2.47275013901033</v>
       </c>
       <c r="D6" s="4" t="n">
-        <v>-8.624242243366872</v>
+        <v>-8.611380065522816</v>
       </c>
       <c r="E6" s="4" t="n">
-        <v>-22.61896017701461</v>
+        <v>-22.60600670247096</v>
       </c>
       <c r="F6" s="4" t="n">
-        <v>-8.892579709866965</v>
+        <v>-8.879640621230699</v>
       </c>
       <c r="G6" s="4" t="n">
-        <v>-13.96743810511781</v>
+        <v>-13.95436644404093</v>
       </c>
       <c r="H6" s="4" t="n">
-        <v>-9.137741995898494</v>
+        <v>-9.124731330021056</v>
       </c>
       <c r="I6" s="4" t="n">
-        <v>-9.224604360955652</v>
+        <v>-9.211566401583106</v>
       </c>
       <c r="J6" s="4" t="n">
-        <v>-9.693582038326738</v>
+        <v>-9.680425553349437</v>
       </c>
       <c r="K6" s="4" t="n">
-        <v>-5.217023576212931</v>
+        <v>-5.203843956079083</v>
       </c>
       <c r="L6" s="4" t="n">
-        <v>3.014001166228319</v>
+        <v>3.027392945665632</v>
       </c>
       <c r="M6" s="4" t="n">
-        <v>2.810224955180978</v>
+        <v>2.82367215058342</v>
       </c>
       <c r="N6" s="4" t="n">
-        <v>2.845413572493932</v>
+        <v>2.858859102825051</v>
       </c>
       <c r="O6" s="4" t="n">
-        <v>6.97031410275126</v>
+        <v>6.983867002340084</v>
       </c>
       <c r="P6" s="4" t="n">
-        <v>7.221811218939031</v>
+        <v>7.211381583238818</v>
       </c>
     </row>
     <row r="7">
@@ -627,46 +627,46 @@
         <v>20</v>
       </c>
       <c r="C7" s="4" t="n">
-        <v>-12.45221185192861</v>
+        <v>-12.43974356331218</v>
       </c>
       <c r="D7" s="4" t="n">
-        <v>-4.092328117644051</v>
+        <v>-4.079463016822103</v>
       </c>
       <c r="E7" s="4" t="n">
-        <v>5.48496520781589</v>
+        <v>5.497937846076212</v>
       </c>
       <c r="F7" s="4" t="n">
-        <v>-4.358407660502898</v>
+        <v>-4.345466138954869</v>
       </c>
       <c r="G7" s="4" t="n">
-        <v>5.080242194183882</v>
+        <v>5.093324396401087</v>
       </c>
       <c r="H7" s="4" t="n">
-        <v>5.378396235998963</v>
+        <v>5.39141399180204</v>
       </c>
       <c r="I7" s="4" t="n">
-        <v>5.295193621081566</v>
+        <v>5.308237785927155</v>
       </c>
       <c r="J7" s="4" t="n">
-        <v>-0.1625066043013277</v>
+        <v>-0.1493467329476204</v>
       </c>
       <c r="K7" s="4" t="n">
-        <v>9.764010182377525</v>
+        <v>9.777194411306112</v>
       </c>
       <c r="L7" s="4" t="n">
-        <v>8.917056726333087</v>
+        <v>8.930449895294743</v>
       </c>
       <c r="M7" s="4" t="n">
-        <v>13.71098089474658</v>
+        <v>13.72443009848551</v>
       </c>
       <c r="N7" s="4" t="n">
-        <v>8.751486907348777</v>
+        <v>8.764933131871992</v>
       </c>
       <c r="O7" s="4" t="n">
-        <v>-1.663874284441583</v>
+        <v>-1.650321970945001</v>
       </c>
       <c r="P7" s="4" t="n">
-        <v>3.585447582575398</v>
+        <v>3.57501794687952</v>
       </c>
     </row>
     <row r="8">
@@ -679,46 +679,46 @@
         <v>39</v>
       </c>
       <c r="C8" s="4" t="n">
-        <v>9.015242360267649</v>
+        <v>9.027727994477438</v>
       </c>
       <c r="D8" s="4" t="n">
-        <v>-0.2577928746162854</v>
+        <v>-0.244925476335986</v>
       </c>
       <c r="E8" s="4" t="n">
-        <v>12.1326333005573</v>
+        <v>12.14561027952269</v>
       </c>
       <c r="F8" s="4" t="n">
-        <v>7.150683001250492</v>
+        <v>7.163631472176114</v>
       </c>
       <c r="G8" s="4" t="n">
-        <v>14.28956001420016</v>
+        <v>14.3026472762896</v>
       </c>
       <c r="H8" s="4" t="n">
-        <v>17.14893201751656</v>
+        <v>17.16195562548631</v>
       </c>
       <c r="I8" s="4" t="n">
-        <v>17.06876831390026</v>
+        <v>17.08181760011371</v>
       </c>
       <c r="J8" s="4" t="n">
-        <v>14.04638061854768</v>
+        <v>14.05954577682413</v>
       </c>
       <c r="K8" s="4" t="n">
-        <v>19.11080039174468</v>
+        <v>19.12398752381434</v>
       </c>
       <c r="L8" s="4" t="n">
-        <v>23.38923696177967</v>
+        <v>23.40263379484898</v>
       </c>
       <c r="M8" s="4" t="n">
-        <v>23.1907000253732</v>
+        <v>23.20415101963742</v>
       </c>
       <c r="N8" s="4" t="n">
-        <v>20.66837827446631</v>
+        <v>20.68182599367284</v>
       </c>
       <c r="O8" s="4" t="n">
-        <v>25.38047224884836</v>
+        <v>25.39402628510122</v>
       </c>
       <c r="P8" s="4" t="n">
-        <v>25.63672963385744</v>
+        <v>25.62629999815812</v>
       </c>
     </row>
     <row r="9">
@@ -731,46 +731,46 @@
         <v>56</v>
       </c>
       <c r="C9" s="4" t="n">
-        <v>8.193113020442652</v>
+        <v>8.205597220102966</v>
       </c>
       <c r="D9" s="4" t="n">
-        <v>1.248515276311387</v>
+        <v>1.26138284375557</v>
       </c>
       <c r="E9" s="4" t="n">
-        <v>7.977025793673789</v>
+        <v>7.989999157987647</v>
       </c>
       <c r="F9" s="4" t="n">
-        <v>11.67142821131178</v>
+        <v>11.68437909928449</v>
       </c>
       <c r="G9" s="4" t="n">
-        <v>5.792171874354324</v>
+        <v>5.805253595695383</v>
       </c>
       <c r="H9" s="4" t="n">
-        <v>-2.819498717796151</v>
+        <v>-2.806486167026392</v>
       </c>
       <c r="I9" s="4" t="n">
-        <v>6.007584785833011</v>
+        <v>6.020628610892999</v>
       </c>
       <c r="J9" s="4" t="n">
-        <v>-1.589070572165106</v>
+        <v>-1.575912015215572</v>
       </c>
       <c r="K9" s="4" t="n">
-        <v>-1.650322518871981</v>
+        <v>-1.637142543727592</v>
       </c>
       <c r="L9" s="4" t="n">
-        <v>1.067565346329658</v>
+        <v>1.080956083503381</v>
       </c>
       <c r="M9" s="4" t="n">
-        <v>4.432014254189738</v>
+        <v>4.445461396621127</v>
       </c>
       <c r="N9" s="4" t="n">
-        <v>0.8981912600264224</v>
+        <v>0.9116362556124713</v>
       </c>
       <c r="O9" s="4" t="n">
-        <v>0.4783705635167266</v>
+        <v>0.4919229042491082</v>
       </c>
       <c r="P9" s="4" t="n">
-        <v>-2.843123845996033</v>
+        <v>-2.853553481693375</v>
       </c>
     </row>
     <row r="10">
@@ -783,46 +783,46 @@
         <v>60</v>
       </c>
       <c r="C10" s="4" t="n">
-        <v>0.8366096755069492</v>
+        <v>0.8490862664495396</v>
       </c>
       <c r="D10" s="4" t="n">
-        <v>-0.769000392235867</v>
+        <v>-0.7561357760017842</v>
       </c>
       <c r="E10" s="4" t="n">
-        <v>-11.13473333418563</v>
+        <v>-11.12177548266827</v>
       </c>
       <c r="F10" s="4" t="n">
-        <v>-14.33213992877891</v>
+        <v>-14.31920780576192</v>
       </c>
       <c r="G10" s="4" t="n">
-        <v>-4.897094832863992</v>
+        <v>-4.884020602985537</v>
       </c>
       <c r="H10" s="4" t="n">
-        <v>-6.26442330106174</v>
+        <v>-6.251413647215585</v>
       </c>
       <c r="I10" s="4" t="n">
-        <v>-11.34158812398757</v>
+        <v>-11.32855337529146</v>
       </c>
       <c r="J10" s="4" t="n">
-        <v>-15.13892929593312</v>
+        <v>-15.12577712248648</v>
       </c>
       <c r="K10" s="4" t="n">
-        <v>-10.21037387084348</v>
+        <v>-10.19719747568304</v>
       </c>
       <c r="L10" s="4" t="n">
-        <v>-17.7221256070715</v>
+        <v>-17.70874055078287</v>
       </c>
       <c r="M10" s="4" t="n">
-        <v>-16.26596323008839</v>
+        <v>-16.25252070863516</v>
       </c>
       <c r="N10" s="4" t="n">
-        <v>-16.23562022128356</v>
+        <v>-16.22217784046382</v>
       </c>
       <c r="O10" s="4" t="n">
-        <v>-18.32618502713117</v>
+        <v>-18.31263411370316</v>
       </c>
       <c r="P10" s="4" t="n">
-        <v>-18.08121908409127</v>
+        <v>-18.09164871979018</v>
       </c>
     </row>
     <row r="11">
@@ -835,46 +835,46 @@
         <v>64</v>
       </c>
       <c r="C11" s="4" t="n">
-        <v>-2.485212273683004</v>
+        <v>-2.472740288110309</v>
       </c>
       <c r="D11" s="4" t="n">
-        <v>-0.9765740426974006</v>
+        <v>-0.963711132996977</v>
       </c>
       <c r="E11" s="4" t="n">
-        <v>-7.602461194155993</v>
+        <v>-7.589502461786005</v>
       </c>
       <c r="F11" s="4" t="n">
-        <v>-2.799424292782639</v>
+        <v>-2.786485742624144</v>
       </c>
       <c r="G11" s="4" t="n">
-        <v>-6.455455025540502</v>
+        <v>-6.442383123907213</v>
       </c>
       <c r="H11" s="4" t="n">
-        <v>-4.600909135660601</v>
+        <v>-4.587899742101754</v>
       </c>
       <c r="I11" s="4" t="n">
-        <v>-4.686776065205699</v>
+        <v>-4.673739182268164</v>
       </c>
       <c r="J11" s="4" t="n">
-        <v>-3.594282404215797</v>
+        <v>-3.581126395832833</v>
       </c>
       <c r="K11" s="4" t="n">
-        <v>-0.5354529921620994</v>
+        <v>-0.5222739617265972</v>
       </c>
       <c r="L11" s="4" t="n">
-        <v>-4.50657751641954</v>
+        <v>-4.493189469072945</v>
       </c>
       <c r="M11" s="4" t="n">
-        <v>-7.834854748188306</v>
+        <v>-7.821411000992398</v>
       </c>
       <c r="N11" s="4" t="n">
-        <v>-10.92569782597164</v>
+        <v>-10.91225508241406</v>
       </c>
       <c r="O11" s="4" t="n">
-        <v>-16.03497625618748</v>
+        <v>-16.02142539079234</v>
       </c>
       <c r="P11" s="4" t="n">
-        <v>-12.6645524174246</v>
+        <v>-12.67498205312204</v>
       </c>
     </row>
     <row r="12">
@@ -887,46 +887,46 @@
         <v>57</v>
       </c>
       <c r="C12" s="4" t="n">
-        <v>-5.107203563659141</v>
+        <v>-5.094735845566781</v>
       </c>
       <c r="D12" s="4" t="n">
-        <v>-4.965571083847976</v>
+        <v>-4.952713313259103</v>
       </c>
       <c r="E12" s="4" t="n">
-        <v>3.384985633686767</v>
+        <v>3.397951566746357</v>
       </c>
       <c r="F12" s="4" t="n">
-        <v>0.01659920216764021</v>
+        <v>0.02953844163410224</v>
       </c>
       <c r="G12" s="4" t="n">
-        <v>-7.521412912977461</v>
+        <v>-7.508343144975939</v>
       </c>
       <c r="H12" s="4" t="n">
-        <v>-10.72754410815515</v>
+        <v>-10.71453955912523</v>
       </c>
       <c r="I12" s="4" t="n">
-        <v>-14.31719179189692</v>
+        <v>-14.30416097959297</v>
       </c>
       <c r="J12" s="4" t="n">
-        <v>-25.29644409684942</v>
+        <v>-25.28329867275902</v>
       </c>
       <c r="K12" s="4" t="n">
-        <v>-23.61245217687796</v>
+        <v>-23.59928240652057</v>
       </c>
       <c r="L12" s="4" t="n">
-        <v>-24.46815707766716</v>
+        <v>-24.45477559139727</v>
       </c>
       <c r="M12" s="4" t="n">
-        <v>-24.67939661756191</v>
+        <v>-24.66595714279237</v>
       </c>
       <c r="N12" s="4" t="n">
-        <v>-17.63784524952892</v>
+        <v>-17.62440387579992</v>
       </c>
       <c r="O12" s="4" t="n">
-        <v>-18.0627887151423</v>
+        <v>-18.0492382111812</v>
       </c>
       <c r="P12" s="4" t="n">
-        <v>-19.57244715426671</v>
+        <v>-19.58287678996565</v>
       </c>
     </row>
     <row r="13">
@@ -939,46 +939,46 @@
         <v>78</v>
       </c>
       <c r="C13" s="4" t="n">
-        <v>-1.207060352312375</v>
+        <v>-1.194590931895497</v>
       </c>
       <c r="D13" s="4" t="n">
-        <v>-4.090682790647364</v>
+        <v>-4.077826333519518</v>
       </c>
       <c r="E13" s="4" t="n">
-        <v>-0.651570111098863</v>
+        <v>-0.638609073400076</v>
       </c>
       <c r="F13" s="4" t="n">
-        <v>-3.078660994783171</v>
+        <v>-3.065725664094153</v>
       </c>
       <c r="G13" s="4" t="n">
-        <v>-8.732257960444286</v>
+        <v>-8.719190773830228</v>
       </c>
       <c r="H13" s="4" t="n">
-        <v>-8.43758021908323</v>
+        <v>-8.424575932933408</v>
       </c>
       <c r="I13" s="4" t="n">
-        <v>-4.685867815666818</v>
+        <v>-4.672833377238881</v>
       </c>
       <c r="J13" s="4" t="n">
-        <v>-6.433097300908315</v>
+        <v>-6.419944843228954</v>
       </c>
       <c r="K13" s="4" t="n">
-        <v>-3.935611159782624</v>
+        <v>-3.922435157994265</v>
       </c>
       <c r="L13" s="4" t="n">
-        <v>-2.224795876068761</v>
+        <v>-2.211408630264685</v>
       </c>
       <c r="M13" s="4" t="n">
-        <v>1.412860969408378</v>
+        <v>1.426305659571014</v>
       </c>
       <c r="N13" s="4" t="n">
-        <v>2.729012567583283</v>
+        <v>2.742456602139633</v>
       </c>
       <c r="O13" s="4" t="n">
-        <v>-1.535501825064578</v>
+        <v>-1.521950294369915</v>
       </c>
       <c r="P13" s="4" t="n">
-        <v>-6.414552417424311</v>
+        <v>-6.42498205312188</v>
       </c>
     </row>
     <row r="14">
@@ -991,46 +991,46 @@
         <v>82</v>
       </c>
       <c r="C14" s="4" t="n">
-        <v>-0.0541727739232698</v>
+        <v>-0.04170459846839236</v>
       </c>
       <c r="D14" s="4" t="n">
-        <v>-0.4439974659538777</v>
+        <v>-0.4311400649571624</v>
       </c>
       <c r="E14" s="4" t="n">
-        <v>-0.8385010872514513</v>
+        <v>-0.8255423455585174</v>
       </c>
       <c r="F14" s="4" t="n">
-        <v>1.723531896244829</v>
+        <v>1.736469023778277</v>
       </c>
       <c r="G14" s="4" t="n">
-        <v>-0.02943694337238867</v>
+        <v>-0.01636565223545006</v>
       </c>
       <c r="H14" s="4" t="n">
-        <v>3.917787151510346</v>
+        <v>3.93079747934182</v>
       </c>
       <c r="I14" s="4" t="n">
-        <v>0.1828738593781338</v>
+        <v>0.1959095001346398</v>
       </c>
       <c r="J14" s="4" t="n">
-        <v>3.369255364453565</v>
+        <v>3.382411163753531</v>
       </c>
       <c r="K14" s="4" t="n">
-        <v>0.8732947286165924</v>
+        <v>0.8864715765831761</v>
       </c>
       <c r="L14" s="4" t="n">
-        <v>-4.848314933172027</v>
+        <v>-4.83492939504211</v>
       </c>
       <c r="M14" s="4" t="n">
-        <v>-1.399034816070035</v>
+        <v>-1.385591376177409</v>
       </c>
       <c r="N14" s="4" t="n">
-        <v>-5.021464794151136</v>
+        <v>-5.008022384404072</v>
       </c>
       <c r="O14" s="4" t="n">
-        <v>-12.75803465644127</v>
+        <v>-12.74448425564632</v>
       </c>
       <c r="P14" s="4" t="n">
-        <v>-11.29260119791268</v>
+        <v>-11.30303083361083</v>
       </c>
     </row>
     <row r="15">
@@ -1043,46 +1043,46 @@
         <v>89</v>
       </c>
       <c r="C15" s="4" t="n">
-        <v>-5.282242776389765</v>
+        <v>-5.269783128003589</v>
       </c>
       <c r="D15" s="4" t="n">
-        <v>-10.24768529358822</v>
+        <v>-10.2348406258385</v>
       </c>
       <c r="E15" s="4" t="n">
-        <v>-11.76501906174308</v>
+        <v>-11.75207307985226</v>
       </c>
       <c r="F15" s="4" t="n">
-        <v>-14.99936634941976</v>
+        <v>-14.98644559270481</v>
       </c>
       <c r="G15" s="4" t="n">
-        <v>-13.29940041951131</v>
+        <v>-13.28634135304158</v>
       </c>
       <c r="H15" s="4" t="n">
-        <v>-13.00647027629591</v>
+        <v>-12.99347307026567</v>
       </c>
       <c r="I15" s="4" t="n">
-        <v>-17.58005144936519</v>
+        <v>-17.56702801068664</v>
       </c>
       <c r="J15" s="4" t="n">
-        <v>-12.44311943731012</v>
+        <v>-12.42997297141947</v>
       </c>
       <c r="K15" s="4" t="n">
-        <v>-11.38610310312493</v>
+        <v>-11.37293260228378</v>
       </c>
       <c r="L15" s="4" t="n">
-        <v>-11.11636240939758</v>
+        <v>-11.1029800906834</v>
       </c>
       <c r="M15" s="4" t="n">
-        <v>-14.69228881549038</v>
+        <v>-14.67884951445972</v>
       </c>
       <c r="N15" s="4" t="n">
-        <v>-15.785073266643</v>
+        <v>-15.77163324623845</v>
       </c>
       <c r="O15" s="4" t="n">
-        <v>-9.470236048053103</v>
+        <v>-9.456685703467365</v>
       </c>
       <c r="P15" s="4" t="n">
-        <v>-8.099945675851309</v>
+        <v>-8.110375311549717</v>
       </c>
     </row>
     <row r="16">
@@ -1095,46 +1095,46 @@
         <v>68</v>
       </c>
       <c r="C16" s="4" t="n">
-        <v>-11.27253365816102</v>
+        <v>-11.26008416604732</v>
       </c>
       <c r="D16" s="4" t="n">
-        <v>-15.81089729971379</v>
+        <v>-15.79806215382964</v>
       </c>
       <c r="E16" s="4" t="n">
-        <v>-20.60721919777272</v>
+        <v>-20.59428529105889</v>
       </c>
       <c r="F16" s="4" t="n">
-        <v>-14.6183800040167</v>
+        <v>-14.60546226347972</v>
       </c>
       <c r="G16" s="4" t="n">
-        <v>-7.826675538879194</v>
+        <v>-7.81361499803824</v>
       </c>
       <c r="H16" s="4" t="n">
-        <v>-13.40062872589232</v>
+        <v>-13.38763437812587</v>
       </c>
       <c r="I16" s="4" t="n">
-        <v>-9.08653682201944</v>
+        <v>-9.0735105932132</v>
       </c>
       <c r="J16" s="4" t="n">
-        <v>-11.02358020393359</v>
+        <v>-11.01043491591749</v>
       </c>
       <c r="K16" s="4" t="n">
-        <v>-9.619927092328119</v>
+        <v>-9.60675736771789</v>
       </c>
       <c r="L16" s="4" t="n">
-        <v>-17.81623689679281</v>
+        <v>-17.80285823287985</v>
       </c>
       <c r="M16" s="4" t="n">
-        <v>-13.61861304243509</v>
+        <v>-13.60517448124518</v>
       </c>
       <c r="N16" s="4" t="n">
-        <v>-16.52773802268732</v>
+        <v>-16.51429884450019</v>
       </c>
       <c r="O16" s="4" t="n">
-        <v>-14.01268708221721</v>
+        <v>-13.99913745430481</v>
       </c>
       <c r="P16" s="4" t="n">
-        <v>-13.76749359389552</v>
+        <v>-13.77792322959334</v>
       </c>
     </row>
     <row r="17">
@@ -1147,46 +1147,46 @@
         <v>60</v>
       </c>
       <c r="C17" s="4" t="n">
-        <v>-7.462363372620189</v>
+        <v>-7.449912654462182</v>
       </c>
       <c r="D17" s="4" t="n">
-        <v>-5.747359433318152</v>
+        <v>-5.734516717055975</v>
       </c>
       <c r="E17" s="4" t="n">
-        <v>-2.820998313941764</v>
+        <v>-2.808049973829796</v>
       </c>
       <c r="F17" s="4" t="n">
-        <v>-2.692164676898393</v>
+        <v>-2.679238825353657</v>
       </c>
       <c r="G17" s="4" t="n">
-        <v>-3.230556568299313</v>
+        <v>-3.217494420401621</v>
       </c>
       <c r="H17" s="4" t="n">
-        <v>-2.934637088924674</v>
+        <v>-2.921637274664839</v>
       </c>
       <c r="I17" s="4" t="n">
-        <v>0.3059972363779622</v>
+        <v>0.3190277531440771</v>
       </c>
       <c r="J17" s="4" t="n">
-        <v>3.166994103420286</v>
+        <v>3.1801456363875</v>
       </c>
       <c r="K17" s="4" t="n">
-        <v>1.442250584564377</v>
+        <v>1.455424123000448</v>
       </c>
       <c r="L17" s="4" t="n">
-        <v>10.58138811977051</v>
+        <v>10.59477602012106</v>
       </c>
       <c r="M17" s="4" t="n">
-        <v>5.384121336936417</v>
+        <v>5.397564303390617</v>
       </c>
       <c r="N17" s="4" t="n">
-        <v>5.420077190263093</v>
+        <v>5.433519805573297</v>
       </c>
       <c r="O17" s="4" t="n">
-        <v>5.001303933683189</v>
+        <v>5.014855021786481</v>
       </c>
       <c r="P17" s="4" t="n">
-        <v>5.252114249242446</v>
+        <v>5.241684613543917</v>
       </c>
     </row>
     <row r="18">
@@ -1199,46 +1199,46 @@
         <v>80</v>
       </c>
       <c r="C18" s="4" t="n">
-        <v>6.233391057447186</v>
+        <v>6.245855527331543</v>
       </c>
       <c r="D18" s="4" t="n">
-        <v>7.122140053296633</v>
+        <v>7.134994518894523</v>
       </c>
       <c r="E18" s="4" t="n">
-        <v>5.484337361631681</v>
+        <v>5.497291851983938</v>
       </c>
       <c r="F18" s="4" t="n">
-        <v>3.123478161282101</v>
+        <v>3.136407196698258</v>
       </c>
       <c r="G18" s="4" t="n">
-        <v>6.326387966596769</v>
+        <v>6.339456209417492</v>
       </c>
       <c r="H18" s="4" t="n">
-        <v>4.131448816801566</v>
+        <v>4.144452124037002</v>
       </c>
       <c r="I18" s="4" t="n">
-        <v>5.295148773724449</v>
+        <v>5.30818111142618</v>
       </c>
       <c r="J18" s="4" t="n">
-        <v>4.830377058706574</v>
+        <v>4.843528328983098</v>
       </c>
       <c r="K18" s="4" t="n">
-        <v>9.762552552754336</v>
+        <v>9.775729053563481</v>
       </c>
       <c r="L18" s="4" t="n">
-        <v>6.419412197379735</v>
+        <v>6.432797883022687</v>
       </c>
       <c r="M18" s="4" t="n">
-        <v>7.465323617318816</v>
+        <v>7.478766622837135</v>
       </c>
       <c r="N18" s="4" t="n">
-        <v>12.49887665532586</v>
+        <v>12.512320262709</v>
       </c>
       <c r="O18" s="4" t="n">
-        <v>10.83276845933791</v>
+        <v>10.84631991406259</v>
       </c>
       <c r="P18" s="4" t="n">
-        <v>9.835447582575114</v>
+        <v>9.825017946877246</v>
       </c>
     </row>
     <row r="19">
@@ -1251,46 +1251,46 @@
         <v>82</v>
       </c>
       <c r="C19" s="4" t="n">
-        <v>-6.124855922177822</v>
+        <v>-6.112410487522446</v>
       </c>
       <c r="D19" s="4" t="n">
-        <v>-5.300778026834891</v>
+        <v>-5.28794129498732</v>
       </c>
       <c r="E19" s="4" t="n">
-        <v>-2.050891187142561</v>
+        <v>-2.037947640249229</v>
       </c>
       <c r="F19" s="4" t="n">
-        <v>-0.7060690385165813</v>
+        <v>-0.6931464015507274</v>
       </c>
       <c r="G19" s="4" t="n">
-        <v>-4.892059223051881</v>
+        <v>-4.87900326386773</v>
       </c>
       <c r="H19" s="4" t="n">
-        <v>-5.812977347317364</v>
+        <v>-5.799984107023278</v>
       </c>
       <c r="I19" s="4" t="n">
-        <v>-13.20043391857822</v>
+        <v>-13.18741644569739</v>
       </c>
       <c r="J19" s="4" t="n">
-        <v>-12.45382586428682</v>
+        <v>-12.44068664644782</v>
       </c>
       <c r="K19" s="4" t="n">
-        <v>-14.95465705468308</v>
+        <v>-14.94149414649547</v>
       </c>
       <c r="L19" s="4" t="n">
-        <v>-12.15469610431614</v>
+        <v>-12.14131893140184</v>
       </c>
       <c r="M19" s="4" t="n">
-        <v>-8.708474813544882</v>
+        <v>-8.69503742283046</v>
       </c>
       <c r="N19" s="4" t="n">
-        <v>-8.676942364187163</v>
+        <v>-8.663503435557686</v>
       </c>
       <c r="O19" s="4" t="n">
-        <v>-7.880899342940999</v>
+        <v>-7.86734999847895</v>
       </c>
       <c r="P19" s="4" t="n">
-        <v>-6.414552417424325</v>
+        <v>-6.424982053122754</v>
       </c>
     </row>
     <row r="20">
@@ -1303,46 +1303,46 @@
         <v>92</v>
       </c>
       <c r="C20" s="4" t="n">
-        <v>7.26038137280257</v>
+        <v>7.27284079010446</v>
       </c>
       <c r="D20" s="4" t="n">
-        <v>5.659272591229708</v>
+        <v>5.672118976069697</v>
       </c>
       <c r="E20" s="4" t="n">
-        <v>8.515749234413711</v>
+        <v>8.528701580564352</v>
       </c>
       <c r="F20" s="4" t="n">
-        <v>6.481511114697653</v>
+        <v>6.494438232260016</v>
       </c>
       <c r="G20" s="4" t="n">
-        <v>0.527533767395397</v>
+        <v>0.540591585222181</v>
       </c>
       <c r="H20" s="4" t="n">
-        <v>-0.2593268327728993</v>
+        <v>-0.2463319304363409</v>
       </c>
       <c r="I20" s="4" t="n">
-        <v>-2.512833001742841</v>
+        <v>-2.499810782641838</v>
       </c>
       <c r="J20" s="4" t="n">
-        <v>-5.149744865276851</v>
+        <v>-5.136603762606761</v>
       </c>
       <c r="K20" s="4" t="n">
-        <v>-6.298375203777987</v>
+        <v>-6.285210112123188</v>
       </c>
       <c r="L20" s="4" t="n">
-        <v>-7.14975425239853</v>
+        <v>-7.136376816220604</v>
       </c>
       <c r="M20" s="4" t="n">
-        <v>-8.443111968320821</v>
+        <v>-8.429675802745159</v>
       </c>
       <c r="N20" s="4" t="n">
-        <v>-6.239177527112261</v>
+        <v>-6.225738949886328</v>
       </c>
       <c r="O20" s="4" t="n">
-        <v>-9.92141695532937</v>
+        <v>-9.907868272875362</v>
       </c>
       <c r="P20" s="4" t="n">
-        <v>-10.76237850438137</v>
+        <v>-10.77280814007928</v>
       </c>
     </row>
     <row r="21">
@@ -1352,49 +1352,49 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="C21" s="4" t="n">
-        <v>-0.8623522720673478</v>
+        <v>-0.8415603566054202</v>
       </c>
       <c r="D21" s="4" t="n">
-        <v>1.452067898375653</v>
+        <v>1.461069879139743</v>
       </c>
       <c r="E21" s="4" t="n">
-        <v>2.368261387097327</v>
+        <v>2.36915019385544</v>
       </c>
       <c r="F21" s="4" t="n">
-        <v>9.057596159827732</v>
+        <v>9.013233691604427</v>
       </c>
       <c r="G21" s="4" t="n">
-        <v>8.519748535437607</v>
+        <v>8.479721127472516</v>
       </c>
       <c r="H21" s="4" t="n">
-        <v>8.819926796082733</v>
+        <v>8.779717700334707</v>
       </c>
       <c r="I21" s="4" t="n">
-        <v>12.01908961645837</v>
+        <v>11.95848067539684</v>
       </c>
       <c r="J21" s="4" t="n">
-        <v>11.55250544651809</v>
+        <v>11.49644773630212</v>
       </c>
       <c r="K21" s="4" t="n">
-        <v>10.83894476097368</v>
+        <v>10.78616761603715</v>
       </c>
       <c r="L21" s="4" t="n">
-        <v>8.015493301738729</v>
+        <v>7.982761312652059</v>
       </c>
       <c r="M21" s="4" t="n">
-        <v>10.44270730021113</v>
+        <v>10.39205288636312</v>
       </c>
       <c r="N21" s="4" t="n">
-        <v>8.506389440327069</v>
+        <v>8.470334880063668</v>
       </c>
       <c r="O21" s="4" t="n">
-        <v>8.083297969296105</v>
+        <v>8.052955387384841</v>
       </c>
       <c r="P21" s="4" t="n">
-        <v>10.03281600362803</v>
+        <v>10.2416846135439</v>
       </c>
     </row>
     <row r="22">
@@ -1407,46 +1407,46 @@
         <v>132</v>
       </c>
       <c r="C22" s="4" t="n">
-        <v>2.315781791075885</v>
+        <v>1.929285082479851</v>
       </c>
       <c r="D22" s="4" t="n">
-        <v>2.143309362727393</v>
+        <v>2.156425422057701</v>
       </c>
       <c r="E22" s="4" t="n">
-        <v>-4.640836598908791</v>
+        <v>-5.043091607727149</v>
       </c>
       <c r="F22" s="4" t="n">
-        <v>-3.745967269406762</v>
+        <v>-3.730988248195423</v>
       </c>
       <c r="G22" s="4" t="n">
-        <v>-4.640652472628595</v>
+        <v>-5.045212901240028</v>
       </c>
       <c r="H22" s="4" t="n">
-        <v>-3.924788051896542</v>
+        <v>-4.329444091733606</v>
       </c>
       <c r="I22" s="4" t="n">
-        <v>-3.256884227568456</v>
+        <v>-3.242103678352002</v>
       </c>
       <c r="J22" s="4" t="n">
-        <v>-3.735058535705079</v>
+        <v>-3.719901303831492</v>
       </c>
       <c r="K22" s="4" t="n">
-        <v>-2.281500372227306</v>
+        <v>-2.266925713836557</v>
       </c>
       <c r="L22" s="4" t="n">
-        <v>-5.420319104017722</v>
+        <v>-5.404305055908935</v>
       </c>
       <c r="M22" s="4" t="n">
-        <v>-7.14074356844975</v>
+        <v>-7.124160955474906</v>
       </c>
       <c r="N22" s="4" t="n">
-        <v>-5.919607135512045</v>
+        <v>-6.339017583920835</v>
       </c>
       <c r="O22" s="4" t="n">
-        <v>-5.906697992125302</v>
+        <v>-6.332625414454206</v>
       </c>
       <c r="P22" s="4" t="n">
-        <v>-5.656976659848844</v>
+        <v>-5.667406295546996</v>
       </c>
     </row>
     <row r="23">
@@ -1459,46 +1459,46 @@
         <v>171</v>
       </c>
       <c r="C23" s="4" t="n">
-        <v>-2.263922007208798</v>
+        <v>-2.251399717533175</v>
       </c>
       <c r="D23" s="4" t="n">
-        <v>5.160509413010494</v>
+        <v>4.853130490887942</v>
       </c>
       <c r="E23" s="4" t="n">
-        <v>7.680263396208503</v>
+        <v>7.693270527626105</v>
       </c>
       <c r="F23" s="4" t="n">
-        <v>6.96952360737334</v>
+        <v>6.662405528202129</v>
       </c>
       <c r="G23" s="4" t="n">
-        <v>5.839718710644512</v>
+        <v>5.852829515019451</v>
       </c>
       <c r="H23" s="4" t="n">
-        <v>8.474000333652114</v>
+        <v>8.48704322994648</v>
       </c>
       <c r="I23" s="4" t="n">
-        <v>5.792338479323902</v>
+        <v>5.480613713100837</v>
       </c>
       <c r="J23" s="4" t="n">
-        <v>6.492112630080662</v>
+        <v>6.503331212181678</v>
       </c>
       <c r="K23" s="4" t="n">
-        <v>4.680747419440856</v>
+        <v>4.692579264839345</v>
       </c>
       <c r="L23" s="4" t="n">
-        <v>6.748920505947808</v>
+        <v>6.760309847993476</v>
       </c>
       <c r="M23" s="4" t="n">
-        <v>6.879492440740549</v>
+        <v>6.558050555720705</v>
       </c>
       <c r="N23" s="4" t="n">
-        <v>3.989898989898983</v>
+        <v>4.003351278619093</v>
       </c>
       <c r="O23" s="4" t="n">
-        <v>7.078416308778777</v>
+        <v>7.09197235513038</v>
       </c>
       <c r="P23" s="4" t="n">
-        <v>7.328137641055065</v>
+        <v>7.317708005356913</v>
       </c>
     </row>
     <row r="24">
@@ -1511,46 +1511,46 @@
         <v>167</v>
       </c>
       <c r="C24" s="4" t="n">
-        <v>-1.349530483709074</v>
+        <v>-1.337008194033452</v>
       </c>
       <c r="D24" s="4" t="n">
-        <v>-4.786800529893704</v>
+        <v>-4.773890720317652</v>
       </c>
       <c r="E24" s="4" t="n">
-        <v>-2.191144075632032</v>
+        <v>-2.17813694421443</v>
       </c>
       <c r="F24" s="4" t="n">
-        <v>-2.053917312645659</v>
+        <v>-2.040938170247195</v>
       </c>
       <c r="G24" s="4" t="n">
-        <v>0.3877261875720706</v>
+        <v>0.4008369919470098</v>
       </c>
       <c r="H24" s="4" t="n">
-        <v>-2.30535703557053</v>
+        <v>-2.292314139276165</v>
       </c>
       <c r="I24" s="4" t="n">
-        <v>-3.593274447565065</v>
+        <v>-3.580208193264589</v>
       </c>
       <c r="J24" s="4" t="n">
-        <v>2.250649752121205</v>
+        <v>1.928891943400068</v>
       </c>
       <c r="K24" s="4" t="n">
-        <v>3.723384261948702</v>
+        <v>3.402313752268689</v>
       </c>
       <c r="L24" s="4" t="n">
-        <v>4.405392944383955</v>
+        <v>4.077755216023739</v>
       </c>
       <c r="M24" s="4" t="n">
-        <v>3.601837224856801</v>
+        <v>3.615294518567019</v>
       </c>
       <c r="N24" s="4" t="n">
-        <v>3.63622038220209</v>
+        <v>3.6496726709222</v>
       </c>
       <c r="O24" s="4" t="n">
-        <v>0.8207561904187344</v>
+        <v>0.8343122367703373</v>
       </c>
       <c r="P24" s="4" t="n">
-        <v>-1.324732058143297</v>
+        <v>-1.335161693841449</v>
       </c>
     </row>
     <row r="25">
@@ -1563,46 +1563,46 @@
         <v>153</v>
       </c>
       <c r="C25" s="4" t="n">
-        <v>-5.434614790798214</v>
+        <v>-5.422092501122592</v>
       </c>
       <c r="D25" s="4" t="n">
-        <v>-3.778214547553461</v>
+        <v>-3.765304737977409</v>
       </c>
       <c r="E25" s="4" t="n">
-        <v>-6.133867567875548</v>
+        <v>-6.120860436457946</v>
       </c>
       <c r="F25" s="4" t="n">
-        <v>-7.96439874899324</v>
+        <v>-7.951419606594776</v>
       </c>
       <c r="G25" s="4" t="n">
-        <v>-6.542035650340218</v>
+        <v>-6.528924845965278</v>
       </c>
       <c r="H25" s="4" t="n">
-        <v>-8.858972797591726</v>
+        <v>-8.84592990129736</v>
       </c>
       <c r="I25" s="4" t="n">
-        <v>-9.597301286105981</v>
+        <v>-9.584235031805505</v>
       </c>
       <c r="J25" s="4" t="n">
-        <v>-8.10370037116185</v>
+        <v>-8.090519361866612</v>
       </c>
       <c r="K25" s="4" t="n">
-        <v>-8.81829502858583</v>
+        <v>-8.805096289631066</v>
       </c>
       <c r="L25" s="4" t="n">
-        <v>-8.361230671130095</v>
+        <v>-8.347825543477263</v>
       </c>
       <c r="M25" s="4" t="n">
-        <v>-8.565983995447823</v>
+        <v>-8.552526701737605</v>
       </c>
       <c r="N25" s="4" t="n">
-        <v>-8.531600838102243</v>
+        <v>-8.518148549382133</v>
       </c>
       <c r="O25" s="4" t="n">
-        <v>-6.991071135321654</v>
+        <v>-6.977515088970051</v>
       </c>
       <c r="P25" s="4" t="n">
-        <v>-8.702134116771006</v>
+        <v>-8.712563752469158</v>
       </c>
     </row>
     <row r="26">
@@ -1615,46 +1615,46 @@
         <v>166</v>
       </c>
       <c r="C26" s="4" t="n">
-        <v>1.723429149669542</v>
+        <v>1.735951439345165</v>
       </c>
       <c r="D26" s="4" t="n">
-        <v>-2.900192656065528</v>
+        <v>-2.887282846489477</v>
       </c>
       <c r="E26" s="4" t="n">
-        <v>-2.692651724108039</v>
+        <v>-2.679644592690437</v>
       </c>
       <c r="F26" s="4" t="n">
-        <v>1.654468878378708</v>
+        <v>1.667448020777172</v>
       </c>
       <c r="G26" s="4" t="n">
-        <v>3.52568621752355</v>
+        <v>3.538797021898489</v>
       </c>
       <c r="H26" s="4" t="n">
-        <v>4.425537793793424</v>
+        <v>4.43858069008779</v>
       </c>
       <c r="I26" s="4" t="n">
-        <v>4.34080407652128</v>
+        <v>4.353870330821756</v>
       </c>
       <c r="J26" s="4" t="n">
-        <v>0.2591628464142062</v>
+        <v>0.272343855709444</v>
       </c>
       <c r="K26" s="4" t="n">
-        <v>-2.813885232539313</v>
+        <v>-2.80068649358455</v>
       </c>
       <c r="L26" s="4" t="n">
-        <v>-3.664010417566978</v>
+        <v>-3.650605289914147</v>
       </c>
       <c r="M26" s="4" t="n">
-        <v>-3.266354103330329</v>
+        <v>-3.252896809620111</v>
       </c>
       <c r="N26" s="4" t="n">
-        <v>-2.027151668876606</v>
+        <v>-2.013699380156496</v>
       </c>
       <c r="O26" s="4" t="n">
-        <v>-4.857044834038106</v>
+        <v>-4.843488787686503</v>
       </c>
       <c r="P26" s="4" t="n">
-        <v>-3.402504224653654</v>
+        <v>-3.412933860351806</v>
       </c>
     </row>
     <row r="27">
@@ -1664,101 +1664,101 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="C27" s="4" t="n">
-        <v>-7.151823413377535</v>
+        <v>-6.80190368485534</v>
       </c>
       <c r="D27" s="4" t="n">
-        <v>0.5533731599934697</v>
+        <v>0.846169481339949</v>
       </c>
       <c r="E27" s="4" t="n">
-        <v>0.7796224658193793</v>
+        <v>1.068682047202195</v>
       </c>
       <c r="F27" s="4" t="n">
-        <v>-2.816832476107422</v>
+        <v>-2.504796512912868</v>
       </c>
       <c r="G27" s="4" t="n">
-        <v>-0.2496636290676548</v>
+        <v>0.04333368707786178</v>
       </c>
       <c r="H27" s="4" t="n">
-        <v>0.6688963210702354</v>
+        <v>0.9579916673300914</v>
       </c>
       <c r="I27" s="4" t="n">
-        <v>-3.763663483158574</v>
+        <v>-3.447706346257206</v>
       </c>
       <c r="J27" s="4" t="n">
-        <v>-4.85196489436229</v>
+        <v>-4.532058940660953</v>
       </c>
       <c r="K27" s="4" t="n">
-        <v>-4.912964780544591</v>
+        <v>-5.210325047800872</v>
       </c>
       <c r="L27" s="4" t="n">
-        <v>-5.141971953150438</v>
+        <v>-5.442959893513724</v>
       </c>
       <c r="M27" s="4" t="n">
-        <v>-6.588961302312597</v>
+        <v>-6.264945002391201</v>
       </c>
       <c r="N27" s="4" t="n">
-        <v>-8.417932182234246</v>
+        <v>-8.69970265250501</v>
       </c>
       <c r="O27" s="4" t="n">
-        <v>-6.97483275591221</v>
+        <v>-7.268001653966714</v>
       </c>
       <c r="P27" s="4" t="n">
-        <v>-6.103993411213281</v>
+        <v>-6.424982053122754</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>X ≈ -0.1217</t>
+          <t>X ≈ -0.1216</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="C28" s="4" t="n">
-        <v>3.188379861608077</v>
+        <v>2.947655398037078</v>
       </c>
       <c r="D28" s="4" t="n">
-        <v>-1.832284660447151</v>
+        <v>-2.092102123598245</v>
       </c>
       <c r="E28" s="4" t="n">
-        <v>-2.227153367043677</v>
+        <v>-2.486873508353085</v>
       </c>
       <c r="F28" s="4" t="n">
-        <v>-0.3923547798905247</v>
+        <v>-0.6423626504792068</v>
       </c>
       <c r="G28" s="4" t="n">
-        <v>0.773769459582752</v>
+        <v>0.533633510710942</v>
       </c>
       <c r="H28" s="4" t="n">
-        <v>1.639393215480233</v>
+        <v>1.402436111774598</v>
       </c>
       <c r="I28" s="4" t="n">
-        <v>-1.854431410883016</v>
+        <v>-2.110845676062929</v>
       </c>
       <c r="J28" s="4" t="n">
-        <v>-1.185251173300884</v>
+        <v>-1.435057176992657</v>
       </c>
       <c r="K28" s="4" t="n">
-        <v>-0.6780692413013725</v>
+        <v>-0.3531821906584227</v>
       </c>
       <c r="L28" s="4" t="n">
-        <v>-0.9600126081476077</v>
+        <v>-0.6316724155598337</v>
       </c>
       <c r="M28" s="4" t="n">
-        <v>2.812506794807675</v>
+        <v>2.592197854751653</v>
       </c>
       <c r="N28" s="4" t="n">
-        <v>1.710526315789473</v>
+        <v>2.055147435678407</v>
       </c>
       <c r="O28" s="4" t="n">
-        <v>1.858453523026512</v>
+        <v>2.206425153793703</v>
       </c>
       <c r="P28" s="4" t="n">
-        <v>4.949083946211765</v>
+        <v>5.289303661163089</v>
       </c>
     </row>
     <row r="29">
@@ -1771,46 +1771,46 @@
         <v>239</v>
       </c>
       <c r="C29" s="4" t="n">
-        <v>3.991917328325584</v>
+        <v>4.004439618001207</v>
       </c>
       <c r="D29" s="4" t="n">
-        <v>4.05398388272544</v>
+        <v>4.066893692301491</v>
       </c>
       <c r="E29" s="4" t="n">
-        <v>2.822295092446751</v>
+        <v>2.835302223864353</v>
       </c>
       <c r="F29" s="4" t="n">
-        <v>-3.323602402560859</v>
+        <v>-3.310623260162394</v>
       </c>
       <c r="G29" s="4" t="n">
-        <v>-1.769973408428008</v>
+        <v>-1.756862604053069</v>
       </c>
       <c r="H29" s="4" t="n">
-        <v>0.2011086966517226</v>
+        <v>0.214151592946088</v>
       </c>
       <c r="I29" s="4" t="n">
-        <v>3.045245272266463</v>
+        <v>3.058311526566939</v>
       </c>
       <c r="J29" s="4" t="n">
-        <v>3.833291999007983</v>
+        <v>3.846473008303221</v>
       </c>
       <c r="K29" s="4" t="n">
-        <v>5.027522238348695</v>
+        <v>5.040720977303458</v>
       </c>
       <c r="L29" s="4" t="n">
-        <v>5.851037220684873</v>
+        <v>5.864442348337704</v>
       </c>
       <c r="M29" s="4" t="n">
-        <v>6.483103980049208</v>
+        <v>6.496561273759426</v>
       </c>
       <c r="N29" s="4" t="n">
-        <v>6.517487137394596</v>
+        <v>6.530939426114706</v>
       </c>
       <c r="O29" s="4" t="n">
-        <v>7.770872693813651</v>
+        <v>7.784428740165254</v>
       </c>
       <c r="P29" s="4" t="n">
-        <v>7.602183984249038</v>
+        <v>7.591754348550886</v>
       </c>
     </row>
     <row r="30">
@@ -1823,46 +1823,46 @@
         <v>225</v>
       </c>
       <c r="C30" s="4" t="n">
-        <v>-8.493438320209926</v>
+        <v>-8.480916030534303</v>
       </c>
       <c r="D30" s="4" t="n">
-        <v>-5.216123044285396</v>
+        <v>-5.203213234709345</v>
       </c>
       <c r="E30" s="4" t="n">
-        <v>-3.833213973104151</v>
+        <v>-3.820206841686549</v>
       </c>
       <c r="F30" s="4" t="n">
-        <v>-5.036294173829987</v>
+        <v>-5.023315031431522</v>
       </c>
       <c r="G30" s="4" t="n">
-        <v>-1.130270944457713</v>
+        <v>-1.117160140082774</v>
       </c>
       <c r="H30" s="4" t="n">
-        <v>-3.499495673408767</v>
+        <v>-3.486452777114401</v>
       </c>
       <c r="I30" s="4" t="n">
-        <v>-2.25089605734766</v>
+        <v>-2.237829803047184</v>
       </c>
       <c r="J30" s="4" t="n">
-        <v>-2.718079456129161</v>
+        <v>-2.704898446833923</v>
       </c>
       <c r="K30" s="4" t="n">
-        <v>-4.112412675644805</v>
+        <v>-4.099213936690042</v>
       </c>
       <c r="L30" s="4" t="n">
-        <v>-3.62920452733939</v>
+        <v>-3.615799399686559</v>
       </c>
       <c r="M30" s="4" t="n">
-        <v>-5.167291184990312</v>
+        <v>-5.153833891280094</v>
       </c>
       <c r="N30" s="4" t="n">
-        <v>-2.910685805422602</v>
+        <v>-2.897233516702492</v>
       </c>
       <c r="O30" s="4" t="n">
-        <v>-1.997607083034268</v>
+        <v>-1.984051036682665</v>
       </c>
       <c r="P30" s="4" t="n">
-        <v>-2.636774639646823</v>
+        <v>-2.647204275344976</v>
       </c>
     </row>
     <row r="31">
@@ -1875,46 +1875,46 @@
         <v>221</v>
       </c>
       <c r="C31" s="4" t="n">
-        <v>-0.9097279129702045</v>
+        <v>-0.8972056232945818</v>
       </c>
       <c r="D31" s="4" t="n">
-        <v>-1.163835462585993</v>
+        <v>-1.150925653009942</v>
       </c>
       <c r="E31" s="4" t="n">
-        <v>-2.463681544748248</v>
+        <v>-2.450674413330646</v>
       </c>
       <c r="F31" s="4" t="n">
-        <v>2.191458465687354</v>
+        <v>2.204437608085819</v>
       </c>
       <c r="G31" s="4" t="n">
-        <v>-2.87184962721286</v>
+        <v>-2.858738822837921</v>
       </c>
       <c r="H31" s="4" t="n">
-        <v>-3.931873752845569</v>
+        <v>-3.918830856551203</v>
       </c>
       <c r="I31" s="4" t="n">
-        <v>-4.016607470117904</v>
+        <v>-4.003541215817428</v>
       </c>
       <c r="J31" s="4" t="n">
-        <v>-4.936279556682209</v>
+        <v>-4.923098547386971</v>
       </c>
       <c r="K31" s="4" t="n">
-        <v>-6.807234193995782</v>
+        <v>-6.794035455041019</v>
       </c>
       <c r="L31" s="4" t="n">
-        <v>-4.489938564544012</v>
+        <v>-4.476533436891181</v>
       </c>
       <c r="M31" s="4" t="n">
-        <v>-6.504646639992821</v>
+        <v>-6.491189346282603</v>
       </c>
       <c r="N31" s="4" t="n">
-        <v>-7.375240858213004</v>
+        <v>-7.361788569492894</v>
       </c>
       <c r="O31" s="4" t="n">
-        <v>-6.890518093592242</v>
+        <v>-6.876962047240639</v>
       </c>
       <c r="P31" s="4" t="n">
-        <v>-7.998262824664423</v>
+        <v>-8.008692460362575</v>
       </c>
     </row>
     <row r="32">
@@ -1927,46 +1927,46 @@
         <v>232</v>
       </c>
       <c r="C32" s="4" t="n">
-        <v>2.67897547289347</v>
+        <v>2.691497762569092</v>
       </c>
       <c r="D32" s="4" t="n">
-        <v>1.929470825446451</v>
+        <v>1.942380635022502</v>
       </c>
       <c r="E32" s="4" t="n">
-        <v>-0.1895358121845661</v>
+        <v>-0.1765286807669639</v>
       </c>
       <c r="F32" s="4" t="n">
-        <v>-3.938593024404703</v>
+        <v>-3.925613882006239</v>
       </c>
       <c r="G32" s="4" t="n">
-        <v>-4.908048722235492</v>
+        <v>-4.894937917860553</v>
       </c>
       <c r="H32" s="4" t="n">
-        <v>-4.610606784519902</v>
+        <v>-4.597563888225537</v>
       </c>
       <c r="I32" s="4" t="n">
-        <v>-3.833271536274871</v>
+        <v>-3.820205281974395</v>
       </c>
       <c r="J32" s="4" t="n">
-        <v>-0.8521790729874041</v>
+        <v>-0.8389980636921663</v>
       </c>
       <c r="K32" s="4" t="n">
-        <v>-0.4821444764110367</v>
+        <v>-0.4689457374562735</v>
       </c>
       <c r="L32" s="4" t="n">
-        <v>-1.332269661439014</v>
+        <v>-1.318864533786183</v>
       </c>
       <c r="M32" s="4" t="n">
-        <v>-0.2439195374807355</v>
+        <v>-0.2304622437705177</v>
       </c>
       <c r="N32" s="4" t="n">
-        <v>-2.364708793928394</v>
+        <v>-2.351256505208283</v>
       </c>
       <c r="O32" s="4" t="n">
-        <v>-1.922894439356014</v>
+        <v>-1.909338393004411</v>
       </c>
       <c r="P32" s="4" t="n">
-        <v>-4.259380003631499</v>
+        <v>-4.269809639329651</v>
       </c>
     </row>
     <row r="33">
@@ -1979,46 +1979,46 @@
         <v>225</v>
       </c>
       <c r="C33" s="4" t="n">
-        <v>7.951006124234468</v>
+        <v>7.96352841391009</v>
       </c>
       <c r="D33" s="4" t="n">
-        <v>6.339432511270211</v>
+        <v>6.352342320846262</v>
       </c>
       <c r="E33" s="4" t="n">
-        <v>3.277897138006985</v>
+        <v>3.290904269424587</v>
       </c>
       <c r="F33" s="4" t="n">
-        <v>6.51926138172557</v>
+        <v>6.532240524124035</v>
       </c>
       <c r="G33" s="4" t="n">
-        <v>3.758617944431194</v>
+        <v>3.771728748806133</v>
       </c>
       <c r="H33" s="4" t="n">
-        <v>5.38939321548019</v>
+        <v>5.402436111774556</v>
       </c>
       <c r="I33" s="4" t="n">
-        <v>10.19354838709678</v>
+        <v>10.20661464139725</v>
       </c>
       <c r="J33" s="4" t="n">
-        <v>9.281920543870832</v>
+        <v>9.29510155316607</v>
       </c>
       <c r="K33" s="4" t="n">
-        <v>6.998698435466309</v>
+        <v>7.011897174421073</v>
       </c>
       <c r="L33" s="4" t="n">
-        <v>7.037462139327268</v>
+        <v>7.050867266980099</v>
       </c>
       <c r="M33" s="4" t="n">
-        <v>6.832708815009688</v>
+        <v>6.846166108719906</v>
       </c>
       <c r="N33" s="4" t="n">
-        <v>6.867091972355119</v>
+        <v>6.880544261075229</v>
       </c>
       <c r="O33" s="4" t="n">
-        <v>6.891281805854589</v>
+        <v>6.904837852206192</v>
       </c>
       <c r="P33" s="4" t="n">
-        <v>8.474336471464255</v>
+        <v>8.463906835766103</v>
       </c>
     </row>
     <row r="34">
@@ -2093,7 +2093,7 @@
     <row r="3" ht="22" customHeight="1">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>Measures the winrate at horizon h days, given that Drawdown-120 is above threshold x, minus the unconditional baseline winrate.</t>
+          <t>Measures the winrate at horizon h, given that Drawdown-120 is above threshold x, minus the unconditional baseline winrate.</t>
         </is>
       </c>
     </row>
@@ -2186,49 +2186,49 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>3977</v>
+        <v>3978</v>
       </c>
       <c r="C6" s="4" t="n">
-        <v>0.01282734395042695</v>
+        <v>0.01219346583247471</v>
       </c>
       <c r="D6" s="4" t="n">
-        <v>0.01882862837000943</v>
+        <v>0.01817356562487049</v>
       </c>
       <c r="E6" s="4" t="n">
-        <v>-0.06156569493632702</v>
+        <v>-0.0622056718027082</v>
       </c>
       <c r="F6" s="4" t="n">
-        <v>0.007096846987671768</v>
+        <v>0.006440903038551937</v>
       </c>
       <c r="G6" s="4" t="n">
-        <v>-0.1162775230382991</v>
+        <v>-0.1169093249335447</v>
       </c>
       <c r="H6" s="4" t="n">
-        <v>-0.0811212136289825</v>
+        <v>-0.08175856961031513</v>
       </c>
       <c r="I6" s="4" t="n">
-        <v>-0.07686660620977648</v>
+        <v>-0.07750636794332166</v>
       </c>
       <c r="J6" s="4" t="n">
-        <v>-0.203949961331837</v>
+        <v>-0.2045637748125131</v>
       </c>
       <c r="K6" s="4" t="n">
-        <v>-0.07535703637921642</v>
+        <v>-0.07600418413054655</v>
       </c>
       <c r="L6" s="4" t="n">
-        <v>-0.2082885095884137</v>
+        <v>-0.2089128546784664</v>
       </c>
       <c r="M6" s="4" t="n">
-        <v>-0.1980002860511618</v>
+        <v>-0.1986300061590995</v>
       </c>
       <c r="N6" s="4" t="n">
-        <v>-0.07412720610958701</v>
+        <v>-0.07478795556351514</v>
       </c>
       <c r="O6" s="4" t="n">
-        <v>-0.05291125598545676</v>
+        <v>-0.05358274481699254</v>
       </c>
       <c r="P6" s="4" t="n">
-        <v>-0.065545628387639</v>
+        <v>-0.06500216373110135</v>
       </c>
     </row>
     <row r="7">
@@ -2238,49 +2238,49 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>3955</v>
+        <v>3956</v>
       </c>
       <c r="C7" s="4" t="n">
-        <v>0.02672297011260127</v>
+        <v>0.02601266687053538</v>
       </c>
       <c r="D7" s="4" t="n">
-        <v>0.06690639301683632</v>
+        <v>0.06616400543408218</v>
       </c>
       <c r="E7" s="4" t="n">
-        <v>0.06391159421808368</v>
+        <v>0.06316430359535019</v>
       </c>
       <c r="F7" s="4" t="n">
-        <v>0.05660200103339719</v>
+        <v>0.05585793881557066</v>
       </c>
       <c r="G7" s="4" t="n">
-        <v>-0.0392293478661685</v>
+        <v>-0.03995683337127076</v>
       </c>
       <c r="H7" s="4" t="n">
-        <v>-0.03074304492861302</v>
+        <v>-0.03146903454231875</v>
       </c>
       <c r="I7" s="4" t="n">
-        <v>-0.0259815921505151</v>
+        <v>-0.02671028079973325</v>
       </c>
       <c r="J7" s="4" t="n">
-        <v>-0.1511631330906482</v>
+        <v>-0.1518668690673692</v>
       </c>
       <c r="K7" s="4" t="n">
-        <v>-0.04675610998823032</v>
+        <v>-0.04748738054539814</v>
       </c>
       <c r="L7" s="4" t="n">
-        <v>-0.2262127505158418</v>
+        <v>-0.2269105107976728</v>
       </c>
       <c r="M7" s="4" t="n">
-        <v>-0.2147337766471509</v>
+        <v>-0.2154375510145883</v>
       </c>
       <c r="N7" s="4" t="n">
-        <v>-0.09036738237489317</v>
+        <v>-0.09110247408843009</v>
       </c>
       <c r="O7" s="4" t="n">
-        <v>-0.09197850197590896</v>
+        <v>-0.09271921964951702</v>
       </c>
       <c r="P7" s="4" t="n">
-        <v>-0.1060821266534262</v>
+        <v>-0.1054673918487339</v>
       </c>
     </row>
     <row r="8">
@@ -2290,49 +2290,49 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>3935</v>
+        <v>3936</v>
       </c>
       <c r="C8" s="4" t="n">
-        <v>0.09014830592984424</v>
+        <v>0.08935492413771584</v>
       </c>
       <c r="D8" s="4" t="n">
-        <v>0.08804608557418447</v>
+        <v>0.08722918339270791</v>
       </c>
       <c r="E8" s="4" t="n">
-        <v>0.03635858982877238</v>
+        <v>0.03554858437543373</v>
       </c>
       <c r="F8" s="4" t="n">
-        <v>0.07904169435759201</v>
+        <v>0.07822239043026968</v>
       </c>
       <c r="G8" s="4" t="n">
-        <v>-0.06524953359451047</v>
+        <v>-0.06604057945751407</v>
       </c>
       <c r="H8" s="4" t="n">
-        <v>-0.05823549362456504</v>
+        <v>-0.0590243344729231</v>
       </c>
       <c r="I8" s="4" t="n">
-        <v>-0.05302695536897062</v>
+        <v>-0.05381875674854797</v>
       </c>
       <c r="J8" s="4" t="n">
-        <v>-0.1511054788532391</v>
+        <v>-0.1518796746370796</v>
       </c>
       <c r="K8" s="4" t="n">
-        <v>-0.09662023345642012</v>
+        <v>-0.09740954412187364</v>
       </c>
       <c r="L8" s="4" t="n">
-        <v>-0.2726842599280346</v>
+        <v>-0.273441813674161</v>
       </c>
       <c r="M8" s="4" t="n">
-        <v>-0.285512504328949</v>
+        <v>-0.2862702118352161</v>
       </c>
       <c r="N8" s="4" t="n">
-        <v>-0.1353069213315479</v>
+        <v>-0.1361026550130262</v>
       </c>
       <c r="O8" s="4" t="n">
-        <v>-0.08398919685536299</v>
+        <v>-0.08480457152302279</v>
       </c>
       <c r="P8" s="4" t="n">
-        <v>-0.124844666471617</v>
+        <v>-0.1241690449926764</v>
       </c>
     </row>
     <row r="9">
@@ -2342,49 +2342,49 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>3896</v>
+        <v>3897</v>
       </c>
       <c r="C9" s="4" t="n">
-        <v>0.0008057319772802884</v>
+        <v>-9.76162121020252e-05</v>
       </c>
       <c r="D9" s="4" t="n">
-        <v>0.09150802588411011</v>
+        <v>0.09055328699275833</v>
       </c>
       <c r="E9" s="4" t="n">
-        <v>-0.0847283490106534</v>
+        <v>-0.08564525860910521</v>
       </c>
       <c r="F9" s="4" t="n">
-        <v>0.008252677168471223</v>
+        <v>0.007313754508246006</v>
       </c>
       <c r="G9" s="4" t="n">
-        <v>-0.2089450090472695</v>
+        <v>-0.2098380714703794</v>
       </c>
       <c r="H9" s="4" t="n">
-        <v>-0.2304838337001556</v>
+        <v>-0.2313667051268666</v>
       </c>
       <c r="I9" s="4" t="n">
-        <v>-0.224420696514116</v>
+        <v>-0.2253070343768826</v>
       </c>
       <c r="J9" s="4" t="n">
-        <v>-0.2932261045715663</v>
+        <v>-0.2941033319650188</v>
       </c>
       <c r="K9" s="4" t="n">
-        <v>-0.2888916411522189</v>
+        <v>-0.2897714855253923</v>
       </c>
       <c r="L9" s="4" t="n">
-        <v>-0.5095464076812704</v>
+        <v>-0.5103848336208827</v>
       </c>
       <c r="M9" s="4" t="n">
-        <v>-0.5205156585020347</v>
+        <v>-0.5213552588014636</v>
       </c>
       <c r="N9" s="4" t="n">
-        <v>-0.3435573634866174</v>
+        <v>-0.3444422026904093</v>
       </c>
       <c r="O9" s="4" t="n">
-        <v>-0.338895253421704</v>
+        <v>-0.3397890219742266</v>
       </c>
       <c r="P9" s="4" t="n">
-        <v>-0.3827249020241936</v>
+        <v>-0.3818719684422263</v>
       </c>
     </row>
     <row r="10">
@@ -2394,49 +2394,49 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>3840</v>
+        <v>3841</v>
       </c>
       <c r="C10" s="4" t="n">
-        <v>-0.1186654159795069</v>
+        <v>-0.1197328442343988</v>
       </c>
       <c r="D10" s="4" t="n">
-        <v>0.07463500348204377</v>
+        <v>0.07348313464215295</v>
       </c>
       <c r="E10" s="4" t="n">
-        <v>-0.2022955969248059</v>
+        <v>-0.2033844117800072</v>
       </c>
       <c r="F10" s="4" t="n">
-        <v>-0.1618352993711198</v>
+        <v>-0.1629324468214719</v>
       </c>
       <c r="G10" s="4" t="n">
-        <v>-0.2964612969302181</v>
+        <v>-0.2975353204579534</v>
       </c>
       <c r="H10" s="4" t="n">
-        <v>-0.1927273666404119</v>
+        <v>-0.1938226567367636</v>
       </c>
       <c r="I10" s="4" t="n">
-        <v>-0.3153041097983547</v>
+        <v>-0.3163698815872706</v>
       </c>
       <c r="J10" s="4" t="n">
-        <v>-0.2743283727524926</v>
+        <v>-0.2754151553802728</v>
       </c>
       <c r="K10" s="4" t="n">
-        <v>-0.2690374408521379</v>
+        <v>-0.2701274398968323</v>
       </c>
       <c r="L10" s="4" t="n">
-        <v>-0.5325459540939335</v>
+        <v>-0.5335858467317891</v>
       </c>
       <c r="M10" s="4" t="n">
-        <v>-0.5927400530621298</v>
+        <v>-0.5937691439104498</v>
       </c>
       <c r="N10" s="4" t="n">
-        <v>-0.3616661975795168</v>
+        <v>-0.3627552445193487</v>
       </c>
       <c r="O10" s="4" t="n">
-        <v>-0.3508137132520517</v>
+        <v>-0.3519149964258048</v>
       </c>
       <c r="P10" s="4" t="n">
-        <v>-0.3468440840912663</v>
+        <v>-0.3458359974080949</v>
       </c>
     </row>
     <row r="11">
@@ -2446,49 +2446,49 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>3780</v>
+        <v>3781</v>
       </c>
       <c r="C11" s="4" t="n">
-        <v>-0.1338285126697656</v>
+        <v>-0.1351068581569166</v>
       </c>
       <c r="D11" s="4" t="n">
-        <v>0.08802604150930904</v>
+        <v>0.08664820595625855</v>
       </c>
       <c r="E11" s="4" t="n">
-        <v>-0.02876483919050798</v>
+        <v>-0.03012245350089415</v>
       </c>
       <c r="F11" s="4" t="n">
-        <v>0.06309017093693825</v>
+        <v>0.06171090719504235</v>
       </c>
       <c r="G11" s="4" t="n">
-        <v>-0.2234353677884044</v>
+        <v>-0.2247532212906265</v>
       </c>
       <c r="H11" s="4" t="n">
-        <v>-0.09635124069723133</v>
+        <v>-0.09769584916502794</v>
       </c>
       <c r="I11" s="4" t="n">
-        <v>-0.1402837286207372</v>
+        <v>-0.1416195484420086</v>
       </c>
       <c r="J11" s="4" t="n">
-        <v>-0.03838232635280292</v>
+        <v>-0.03975746746004205</v>
       </c>
       <c r="K11" s="4" t="n">
-        <v>-0.1112384498998935</v>
+        <v>-0.1125965744783741</v>
       </c>
       <c r="L11" s="4" t="n">
-        <v>-0.2596954834117469</v>
+        <v>-0.2610364465088111</v>
       </c>
       <c r="M11" s="4" t="n">
-        <v>-0.3439587327918758</v>
+        <v>-0.3452832687759795</v>
       </c>
       <c r="N11" s="4" t="n">
-        <v>-0.1096986733937442</v>
+        <v>-0.1110849573581092</v>
       </c>
       <c r="O11" s="4" t="n">
-        <v>-0.06549035906349587</v>
+        <v>-0.06689961768032759</v>
       </c>
       <c r="P11" s="4" t="n">
-        <v>-0.06534606821825406</v>
+        <v>-0.06423092908148931</v>
       </c>
     </row>
     <row r="12">
@@ -2498,49 +2498,49 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>3716</v>
+        <v>3717</v>
       </c>
       <c r="C12" s="4" t="n">
-        <v>-0.09333105284606802</v>
+        <v>-0.09485704930111183</v>
       </c>
       <c r="D12" s="4" t="n">
-        <v>0.1063614573837057</v>
+        <v>0.1047334891666338</v>
       </c>
       <c r="E12" s="4" t="n">
-        <v>0.1016755716592783</v>
+        <v>0.1000363628914158</v>
       </c>
       <c r="F12" s="4" t="n">
-        <v>0.1123907429708666</v>
+        <v>0.1107516888976008</v>
       </c>
       <c r="G12" s="4" t="n">
-        <v>-0.116102413510653</v>
+        <v>-0.1176969087354891</v>
       </c>
       <c r="H12" s="4" t="n">
-        <v>-0.01877004982595309</v>
+        <v>-0.02038268017177103</v>
       </c>
       <c r="I12" s="4" t="n">
-        <v>-0.06198030839968993</v>
+        <v>-0.06358466639603932</v>
       </c>
       <c r="J12" s="4" t="n">
-        <v>0.02286030146829887</v>
+        <v>0.02121848395665182</v>
       </c>
       <c r="K12" s="4" t="n">
-        <v>-0.1039322790966821</v>
+        <v>-0.1055426727339892</v>
       </c>
       <c r="L12" s="4" t="n">
-        <v>-0.1865521975902951</v>
+        <v>-0.1881664455822261</v>
       </c>
       <c r="M12" s="4" t="n">
-        <v>-0.2149443773060398</v>
+        <v>-0.2165579056170159</v>
       </c>
       <c r="N12" s="4" t="n">
-        <v>0.07658333569264641</v>
+        <v>0.07489160653847904</v>
       </c>
       <c r="O12" s="4" t="n">
-        <v>0.2095492258170069</v>
+        <v>0.2078083859460378</v>
       </c>
       <c r="P12" s="4" t="n">
-        <v>0.1516477978606545</v>
+        <v>0.1529033383219627</v>
       </c>
     </row>
     <row r="13">
@@ -2550,49 +2550,49 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>3659</v>
+        <v>3660</v>
       </c>
       <c r="C13" s="4" t="n">
-        <v>-0.01522481258470521</v>
+        <v>-0.01699008444123962</v>
       </c>
       <c r="D13" s="4" t="n">
-        <v>0.1853721583539638</v>
+        <v>0.1834970049421258</v>
       </c>
       <c r="E13" s="4" t="n">
-        <v>0.05052807957522276</v>
+        <v>0.04867538840515806</v>
       </c>
       <c r="F13" s="4" t="n">
-        <v>0.1138829861591049</v>
+        <v>0.1120164853713774</v>
       </c>
       <c r="G13" s="4" t="n">
-        <v>-0.0007422882114980212</v>
+        <v>-0.002596680466169232</v>
       </c>
       <c r="H13" s="4" t="n">
-        <v>0.1480515192707301</v>
+        <v>0.1461656646643945</v>
       </c>
       <c r="I13" s="4" t="n">
-        <v>0.1600877578914677</v>
+        <v>0.1581948007767053</v>
       </c>
       <c r="J13" s="4" t="n">
-        <v>0.4172851035191627</v>
+        <v>0.4153052265612374</v>
       </c>
       <c r="K13" s="4" t="n">
-        <v>0.2622840735060947</v>
+        <v>0.2603434378741625</v>
       </c>
       <c r="L13" s="4" t="n">
-        <v>0.1917072935724278</v>
+        <v>0.1897561558689915</v>
       </c>
       <c r="M13" s="4" t="n">
-        <v>0.1661635149308012</v>
+        <v>0.1642114267652204</v>
       </c>
       <c r="N13" s="4" t="n">
-        <v>0.3525391786436245</v>
+        <v>0.3505363722470278</v>
       </c>
       <c r="O13" s="4" t="n">
-        <v>0.4941961956543039</v>
+        <v>0.4921394395078522</v>
       </c>
       <c r="P13" s="4" t="n">
-        <v>0.4589102773007312</v>
+        <v>0.4602638485165969</v>
       </c>
     </row>
     <row r="14">
@@ -2602,49 +2602,49 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>3581</v>
+        <v>3582</v>
       </c>
       <c r="C14" s="4" t="n">
-        <v>0.01073530249453114</v>
+        <v>0.008652815084566612</v>
       </c>
       <c r="D14" s="4" t="n">
-        <v>0.2785115847773412</v>
+        <v>0.2762896404530153</v>
       </c>
       <c r="E14" s="4" t="n">
-        <v>0.0658209192492194</v>
+        <v>0.06364138171079503</v>
       </c>
       <c r="F14" s="4" t="n">
-        <v>0.1834217827280753</v>
+        <v>0.1812135506026209</v>
       </c>
       <c r="G14" s="4" t="n">
-        <v>0.1894443139762032</v>
+        <v>0.18721190113137</v>
       </c>
       <c r="H14" s="4" t="n">
-        <v>0.3350605322815099</v>
+        <v>0.3327982287661797</v>
       </c>
       <c r="I14" s="4" t="n">
-        <v>0.2656405461454625</v>
+        <v>0.2633930693097071</v>
       </c>
       <c r="J14" s="4" t="n">
-        <v>0.5664975658328615</v>
+        <v>0.5641465178632075</v>
       </c>
       <c r="K14" s="4" t="n">
-        <v>0.3537210542926132</v>
+        <v>0.3514257188562198</v>
       </c>
       <c r="L14" s="4" t="n">
-        <v>0.2443426600153202</v>
+        <v>0.2420428262538152</v>
       </c>
       <c r="M14" s="4" t="n">
-        <v>0.1390084181842894</v>
+        <v>0.1367286377761587</v>
       </c>
       <c r="N14" s="4" t="n">
-        <v>0.3007757258825805</v>
+        <v>0.2984510071069835</v>
       </c>
       <c r="O14" s="4" t="n">
-        <v>0.5384063173007902</v>
+        <v>0.5359973399105513</v>
       </c>
       <c r="P14" s="4" t="n">
-        <v>0.6086254658482204</v>
+        <v>0.6101938262742266</v>
       </c>
     </row>
     <row r="15">
@@ -2654,49 +2654,49 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>3499</v>
+        <v>3500</v>
       </c>
       <c r="C15" s="4" t="n">
-        <v>0.01225644061006648</v>
+        <v>0.009832617344947892</v>
       </c>
       <c r="D15" s="4" t="n">
-        <v>0.2954437774495204</v>
+        <v>0.2928637078369007</v>
       </c>
       <c r="E15" s="4" t="n">
-        <v>0.08701394712376498</v>
+        <v>0.08447368617824935</v>
       </c>
       <c r="F15" s="4" t="n">
-        <v>0.1473288906708135</v>
+        <v>0.1447761366596438</v>
       </c>
       <c r="G15" s="4" t="n">
-        <v>0.1945738547314377</v>
+        <v>0.1919814323816809</v>
       </c>
       <c r="H15" s="4" t="n">
-        <v>0.2510983765865262</v>
+        <v>0.2485022463241293</v>
       </c>
       <c r="I15" s="4" t="n">
-        <v>0.267580205566702</v>
+        <v>0.264974112930382</v>
       </c>
       <c r="J15" s="4" t="n">
-        <v>0.5008141878714696</v>
+        <v>0.4981186033023448</v>
       </c>
       <c r="K15" s="4" t="n">
-        <v>0.341544706394771</v>
+        <v>0.3388903587609065</v>
       </c>
       <c r="L15" s="4" t="n">
-        <v>0.3636904515675781</v>
+        <v>0.3609890325813154</v>
       </c>
       <c r="M15" s="4" t="n">
-        <v>0.1750528723737332</v>
+        <v>0.1723944209602166</v>
       </c>
       <c r="N15" s="4" t="n">
-        <v>0.425503854674453</v>
+        <v>0.4227740979938162</v>
       </c>
       <c r="O15" s="4" t="n">
-        <v>0.8500119645848301</v>
+        <v>0.847140051577874</v>
       </c>
       <c r="P15" s="4" t="n">
-        <v>0.88753389294979</v>
+        <v>0.8893036611629626</v>
       </c>
     </row>
     <row r="16">
@@ -2706,101 +2706,101 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>3410</v>
+        <v>3411</v>
       </c>
       <c r="C16" s="4" t="n">
-        <v>0.1504413175346997</v>
+        <v>0.147588642362841</v>
       </c>
       <c r="D16" s="4" t="n">
-        <v>0.5706163543769023</v>
+        <v>0.5675531495540298</v>
       </c>
       <c r="E16" s="4" t="n">
-        <v>0.3963485329856837</v>
+        <v>0.393313516778278</v>
       </c>
       <c r="F16" s="4" t="n">
-        <v>0.5426531945910682</v>
+        <v>0.5395808079916478</v>
       </c>
       <c r="G16" s="4" t="n">
-        <v>0.5467626261119705</v>
+        <v>0.5436585733675159</v>
       </c>
       <c r="H16" s="4" t="n">
-        <v>0.5971170305767117</v>
+        <v>0.5940125961266816</v>
       </c>
       <c r="I16" s="4" t="n">
-        <v>0.7333981578508499</v>
+        <v>0.7302476951648913</v>
       </c>
       <c r="J16" s="4" t="n">
-        <v>0.8386470596137414</v>
+        <v>0.8354390812121224</v>
       </c>
       <c r="K16" s="4" t="n">
-        <v>0.6476328750303253</v>
+        <v>0.6444758889669941</v>
       </c>
       <c r="L16" s="4" t="n">
-        <v>0.6633164646543506</v>
+        <v>0.6601075467913873</v>
       </c>
       <c r="M16" s="4" t="n">
-        <v>0.5630861305027395</v>
+        <v>0.5598938962614071</v>
       </c>
       <c r="N16" s="4" t="n">
-        <v>0.8485951637059088</v>
+        <v>0.8453194669872701</v>
       </c>
       <c r="O16" s="4" t="n">
-        <v>1.11936741124898</v>
+        <v>1.11598804108214</v>
       </c>
       <c r="P16" s="4" t="n">
-        <v>1.122104474070994</v>
+        <v>1.124123780943506</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>X &gt; -0.3368</t>
+          <t>X &gt; -0.3367</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>3342</v>
+        <v>3343</v>
       </c>
       <c r="C17" s="4" t="n">
-        <v>0.3828657036350336</v>
+        <v>0.3796322412177275</v>
       </c>
       <c r="D17" s="4" t="n">
-        <v>0.9039326106540315</v>
+        <v>0.9004463115732051</v>
       </c>
       <c r="E17" s="4" t="n">
-        <v>0.8237101744254218</v>
+        <v>0.8202224964172089</v>
       </c>
       <c r="F17" s="4" t="n">
-        <v>0.851136215987033</v>
+        <v>0.8476462967323073</v>
       </c>
       <c r="G17" s="4" t="n">
-        <v>0.7171377892536199</v>
+        <v>0.7136539675809743</v>
       </c>
       <c r="H17" s="4" t="n">
-        <v>0.8819305289130028</v>
+        <v>0.8784134319774637</v>
       </c>
       <c r="I17" s="4" t="n">
-        <v>0.93320533278537</v>
+        <v>0.9296660510158361</v>
       </c>
       <c r="J17" s="4" t="n">
-        <v>1.080008954862471</v>
+        <v>1.076396135296719</v>
       </c>
       <c r="K17" s="4" t="n">
-        <v>0.8565479192494649</v>
+        <v>0.8529963381008798</v>
       </c>
       <c r="L17" s="4" t="n">
-        <v>1.039321739513234</v>
+        <v>1.035662938061996</v>
       </c>
       <c r="M17" s="4" t="n">
-        <v>0.8516425469479145</v>
+        <v>0.8480257089058725</v>
       </c>
       <c r="N17" s="4" t="n">
-        <v>1.202153110047838</v>
+        <v>1.198431655195812</v>
       </c>
       <c r="O17" s="4" t="n">
-        <v>1.427260800104676</v>
+        <v>1.423444976076546</v>
       </c>
       <c r="P17" s="4" t="n">
-        <v>1.425064578386291</v>
+        <v>1.427246484119244</v>
       </c>
     </row>
     <row r="18">
@@ -2810,49 +2810,49 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>3282</v>
+        <v>3283</v>
       </c>
       <c r="C18" s="4" t="n">
-        <v>0.5262885386671172</v>
+        <v>0.5227247461646698</v>
       </c>
       <c r="D18" s="4" t="n">
-        <v>1.025528443267781</v>
+        <v>1.021706677615775</v>
       </c>
       <c r="E18" s="4" t="n">
-        <v>0.890341042585689</v>
+        <v>0.886532684725104</v>
       </c>
       <c r="F18" s="4" t="n">
-        <v>0.9159131975754349</v>
+        <v>0.9121035332005292</v>
       </c>
       <c r="G18" s="4" t="n">
-        <v>0.7893077043825585</v>
+        <v>0.7854995061977732</v>
       </c>
       <c r="H18" s="4" t="n">
-        <v>0.9517032458753008</v>
+        <v>0.947863033682772</v>
       </c>
       <c r="I18" s="4" t="n">
-        <v>0.9446716599591838</v>
+        <v>0.9408260564597342</v>
       </c>
       <c r="J18" s="4" t="n">
-        <v>1.04185566147018</v>
+        <v>1.037948078621291</v>
       </c>
       <c r="K18" s="4" t="n">
-        <v>0.8458403750938004</v>
+        <v>0.8419863877219669</v>
       </c>
       <c r="L18" s="4" t="n">
-        <v>0.8648781128175003</v>
+        <v>0.8609609018379558</v>
       </c>
       <c r="M18" s="4" t="n">
-        <v>0.7687818743704256</v>
+        <v>0.764878491218056</v>
       </c>
       <c r="N18" s="4" t="n">
-        <v>1.12504298061063</v>
+        <v>1.121031323480103</v>
       </c>
       <c r="O18" s="4" t="n">
-        <v>1.361921803147112</v>
+        <v>1.357808484226837</v>
       </c>
       <c r="P18" s="4" t="n">
-        <v>1.355100233398062</v>
+        <v>1.35753393834846</v>
       </c>
     </row>
     <row r="19">
@@ -2862,49 +2862,49 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>3202</v>
+        <v>3203</v>
       </c>
       <c r="C19" s="4" t="n">
-        <v>0.3837000934758663</v>
+        <v>0.3797804868785803</v>
       </c>
       <c r="D19" s="4" t="n">
-        <v>0.8732083530734371</v>
+        <v>0.8690176275682262</v>
       </c>
       <c r="E19" s="4" t="n">
-        <v>0.7755628709668088</v>
+        <v>0.7713716689958758</v>
       </c>
       <c r="F19" s="4" t="n">
-        <v>0.8607585451405342</v>
+        <v>0.8565480249021178</v>
       </c>
       <c r="G19" s="4" t="n">
-        <v>0.6509671606670295</v>
+        <v>0.6467806375566312</v>
       </c>
       <c r="H19" s="4" t="n">
-        <v>0.8722592590938802</v>
+        <v>0.8680231563089507</v>
       </c>
       <c r="I19" s="4" t="n">
-        <v>0.835977665861364</v>
+        <v>0.8317444440971542</v>
       </c>
       <c r="J19" s="4" t="n">
-        <v>0.9472017852119308</v>
+        <v>0.9428976821089776</v>
       </c>
       <c r="K19" s="4" t="n">
-        <v>0.6230618072571872</v>
+        <v>0.6188520095554537</v>
       </c>
       <c r="L19" s="4" t="n">
-        <v>0.7261014960888943</v>
+        <v>0.7217954449241901</v>
       </c>
       <c r="M19" s="4" t="n">
-        <v>0.6014728989063798</v>
+        <v>0.5971884972968837</v>
       </c>
       <c r="N19" s="4" t="n">
-        <v>0.8408747438907014</v>
+        <v>0.8365158332714557</v>
       </c>
       <c r="O19" s="4" t="n">
-        <v>1.125298526290372</v>
+        <v>1.120817877175057</v>
       </c>
       <c r="P19" s="4" t="n">
-        <v>1.143223972331796</v>
+        <v>1.146045108912837</v>
       </c>
     </row>
     <row r="20">
@@ -2914,49 +2914,49 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>3120</v>
+        <v>3121</v>
       </c>
       <c r="C20" s="4" t="n">
-        <v>0.5547582964513751</v>
+        <v>0.5503539120310563</v>
       </c>
       <c r="D20" s="4" t="n">
-        <v>1.03547337972487</v>
+        <v>1.030783289743667</v>
       </c>
       <c r="E20" s="4" t="n">
-        <v>0.8498478814683921</v>
+        <v>0.8451826857719382</v>
       </c>
       <c r="F20" s="4" t="n">
-        <v>0.9019379880443452</v>
+        <v>0.8972641232581324</v>
       </c>
       <c r="G20" s="4" t="n">
-        <v>0.7966492643416885</v>
+        <v>0.7919630406059071</v>
       </c>
       <c r="H20" s="4" t="n">
-        <v>1.047960990416229</v>
+        <v>1.04321591362816</v>
       </c>
       <c r="I20" s="4" t="n">
-        <v>1.204883354939582</v>
+        <v>1.200078693684837</v>
       </c>
       <c r="J20" s="4" t="n">
-        <v>1.299408281128244</v>
+        <v>1.294533028133209</v>
       </c>
       <c r="K20" s="4" t="n">
-        <v>1.032476213244081</v>
+        <v>1.027678790970441</v>
       </c>
       <c r="L20" s="4" t="n">
-        <v>1.064635279176464</v>
+        <v>1.059756155868996</v>
       </c>
       <c r="M20" s="4" t="n">
-        <v>0.8461574221182389</v>
+        <v>0.8413290052912572</v>
       </c>
       <c r="N20" s="4" t="n">
-        <v>1.091022501218383</v>
+        <v>1.086115826877347</v>
       </c>
       <c r="O20" s="4" t="n">
-        <v>1.361999880545824</v>
+        <v>1.3569696765354</v>
       </c>
       <c r="P20" s="4" t="n">
-        <v>1.341857838985646</v>
+        <v>1.344963477156</v>
       </c>
     </row>
     <row r="21">
@@ -2966,49 +2966,49 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>3028</v>
+        <v>3029</v>
       </c>
       <c r="C21" s="4" t="n">
-        <v>0.3510207393099236</v>
+        <v>0.3461714119377035</v>
       </c>
       <c r="D21" s="4" t="n">
-        <v>0.8949880668257748</v>
+        <v>0.8898117205320446</v>
       </c>
       <c r="E21" s="4" t="n">
-        <v>0.6169341019205206</v>
+        <v>0.611810702173095</v>
       </c>
       <c r="F21" s="4" t="n">
-        <v>0.7324133091631992</v>
+        <v>0.727260815886666</v>
       </c>
       <c r="G21" s="4" t="n">
-        <v>0.8048258250150866</v>
+        <v>0.7995979610071302</v>
       </c>
       <c r="H21" s="4" t="n">
-        <v>1.08768043550652</v>
+        <v>1.082383428205226</v>
       </c>
       <c r="I21" s="4" t="n">
-        <v>1.317839069871809</v>
+        <v>1.312455660281756</v>
       </c>
       <c r="J21" s="4" t="n">
-        <v>1.495353489011102</v>
+        <v>1.489866334421784</v>
       </c>
       <c r="K21" s="4" t="n">
-        <v>1.255210140049236</v>
+        <v>1.249793607439457</v>
       </c>
       <c r="L21" s="4" t="n">
-        <v>1.31421382504994</v>
+        <v>1.308697797807667</v>
       </c>
       <c r="M21" s="4" t="n">
-        <v>1.128394140718108</v>
+        <v>1.122917794442579</v>
       </c>
       <c r="N21" s="4" t="n">
-        <v>1.313736636821567</v>
+        <v>1.308199233764853</v>
       </c>
       <c r="O21" s="4" t="n">
-        <v>1.704824962745462</v>
+        <v>1.699117280149061</v>
       </c>
       <c r="P21" s="4" t="n">
-        <v>1.70962195509852</v>
+        <v>1.71301728659332</v>
       </c>
     </row>
     <row r="22">
@@ -3021,46 +3021,46 @@
         <v>2876</v>
       </c>
       <c r="C22" s="4" t="n">
-        <v>0.415148937407757</v>
+        <v>0.4093574204867636</v>
       </c>
       <c r="D22" s="4" t="n">
-        <v>0.8655457391499866</v>
+        <v>0.8594214221081913</v>
       </c>
       <c r="E22" s="4" t="n">
-        <v>0.5243743844841973</v>
+        <v>0.5183221965307396</v>
       </c>
       <c r="F22" s="4" t="n">
-        <v>0.2924175534952624</v>
+        <v>0.2864562783397844</v>
       </c>
       <c r="G22" s="4" t="n">
-        <v>0.3970830392069473</v>
+        <v>0.3910239538898779</v>
       </c>
       <c r="H22" s="4" t="n">
-        <v>0.6790220743077811</v>
+        <v>0.6728938094166921</v>
       </c>
       <c r="I22" s="4" t="n">
-        <v>0.7522653274931059</v>
+        <v>0.7460989748462126</v>
       </c>
       <c r="J22" s="4" t="n">
-        <v>0.9638211185169823</v>
+        <v>0.9575273377292604</v>
       </c>
       <c r="K22" s="4" t="n">
-        <v>0.7486984354663093</v>
+        <v>0.7424691208902701</v>
       </c>
       <c r="L22" s="4" t="n">
-        <v>0.960043282471112</v>
+        <v>0.9536450447578773</v>
       </c>
       <c r="M22" s="4" t="n">
-        <v>0.636121678881203</v>
+        <v>0.6298101209155078</v>
       </c>
       <c r="N22" s="4" t="n">
-        <v>0.9335964330201634</v>
+        <v>0.9271815863783033</v>
       </c>
       <c r="O22" s="4" t="n">
-        <v>1.367715123734435</v>
+        <v>1.361100162483176</v>
       </c>
       <c r="P22" s="4" t="n">
-        <v>1.269731309974567</v>
+        <v>1.259301674276415</v>
       </c>
     </row>
     <row r="23">
@@ -3073,46 +3073,46 @@
         <v>2744</v>
       </c>
       <c r="C23" s="4" t="n">
-        <v>0.323719077100094</v>
+        <v>0.3362413667757167</v>
       </c>
       <c r="D23" s="4" t="n">
-        <v>0.8040789759166742</v>
+        <v>0.7970291014109137</v>
       </c>
       <c r="E23" s="4" t="n">
-        <v>0.7728466329564512</v>
+        <v>0.7858537643740533</v>
       </c>
       <c r="F23" s="4" t="n">
-        <v>0.4866838787952119</v>
+        <v>0.4797152715987778</v>
       </c>
       <c r="G23" s="4" t="n">
-        <v>0.6394230856946663</v>
+        <v>0.6525338900696056</v>
       </c>
       <c r="H23" s="4" t="n">
-        <v>0.9004881590960281</v>
+        <v>0.9135310553903935</v>
       </c>
       <c r="I23" s="4" t="n">
-        <v>0.945125291512106</v>
+        <v>0.9379512890671222</v>
       </c>
       <c r="J23" s="4" t="n">
-        <v>1.189860518792976</v>
+        <v>1.182534837979269</v>
       </c>
       <c r="K23" s="4" t="n">
-        <v>0.8944660165944214</v>
+        <v>0.8872359278086108</v>
       </c>
       <c r="L23" s="4" t="n">
-        <v>1.26697033604858</v>
+        <v>1.259493956305988</v>
       </c>
       <c r="M23" s="4" t="n">
-        <v>1.010227441507915</v>
+        <v>1.002814560450325</v>
       </c>
       <c r="N23" s="4" t="n">
-        <v>1.263269490981621</v>
+        <v>1.276721779701731</v>
       </c>
       <c r="O23" s="4" t="n">
-        <v>1.717650448549847</v>
+        <v>1.73120649490145</v>
       </c>
       <c r="P23" s="4" t="n">
-        <v>1.602940293945665</v>
+        <v>1.592510658247512</v>
       </c>
     </row>
     <row r="24">
@@ -3125,46 +3125,46 @@
         <v>2573</v>
       </c>
       <c r="C24" s="4" t="n">
-        <v>0.495692114572627</v>
+        <v>0.5082144042482497</v>
       </c>
       <c r="D24" s="4" t="n">
-        <v>0.5145532842170795</v>
+        <v>0.5274630937931306</v>
       </c>
       <c r="E24" s="4" t="n">
-        <v>0.3137839565024692</v>
+        <v>0.3267910879200713</v>
       </c>
       <c r="F24" s="4" t="n">
-        <v>0.05583833134598848</v>
+        <v>0.06881747374445268</v>
       </c>
       <c r="G24" s="4" t="n">
-        <v>0.2938146318017729</v>
+        <v>0.3069254361767122</v>
       </c>
       <c r="H24" s="4" t="n">
-        <v>0.397157190635447</v>
+        <v>0.4102000869298124</v>
       </c>
       <c r="I24" s="4" t="n">
-        <v>0.6229824795743539</v>
+        <v>0.63604873387483</v>
       </c>
       <c r="J24" s="4" t="n">
-        <v>0.8374760994263966</v>
+        <v>0.8289179782868459</v>
       </c>
       <c r="K24" s="4" t="n">
-        <v>0.6428320795999554</v>
+        <v>0.6343351463736084</v>
       </c>
       <c r="L24" s="4" t="n">
-        <v>0.9026432940537106</v>
+        <v>0.8939131100259488</v>
       </c>
       <c r="M24" s="4" t="n">
-        <v>0.6201596937936529</v>
+        <v>0.6336169875038706</v>
       </c>
       <c r="N24" s="4" t="n">
-        <v>1.082059368822719</v>
+        <v>1.095511657542829</v>
       </c>
       <c r="O24" s="4" t="n">
-        <v>1.361377241360131</v>
+        <v>1.374933287711734</v>
       </c>
       <c r="P24" s="4" t="n">
-        <v>1.222447193924012</v>
+        <v>1.21201755822586</v>
       </c>
     </row>
     <row r="25">
@@ -3177,46 +3177,46 @@
         <v>2406</v>
       </c>
       <c r="C25" s="4" t="n">
-        <v>0.6237686623336671</v>
+        <v>0.6362909520092899</v>
       </c>
       <c r="D25" s="4" t="n">
-        <v>0.8825192388955898</v>
+        <v>0.895429048471641</v>
       </c>
       <c r="E25" s="4" t="n">
-        <v>0.4876505322989999</v>
+        <v>0.500657663716602</v>
       </c>
       <c r="F25" s="4" t="n">
-        <v>0.2022760672340169</v>
+        <v>0.2152552096324811</v>
       </c>
       <c r="G25" s="4" t="n">
-        <v>0.2872962486705788</v>
+        <v>0.3004070530455181</v>
       </c>
       <c r="H25" s="4" t="n">
-        <v>0.5847381863862395</v>
+        <v>0.5977810826806049</v>
       </c>
       <c r="I25" s="4" t="n">
-        <v>0.9156320667864435</v>
+        <v>0.9286983210869195</v>
       </c>
       <c r="J25" s="4" t="n">
-        <v>0.7393879863756823</v>
+        <v>0.7525689956709201</v>
       </c>
       <c r="K25" s="4" t="n">
-        <v>0.4290115415898867</v>
+        <v>0.4422102805446499</v>
       </c>
       <c r="L25" s="4" t="n">
-        <v>0.659518110510426</v>
+        <v>0.6729232381632571</v>
       </c>
       <c r="M25" s="4" t="n">
-        <v>0.4132020264255942</v>
+        <v>0.426659320135812</v>
       </c>
       <c r="N25" s="4" t="n">
-        <v>0.9047755412107676</v>
+        <v>0.9182278299308777</v>
       </c>
       <c r="O25" s="4" t="n">
-        <v>1.398901645145337</v>
+        <v>1.41245769149694</v>
       </c>
       <c r="P25" s="4" t="n">
-        <v>1.399246418818123</v>
+        <v>1.388816783119971</v>
       </c>
     </row>
     <row r="26">
@@ -3229,46 +3229,46 @@
         <v>2253</v>
       </c>
       <c r="C26" s="4" t="n">
-        <v>1.035190175129571</v>
+        <v>1.047712464805194</v>
       </c>
       <c r="D26" s="4" t="n">
-        <v>1.199027125858173</v>
+        <v>1.211936935434224</v>
       </c>
       <c r="E26" s="4" t="n">
-        <v>0.9373142115385491</v>
+        <v>0.9503213429561512</v>
       </c>
       <c r="F26" s="4" t="n">
-        <v>0.7568704954997898</v>
+        <v>0.769849637898254</v>
       </c>
       <c r="G26" s="4" t="n">
-        <v>0.751072449535485</v>
+        <v>0.7641832539104243</v>
       </c>
       <c r="H26" s="4" t="n">
-        <v>1.226055443620425</v>
+        <v>1.23909833991479</v>
       </c>
       <c r="I26" s="4" t="n">
-        <v>1.629559631363691</v>
+        <v>1.642625885664167</v>
       </c>
       <c r="J26" s="4" t="n">
-        <v>1.339917288951469</v>
+        <v>1.353098298246707</v>
       </c>
       <c r="K26" s="4" t="n">
-        <v>1.056991082307555</v>
+        <v>1.070189821262318</v>
       </c>
       <c r="L26" s="4" t="n">
-        <v>1.272112235495335</v>
+        <v>1.285517363148166</v>
       </c>
       <c r="M26" s="4" t="n">
-        <v>1.022973647085443</v>
+        <v>1.036430940795661</v>
       </c>
       <c r="N26" s="4" t="n">
-        <v>1.545594709446405</v>
+        <v>1.559046998166515</v>
       </c>
       <c r="O26" s="4" t="n">
-        <v>1.968660116255613</v>
+        <v>1.982216162607216</v>
       </c>
       <c r="P26" s="4" t="n">
-        <v>2.085225656254941</v>
+        <v>2.074796020556789</v>
       </c>
     </row>
     <row r="27">
@@ -3281,46 +3281,46 @@
         <v>2087</v>
       </c>
       <c r="C27" s="4" t="n">
-        <v>0.9804476404991789</v>
+        <v>0.9929699301748016</v>
       </c>
       <c r="D27" s="4" t="n">
-        <v>1.525079106595769</v>
+        <v>1.53798891617182</v>
       </c>
       <c r="E27" s="4" t="n">
-        <v>1.226041736846334</v>
+        <v>1.239048868263936</v>
       </c>
       <c r="F27" s="4" t="n">
-        <v>0.6854755115237907</v>
+        <v>0.6984546539222549</v>
       </c>
       <c r="G27" s="4" t="n">
-        <v>0.5303796438402202</v>
+        <v>0.5434904482151595</v>
       </c>
       <c r="H27" s="4" t="n">
-        <v>0.9715685868265993</v>
+        <v>0.9846114831209647</v>
       </c>
       <c r="I27" s="4" t="n">
-        <v>1.413907222213638</v>
+        <v>1.426973476514114</v>
       </c>
       <c r="J27" s="4" t="n">
-        <v>1.425880507667891</v>
+        <v>1.439061516963129</v>
       </c>
       <c r="K27" s="4" t="n">
-        <v>1.36488062148559</v>
+        <v>1.378079360440353</v>
       </c>
       <c r="L27" s="4" t="n">
-        <v>1.664731478623438</v>
+        <v>1.678136606276269</v>
       </c>
       <c r="M27" s="4" t="n">
-        <v>1.364146817458717</v>
+        <v>1.377604111168935</v>
       </c>
       <c r="N27" s="4" t="n">
-        <v>1.829770990616318</v>
+        <v>1.843223279336428</v>
       </c>
       <c r="O27" s="4" t="n">
-        <v>2.511576753413621</v>
+        <v>2.525132799765224</v>
       </c>
       <c r="P27" s="4" t="n">
-        <v>2.521719743572049</v>
+        <v>2.511290107873897</v>
       </c>
     </row>
     <row r="28">
@@ -3330,101 +3330,101 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>1926</v>
+        <v>1925</v>
       </c>
       <c r="C28" s="4" t="n">
-        <v>1.66024807646707</v>
+        <v>1.648954099335775</v>
       </c>
       <c r="D28" s="4" t="n">
-        <v>1.606306862256709</v>
+        <v>1.596209564713504</v>
       </c>
       <c r="E28" s="4" t="n">
-        <v>1.26335923561858</v>
+        <v>1.253386231906525</v>
       </c>
       <c r="F28" s="4" t="n">
-        <v>0.9782437285583825</v>
+        <v>0.9680269599104605</v>
       </c>
       <c r="G28" s="4" t="n">
-        <v>0.595585753361604</v>
+        <v>0.5855815626589305</v>
       </c>
       <c r="H28" s="4" t="n">
-        <v>0.9968698509941873</v>
+        <v>0.986851696190115</v>
       </c>
       <c r="I28" s="4" t="n">
-        <v>1.846715572974247</v>
+        <v>1.83720627198889</v>
       </c>
       <c r="J28" s="4" t="n">
-        <v>1.950664053735842</v>
+        <v>1.941566199630721</v>
       </c>
       <c r="K28" s="4" t="n">
-        <v>1.889664167553541</v>
+        <v>1.93253209505599</v>
       </c>
       <c r="L28" s="4" t="n">
-        <v>2.233723821570265</v>
+        <v>2.277418493531322</v>
       </c>
       <c r="M28" s="4" t="n">
-        <v>2.028970497252686</v>
+        <v>2.020769283323084</v>
       </c>
       <c r="N28" s="4" t="n">
-        <v>2.686406614099674</v>
+        <v>2.730472111003081</v>
       </c>
       <c r="O28" s="4" t="n">
-        <v>3.304573602324034</v>
+        <v>3.349282296650713</v>
       </c>
       <c r="P28" s="4" t="n">
-        <v>3.242768454849539</v>
+        <v>3.263329635188938</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>X &gt; -0.1123</t>
+          <t>X &gt; -0.1122</t>
         </is>
       </c>
       <c r="B29" t="n">
         <v>1750</v>
       </c>
       <c r="C29" s="4" t="n">
-        <v>1.506561679790025</v>
+        <v>1.519083969465647</v>
       </c>
       <c r="D29" s="4" t="n">
-        <v>1.952130923968632</v>
+        <v>1.965040733544683</v>
       </c>
       <c r="E29" s="4" t="n">
-        <v>1.614405074514892</v>
+        <v>1.627412205932494</v>
       </c>
       <c r="F29" s="4" t="n">
-        <v>1.116086778550958</v>
+        <v>1.129065920949422</v>
       </c>
       <c r="G29" s="4" t="n">
-        <v>0.5776655634787886</v>
+        <v>0.5907763678537279</v>
       </c>
       <c r="H29" s="4" t="n">
-        <v>0.9322503583373063</v>
+        <v>0.9452932546316717</v>
       </c>
       <c r="I29" s="4" t="n">
-        <v>2.218945212493608</v>
+        <v>2.232011466794084</v>
       </c>
       <c r="J29" s="4" t="n">
-        <v>2.26604752799782</v>
+        <v>2.279228537293058</v>
       </c>
       <c r="K29" s="4" t="n">
-        <v>2.147904784672662</v>
+        <v>2.161103523627425</v>
       </c>
       <c r="L29" s="4" t="n">
-        <v>2.554922456787594</v>
+        <v>2.568327584440425</v>
       </c>
       <c r="M29" s="4" t="n">
-        <v>1.950169132470009</v>
+        <v>1.963626426180227</v>
       </c>
       <c r="N29" s="4" t="n">
-        <v>2.784552289815444</v>
+        <v>2.798004578535554</v>
       </c>
       <c r="O29" s="4" t="n">
-        <v>3.450011964584817</v>
+        <v>3.46356801093642</v>
       </c>
       <c r="P29" s="4" t="n">
-        <v>3.071161868289686</v>
+        <v>3.060732232591533</v>
       </c>
     </row>
     <row r="30">
@@ -3437,46 +3437,46 @@
         <v>1511</v>
       </c>
       <c r="C30" s="4" t="n">
-        <v>1.113444538823778</v>
+        <v>1.125966828499401</v>
       </c>
       <c r="D30" s="4" t="n">
-        <v>1.619673705475662</v>
+        <v>1.632583515051714</v>
       </c>
       <c r="E30" s="4" t="n">
-        <v>1.42334900946809</v>
+        <v>1.436356140885692</v>
       </c>
       <c r="F30" s="4" t="n">
-        <v>1.818327489527611</v>
+        <v>1.831306631926076</v>
       </c>
       <c r="G30" s="4" t="n">
-        <v>0.9489995901404171</v>
+        <v>0.9621103945153564</v>
       </c>
       <c r="H30" s="4" t="n">
-        <v>1.04789751726706</v>
+        <v>1.060940413561426</v>
       </c>
       <c r="I30" s="4" t="n">
-        <v>2.088246526665863</v>
+        <v>2.101312780966339</v>
       </c>
       <c r="J30" s="4" t="n">
-        <v>2.01815114906239</v>
+        <v>2.031332158357628</v>
       </c>
       <c r="K30" s="4" t="n">
-        <v>1.692425915428075</v>
+        <v>1.705624654382838</v>
       </c>
       <c r="L30" s="4" t="n">
-        <v>2.033564793934232</v>
+        <v>2.046969921587063</v>
       </c>
       <c r="M30" s="4" t="n">
-        <v>1.233179437849607</v>
+        <v>1.246636731559825</v>
       </c>
       <c r="N30" s="4" t="n">
-        <v>2.194101311277109</v>
+        <v>2.207553599997219</v>
       </c>
       <c r="O30" s="4" t="n">
-        <v>2.766566753277267</v>
+        <v>2.78012279962887</v>
       </c>
       <c r="P30" s="4" t="n">
-        <v>2.354474716923512</v>
+        <v>2.34404508122536</v>
       </c>
     </row>
     <row r="31">
@@ -3489,98 +3489,98 @@
         <v>1286</v>
       </c>
       <c r="C31" s="4" t="n">
-        <v>2.794275521158603</v>
+        <v>2.806797810834226</v>
       </c>
       <c r="D31" s="4" t="n">
-        <v>2.815672359205244</v>
+        <v>2.828582168781296</v>
       </c>
       <c r="E31" s="4" t="n">
-        <v>2.343043154941462</v>
+        <v>2.356050286359064</v>
       </c>
       <c r="F31" s="4" t="n">
-        <v>3.017619771219259</v>
+        <v>3.030598913617723</v>
       </c>
       <c r="G31" s="4" t="n">
-        <v>1.31279109113931</v>
+        <v>1.325901895514249</v>
       </c>
       <c r="H31" s="4" t="n">
-        <v>1.843514521856527</v>
+        <v>1.856557418150892</v>
       </c>
       <c r="I31" s="4" t="n">
-        <v>2.847427771924842</v>
+        <v>2.860494026225318</v>
       </c>
       <c r="J31" s="4" t="n">
-        <v>2.846807359146453</v>
+        <v>2.859988368441691</v>
       </c>
       <c r="K31" s="4" t="n">
-        <v>2.708046975296966</v>
+        <v>2.721245714251729</v>
       </c>
       <c r="L31" s="4" t="n">
-        <v>3.024329255276818</v>
+        <v>3.037734382929649</v>
       </c>
       <c r="M31" s="4" t="n">
-        <v>2.35301294495612</v>
+        <v>2.366470238666338</v>
       </c>
       <c r="N31" s="4" t="n">
-        <v>3.087240581306226</v>
+        <v>3.100692870026336</v>
       </c>
       <c r="O31" s="4" t="n">
-        <v>3.600111942367548</v>
+        <v>3.613667988719151</v>
       </c>
       <c r="P31" s="4" t="n">
-        <v>3.227749293306346</v>
+        <v>3.217319657608193</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>X &gt; -0.05613</t>
+          <t>X &gt; -0.05612</t>
         </is>
       </c>
       <c r="B32" t="n">
         <v>1065</v>
       </c>
       <c r="C32" s="4" t="n">
-        <v>3.562899707959041</v>
+        <v>3.575421997634663</v>
       </c>
       <c r="D32" s="4" t="n">
-        <v>3.641466940065207</v>
+        <v>3.654376749641258</v>
       </c>
       <c r="E32" s="4" t="n">
-        <v>3.340494947083641</v>
+        <v>3.353502078501243</v>
       </c>
       <c r="F32" s="4" t="n">
-        <v>3.189057938846069</v>
+        <v>3.202037081244534</v>
       </c>
       <c r="G32" s="4" t="n">
-        <v>2.18115315569878</v>
+        <v>2.194263960073719</v>
       </c>
       <c r="H32" s="4" t="n">
-        <v>3.041975375104577</v>
+        <v>3.055018271398943</v>
       </c>
       <c r="I32" s="4" t="n">
-        <v>4.271795648442634</v>
+        <v>4.28486190274311</v>
       </c>
       <c r="J32" s="4" t="n">
-        <v>4.461889244966294</v>
+        <v>4.475070254261531</v>
       </c>
       <c r="K32" s="4" t="n">
-        <v>4.682579499629071</v>
+        <v>4.695778238583834</v>
       </c>
       <c r="L32" s="4" t="n">
-        <v>4.583628023521328</v>
+        <v>4.597033151174159</v>
       </c>
       <c r="M32" s="4" t="n">
-        <v>4.191081271973701</v>
+        <v>4.204538565683919</v>
       </c>
       <c r="N32" s="4" t="n">
-        <v>5.258328279084388</v>
+        <v>5.271780567804498</v>
       </c>
       <c r="O32" s="4" t="n">
-        <v>5.777040804289726</v>
+        <v>5.790596850641329</v>
       </c>
       <c r="P32" s="4" t="n">
-        <v>5.557278568490887</v>
+        <v>5.546848932792734</v>
       </c>
     </row>
     <row r="33">
@@ -3593,46 +3593,46 @@
         <v>833</v>
       </c>
       <c r="C33" s="4" t="n">
-        <v>3.809082688193385</v>
+        <v>3.821604977869008</v>
       </c>
       <c r="D33" s="4" t="n">
-        <v>4.118277382552058</v>
+        <v>4.13118719212811</v>
       </c>
       <c r="E33" s="4" t="n">
-        <v>4.323648771993888</v>
+        <v>4.33665590341149</v>
       </c>
       <c r="F33" s="4" t="n">
-        <v>5.17419001984748</v>
+        <v>5.187169162245944</v>
       </c>
       <c r="G33" s="4" t="n">
-        <v>4.155576727944577</v>
+        <v>4.168687532319517</v>
       </c>
       <c r="H33" s="4" t="n">
-        <v>5.173306780906344</v>
+        <v>5.18634967720071</v>
       </c>
       <c r="I33" s="4" t="n">
-        <v>6.529149294126256</v>
+        <v>6.542215548426732</v>
       </c>
       <c r="J33" s="4" t="n">
-        <v>5.941917876137076</v>
+        <v>5.955098885432314</v>
       </c>
       <c r="K33" s="4" t="n">
-        <v>6.121014028370141</v>
+        <v>6.134212767324904</v>
       </c>
       <c r="L33" s="4" t="n">
-        <v>6.231272997003678</v>
+        <v>6.24467812465651</v>
       </c>
       <c r="M33" s="4" t="n">
-        <v>5.42627957664768</v>
+        <v>5.439736870357898</v>
       </c>
       <c r="N33" s="4" t="n">
-        <v>7.381431041316041</v>
+        <v>7.394883330036151</v>
       </c>
       <c r="O33" s="4" t="n">
-        <v>7.921560584032598</v>
+        <v>7.935116630384201</v>
       </c>
       <c r="P33" s="4" t="n">
-        <v>8.291329935516572</v>
+        <v>8.28090029981842</v>
       </c>
     </row>
     <row r="34">
@@ -3645,46 +3645,46 @@
         <v>608</v>
       </c>
       <c r="C34" s="4" t="n">
-        <v>2.276298521895292</v>
+        <v>2.288820811570915</v>
       </c>
       <c r="D34" s="4" t="n">
-        <v>3.296303856299453</v>
+        <v>3.309213665875504</v>
       </c>
       <c r="E34" s="4" t="n">
-        <v>4.710645676018643</v>
+        <v>4.723652807436245</v>
       </c>
       <c r="F34" s="4" t="n">
-        <v>4.67642512441563</v>
+        <v>4.689404266814094</v>
       </c>
       <c r="G34" s="4" t="n">
-        <v>4.302477593553974</v>
+        <v>4.315588397928913</v>
       </c>
       <c r="H34" s="4" t="n">
-        <v>5.093340583901217</v>
+        <v>5.106383480195582</v>
       </c>
       <c r="I34" s="4" t="n">
-        <v>5.173080550839472</v>
+        <v>5.186146805139948</v>
       </c>
       <c r="J34" s="4" t="n">
-        <v>4.705897152057972</v>
+        <v>4.71907816135321</v>
       </c>
       <c r="K34" s="4" t="n">
-        <v>5.796213055349355</v>
+        <v>5.809411794304118</v>
       </c>
       <c r="L34" s="4" t="n">
-        <v>5.932929975584578</v>
+        <v>5.946335103237409</v>
       </c>
       <c r="M34" s="4" t="n">
-        <v>4.905808230214369</v>
+        <v>4.919265523924587</v>
       </c>
       <c r="N34" s="4" t="n">
-        <v>7.571770334928225</v>
+        <v>7.585222623648335</v>
       </c>
       <c r="O34" s="4" t="n">
-        <v>8.302831513457015</v>
+        <v>8.316387559808618</v>
       </c>
       <c r="P34" s="4" t="n">
-        <v>8.223605477312248</v>
+        <v>8.213175841614095</v>
       </c>
     </row>
     <row r="35">
@@ -3759,7 +3759,7 @@
     <row r="3" ht="22" customHeight="1">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>Measures the winrate at horizon h days, given that Drawdown-120 is below threshold x, minus the unconditional baseline winrate.</t>
+          <t>Measures the winrate at horizon h, given that Drawdown-120 is below threshold x, minus the unconditional baseline winrate.</t>
         </is>
       </c>
     </row>
@@ -3855,46 +3855,46 @@
         <v>82</v>
       </c>
       <c r="C6" s="4" t="n">
-        <v>4.823634850521728</v>
+        <v>4.836157140197351</v>
       </c>
       <c r="D6" s="4" t="n">
-        <v>3.212061237557471</v>
+        <v>3.224971047133522</v>
       </c>
       <c r="E6" s="4" t="n">
-        <v>4.036704726082831</v>
+        <v>4.049711857500434</v>
       </c>
       <c r="F6" s="4" t="n">
-        <v>9.045006639178141</v>
+        <v>9.057985781576605</v>
       </c>
       <c r="G6" s="4" t="n">
-        <v>12.16512200947183</v>
+        <v>12.17823281384677</v>
       </c>
       <c r="H6" s="4" t="n">
-        <v>11.24305175206554</v>
+        <v>11.25609464835991</v>
       </c>
       <c r="I6" s="4" t="n">
-        <v>8.719293644549353</v>
+        <v>8.732359898849829</v>
       </c>
       <c r="J6" s="4" t="n">
-        <v>11.91064683113371</v>
+        <v>11.92382784042895</v>
       </c>
       <c r="K6" s="4" t="n">
-        <v>11.84964694495141</v>
+        <v>11.86284568390617</v>
       </c>
       <c r="L6" s="4" t="n">
-        <v>14.65805834528933</v>
+        <v>14.67146347294216</v>
       </c>
       <c r="M6" s="4" t="n">
-        <v>14.45330502097175</v>
+        <v>14.46676231468197</v>
       </c>
       <c r="N6" s="4" t="n">
-        <v>13.26817598319522</v>
+        <v>13.28162827191533</v>
       </c>
       <c r="O6" s="4" t="n">
-        <v>15.28694576249423</v>
+        <v>15.30050180884584</v>
       </c>
       <c r="P6" s="4" t="n">
-        <v>15.53666709477052</v>
+        <v>15.52623745907237</v>
       </c>
     </row>
     <row r="7">
@@ -3907,46 +3907,46 @@
         <v>104</v>
       </c>
       <c r="C7" s="4" t="n">
-        <v>3.275792449020798</v>
+        <v>3.288314738696421</v>
       </c>
       <c r="D7" s="4" t="n">
-        <v>0.7026803745180814</v>
+        <v>0.7155901840941326</v>
       </c>
       <c r="E7" s="4" t="n">
-        <v>-1.615265255155435</v>
+        <v>-1.602258123737833</v>
       </c>
       <c r="F7" s="4" t="n">
-        <v>5.245757108221291</v>
+        <v>5.258736250619755</v>
       </c>
       <c r="G7" s="4" t="n">
-        <v>6.630412816226048</v>
+        <v>6.643523620600988</v>
       </c>
       <c r="H7" s="4" t="n">
-        <v>6.927854753941709</v>
+        <v>6.940897650236074</v>
       </c>
       <c r="I7" s="4" t="n">
-        <v>4.920044113592503</v>
+        <v>4.933110367892979</v>
       </c>
       <c r="J7" s="4" t="n">
-        <v>7.337476099426389</v>
+        <v>7.350657108721627</v>
       </c>
       <c r="K7" s="4" t="n">
-        <v>8.238014674782548</v>
+        <v>8.251213413737311</v>
       </c>
       <c r="L7" s="4" t="n">
-        <v>12.19558179744693</v>
+        <v>12.20898692509977</v>
       </c>
       <c r="M7" s="4" t="n">
-        <v>11.99082847312935</v>
+        <v>12.00428576683957</v>
       </c>
       <c r="N7" s="4" t="n">
-        <v>11.06367316893632</v>
+        <v>11.07712545765643</v>
       </c>
       <c r="O7" s="4" t="n">
-        <v>13.5280339426068</v>
+        <v>13.54158998895841</v>
       </c>
       <c r="P7" s="4" t="n">
-        <v>13.77775527488309</v>
+        <v>13.76732563918494</v>
       </c>
     </row>
     <row r="8">
@@ -3959,46 +3959,46 @@
         <v>124</v>
       </c>
       <c r="C8" s="4" t="n">
-        <v>0.7323681314029216</v>
+        <v>0.7448904210785443</v>
       </c>
       <c r="D8" s="4" t="n">
-        <v>-0.07275386865810418</v>
+        <v>-0.05984405908205304</v>
       </c>
       <c r="E8" s="4" t="n">
-        <v>-0.4676225752546941</v>
+        <v>-0.454615443837092</v>
       </c>
       <c r="F8" s="4" t="n">
-        <v>3.694888621868941</v>
+        <v>3.707867764267405</v>
       </c>
       <c r="G8" s="4" t="n">
-        <v>6.382273858409668</v>
+        <v>6.395384662784608</v>
       </c>
       <c r="H8" s="4" t="n">
-        <v>6.679715796125329</v>
+        <v>6.692758692419694</v>
       </c>
       <c r="I8" s="4" t="n">
-        <v>4.982078853046602</v>
+        <v>4.995145107347078</v>
       </c>
       <c r="J8" s="4" t="n">
-        <v>6.12779868007155</v>
+        <v>6.140979689366787</v>
       </c>
       <c r="K8" s="4" t="n">
-        <v>8.486153632598928</v>
+        <v>8.499352371553691</v>
       </c>
       <c r="L8" s="4" t="n">
-        <v>11.66828651208712</v>
+        <v>11.68169163973995</v>
       </c>
       <c r="M8" s="4" t="n">
-        <v>12.26998480067277</v>
+        <v>12.28344209438299</v>
       </c>
       <c r="N8" s="4" t="n">
-        <v>10.69146473221176</v>
+        <v>10.70491702093187</v>
       </c>
       <c r="O8" s="4" t="n">
-        <v>11.07766173417007</v>
+        <v>11.09121778052167</v>
       </c>
       <c r="P8" s="4" t="n">
-        <v>12.13383467934959</v>
+        <v>12.12340504365144</v>
       </c>
     </row>
     <row r="9">
@@ -4011,46 +4011,46 @@
         <v>163</v>
       </c>
       <c r="C9" s="4" t="n">
-        <v>2.721285606170397</v>
+        <v>2.73380789584602</v>
       </c>
       <c r="D9" s="4" t="n">
-        <v>-0.1172818718245381</v>
+        <v>-0.1043720622484869</v>
       </c>
       <c r="E9" s="4" t="n">
-        <v>2.555334084155561</v>
+        <v>2.568341215573163</v>
       </c>
       <c r="F9" s="4" t="n">
-        <v>4.526078014309071</v>
+        <v>4.539057156707536</v>
       </c>
       <c r="G9" s="4" t="n">
-        <v>8.282135326844262</v>
+        <v>8.295246131219201</v>
       </c>
       <c r="H9" s="4" t="n">
-        <v>9.193074197075262</v>
+        <v>9.206117093369627</v>
       </c>
       <c r="I9" s="4" t="n">
-        <v>7.881346614772312</v>
+        <v>7.894412869072788</v>
       </c>
       <c r="J9" s="4" t="n">
-        <v>8.027660148506143</v>
+        <v>8.040841157801381</v>
       </c>
       <c r="K9" s="4" t="n">
-        <v>11.03414492490052</v>
+        <v>11.04734366385529</v>
       </c>
       <c r="L9" s="4" t="n">
-        <v>14.47849826747996</v>
+        <v>14.49190339513279</v>
       </c>
       <c r="M9" s="4" t="n">
-        <v>14.88724187567772</v>
+        <v>14.90069916938793</v>
       </c>
       <c r="N9" s="4" t="n">
-        <v>13.08113423547714</v>
+        <v>13.09458652419725</v>
       </c>
       <c r="O9" s="4" t="n">
-        <v>14.50137042207825</v>
+        <v>14.51492646842985</v>
       </c>
       <c r="P9" s="4" t="n">
-        <v>15.36458868686988</v>
+        <v>15.35415905117173</v>
       </c>
     </row>
     <row r="10">
@@ -4063,46 +4063,46 @@
         <v>219</v>
       </c>
       <c r="C10" s="4" t="n">
-        <v>4.127566246000065</v>
+        <v>4.140088535675687</v>
       </c>
       <c r="D10" s="4" t="n">
-        <v>0.232887610204763</v>
+        <v>0.2457974197808142</v>
       </c>
       <c r="E10" s="4" t="n">
-        <v>3.94760794470406</v>
+        <v>3.960615076121663</v>
       </c>
       <c r="F10" s="4" t="n">
-        <v>6.360966100142619</v>
+        <v>6.373945242541083</v>
       </c>
       <c r="G10" s="4" t="n">
-        <v>7.649028903335285</v>
+        <v>7.662139707710224</v>
       </c>
       <c r="H10" s="4" t="n">
-        <v>6.11998682278611</v>
+        <v>6.133029719080476</v>
       </c>
       <c r="I10" s="4" t="n">
-        <v>7.405116119212451</v>
+        <v>7.418182373512927</v>
       </c>
       <c r="J10" s="4" t="n">
-        <v>5.568069706732331</v>
+        <v>5.581250716027569</v>
       </c>
       <c r="K10" s="4" t="n">
-        <v>7.790174843381074</v>
+        <v>7.803373582335837</v>
       </c>
       <c r="L10" s="4" t="n">
-        <v>11.04963869944903</v>
+        <v>11.06304382710186</v>
       </c>
       <c r="M10" s="4" t="n">
-        <v>12.21474838883009</v>
+        <v>12.22820568254031</v>
       </c>
       <c r="N10" s="4" t="n">
-        <v>9.966026523344468</v>
+        <v>9.979478812064578</v>
       </c>
       <c r="O10" s="4" t="n">
-        <v>10.9156349260982</v>
+        <v>10.9291909724498</v>
       </c>
       <c r="P10" s="4" t="n">
-        <v>10.70873525380827</v>
+        <v>10.69830561811012</v>
       </c>
     </row>
     <row r="11">
@@ -4115,46 +4115,46 @@
         <v>279</v>
       </c>
       <c r="C11" s="4" t="n">
-        <v>3.420540174413674</v>
+        <v>3.433062464089296</v>
       </c>
       <c r="D11" s="4" t="n">
-        <v>0.01685186610892231</v>
+        <v>0.02976167568497345</v>
       </c>
       <c r="E11" s="4" t="n">
-        <v>0.697251976716629</v>
+        <v>0.7102591081342311</v>
       </c>
       <c r="F11" s="4" t="n">
-        <v>1.902773926528432</v>
+        <v>1.915753068926897</v>
       </c>
       <c r="G11" s="4" t="n">
-        <v>4.948582102137266</v>
+        <v>4.961692906512205</v>
       </c>
       <c r="H11" s="4" t="n">
-        <v>3.453909344512432</v>
+        <v>3.466952240806798</v>
       </c>
       <c r="I11" s="4" t="n">
-        <v>3.369175627240153</v>
+        <v>3.382241881540629</v>
       </c>
       <c r="J11" s="4" t="n">
-        <v>1.109877533118144</v>
+        <v>1.123058542413382</v>
       </c>
       <c r="K11" s="4" t="n">
-        <v>3.916261159480648</v>
+        <v>3.929459898435411</v>
       </c>
       <c r="L11" s="4" t="n">
-        <v>4.858250669793222</v>
+        <v>4.871655797446053</v>
       </c>
       <c r="M11" s="4" t="n">
-        <v>6.087189101748045</v>
+        <v>6.100646395458263</v>
       </c>
       <c r="N11" s="4" t="n">
-        <v>4.329457563752982</v>
+        <v>4.342909852473092</v>
       </c>
       <c r="O11" s="4" t="n">
-        <v>4.626048830944271</v>
+        <v>4.639604877295874</v>
       </c>
       <c r="P11" s="4" t="n">
-        <v>4.517347224152459</v>
+        <v>4.506917588454307</v>
       </c>
     </row>
     <row r="12">
@@ -4167,46 +4167,46 @@
         <v>343</v>
       </c>
       <c r="C12" s="4" t="n">
-        <v>2.317057306612178</v>
+        <v>2.3295795962878</v>
       </c>
       <c r="D12" s="4" t="n">
-        <v>-0.169151874865193</v>
+        <v>-0.1562420652891419</v>
       </c>
       <c r="E12" s="4" t="n">
-        <v>-0.8555657709661588</v>
+        <v>-0.8425586395485567</v>
       </c>
       <c r="F12" s="4" t="n">
-        <v>1.023958498667589</v>
+        <v>1.036937641066054</v>
       </c>
       <c r="G12" s="4" t="n">
-        <v>2.817898799630406</v>
+        <v>2.831009604005345</v>
       </c>
       <c r="H12" s="4" t="n">
-        <v>1.949159979328563</v>
+        <v>1.962202875622928</v>
       </c>
       <c r="I12" s="4" t="n">
-        <v>1.864426262056284</v>
+        <v>1.87749251635676</v>
       </c>
       <c r="J12" s="4" t="n">
-        <v>0.2310621052573012</v>
+        <v>0.244243114552539</v>
       </c>
       <c r="K12" s="4" t="n">
-        <v>3.085514114118723</v>
+        <v>3.098712853073486</v>
       </c>
       <c r="L12" s="4" t="n">
-        <v>3.110024497603916</v>
+        <v>3.123429625256747</v>
       </c>
       <c r="M12" s="4" t="n">
-        <v>3.488361552295082</v>
+        <v>3.5018188460053</v>
       </c>
       <c r="N12" s="4" t="n">
-        <v>1.48192838310991</v>
+        <v>1.49538067183002</v>
       </c>
       <c r="O12" s="4" t="n">
-        <v>0.7701285826606252</v>
+        <v>0.7836846290122281</v>
       </c>
       <c r="P12" s="4" t="n">
-        <v>1.311395104441296</v>
+        <v>1.300965468743144</v>
       </c>
     </row>
     <row r="13">
@@ -4219,46 +4219,46 @@
         <v>400</v>
       </c>
       <c r="C13" s="4" t="n">
-        <v>1.256561679790025</v>
+        <v>1.269083969465647</v>
       </c>
       <c r="D13" s="4" t="n">
-        <v>-0.8550119331742323</v>
+        <v>-0.8421021235981812</v>
       </c>
       <c r="E13" s="4" t="n">
-        <v>-0.2498806397708222</v>
+        <v>-0.2368735083532201</v>
       </c>
       <c r="F13" s="4" t="n">
-        <v>0.8803724928366776</v>
+        <v>0.8933516352351418</v>
       </c>
       <c r="G13" s="4" t="n">
-        <v>1.341951277764508</v>
+        <v>1.355062082139447</v>
       </c>
       <c r="H13" s="4" t="n">
-        <v>0.1393932154801689</v>
+        <v>0.1524361117745343</v>
       </c>
       <c r="I13" s="4" t="n">
-        <v>-0.4453405017921099</v>
+        <v>-0.4322742474916339</v>
       </c>
       <c r="J13" s="4" t="n">
-        <v>-3.412523900573618</v>
+        <v>-3.39934289127838</v>
       </c>
       <c r="K13" s="4" t="n">
-        <v>-0.723523786755905</v>
+        <v>-0.7103250478011418</v>
       </c>
       <c r="L13" s="4" t="n">
-        <v>-0.8236489717838396</v>
+        <v>-0.8102438441310085</v>
       </c>
       <c r="M13" s="4" t="n">
-        <v>-0.5284022961014188</v>
+        <v>-0.514945002391201</v>
       </c>
       <c r="N13" s="4" t="n">
-        <v>-1.244019138755981</v>
+        <v>-1.230566850035871</v>
       </c>
       <c r="O13" s="4" t="n">
-        <v>-1.914273749700889</v>
+        <v>-1.900717703349287</v>
       </c>
       <c r="P13" s="4" t="n">
-        <v>-1.664552417424602</v>
+        <v>-1.674982053122754</v>
       </c>
     </row>
     <row r="14">
@@ -4271,46 +4271,46 @@
         <v>478</v>
       </c>
       <c r="C14" s="4" t="n">
-        <v>0.8538420145180581</v>
+        <v>0.8663643041936808</v>
       </c>
       <c r="D14" s="4" t="n">
-        <v>-1.385346661207699</v>
+        <v>-1.372436851631647</v>
       </c>
       <c r="E14" s="4" t="n">
-        <v>-0.3157802213607823</v>
+        <v>-0.3027730899431802</v>
       </c>
       <c r="F14" s="4" t="n">
-        <v>0.2328829530877172</v>
+        <v>0.2458620954861814</v>
       </c>
       <c r="G14" s="4" t="n">
-        <v>-0.3055382619844522</v>
+        <v>-0.2924274576095129</v>
       </c>
       <c r="H14" s="4" t="n">
-        <v>-1.263326449791798</v>
+        <v>-1.250283553497432</v>
       </c>
       <c r="I14" s="4" t="n">
-        <v>-1.138855146143577</v>
+        <v>-1.125788891843101</v>
       </c>
       <c r="J14" s="4" t="n">
-        <v>-3.907293775050597</v>
+        <v>-3.894112765755359</v>
       </c>
       <c r="K14" s="4" t="n">
-        <v>-1.248628389266372</v>
+        <v>-1.235429650311609</v>
       </c>
       <c r="L14" s="4" t="n">
-        <v>-1.052728469691786</v>
+        <v>-1.039323342038955</v>
       </c>
       <c r="M14" s="4" t="n">
-        <v>-0.2114566894068588</v>
+        <v>-0.197999395696641</v>
       </c>
       <c r="N14" s="4" t="n">
-        <v>-0.5954835739024347</v>
+        <v>-0.5820312851823246</v>
       </c>
       <c r="O14" s="4" t="n">
-        <v>-1.852558268529336</v>
+        <v>-1.839002222177733</v>
       </c>
       <c r="P14" s="4" t="n">
-        <v>-2.439657019935062</v>
+        <v>-2.450086655633214</v>
       </c>
     </row>
     <row r="15">
@@ -4323,46 +4323,46 @@
         <v>560</v>
       </c>
       <c r="C15" s="4" t="n">
-        <v>0.7208473940757401</v>
+        <v>0.7333696837513628</v>
       </c>
       <c r="D15" s="4" t="n">
-        <v>-1.247869076031371</v>
+        <v>-1.23495926645532</v>
       </c>
       <c r="E15" s="4" t="n">
-        <v>-0.3927377826279681</v>
+        <v>-0.379730651210366</v>
       </c>
       <c r="F15" s="4" t="n">
-        <v>0.4518010642652541</v>
+        <v>0.4647802066637183</v>
       </c>
       <c r="G15" s="4" t="n">
-        <v>-0.265191579378353</v>
+        <v>-0.2520807750034137</v>
       </c>
       <c r="H15" s="4" t="n">
-        <v>-0.503463927376977</v>
+        <v>-0.4904210310826116</v>
       </c>
       <c r="I15" s="4" t="n">
-        <v>-0.9453405017921099</v>
+        <v>-0.9322742474916339</v>
       </c>
       <c r="J15" s="4" t="n">
-        <v>-2.841095329145034</v>
+        <v>-2.827914319849796</v>
       </c>
       <c r="K15" s="4" t="n">
-        <v>-0.9378095010416274</v>
+        <v>-0.9246107620868642</v>
       </c>
       <c r="L15" s="4" t="n">
-        <v>-1.609363257498131</v>
+        <v>-1.5959581298453</v>
       </c>
       <c r="M15" s="4" t="n">
-        <v>-0.3855451532442729</v>
+        <v>-0.3720878595340551</v>
       </c>
       <c r="N15" s="4" t="n">
-        <v>-1.244019138755981</v>
+        <v>-1.230566850035871</v>
       </c>
       <c r="O15" s="4" t="n">
-        <v>-3.449988035415174</v>
+        <v>-3.436431989063571</v>
       </c>
       <c r="P15" s="4" t="n">
-        <v>-3.735980988853171</v>
+        <v>-3.746410624551324</v>
       </c>
     </row>
     <row r="16">
@@ -4375,98 +4375,98 @@
         <v>649</v>
       </c>
       <c r="C16" s="4" t="n">
-        <v>-0.1051486437847018</v>
+        <v>-0.09262635410907905</v>
       </c>
       <c r="D16" s="4" t="n">
-        <v>-2.487138281402274</v>
+        <v>-2.474228471826223</v>
       </c>
       <c r="E16" s="4" t="n">
-        <v>-1.957507758414884</v>
+        <v>-1.944500626997282</v>
       </c>
       <c r="F16" s="4" t="n">
-        <v>-1.673171420876734</v>
+        <v>-1.66019227847827</v>
       </c>
       <c r="G16" s="4" t="n">
-        <v>-2.057509431018232</v>
+        <v>-2.044398626643293</v>
       </c>
       <c r="H16" s="4" t="n">
-        <v>-2.222317108094558</v>
+        <v>-2.209274211800192</v>
       </c>
       <c r="I16" s="4" t="n">
-        <v>-3.231550054950816</v>
+        <v>-3.21848380065034</v>
       </c>
       <c r="J16" s="4" t="n">
-        <v>-4.160983068524303</v>
+        <v>-4.147802059229065</v>
       </c>
       <c r="K16" s="4" t="n">
-        <v>-2.372984495538653</v>
+        <v>-2.359785756583889</v>
       </c>
       <c r="L16" s="4" t="n">
-        <v>-2.914943270705258</v>
+        <v>-2.901538143052427</v>
       </c>
       <c r="M16" s="4" t="n">
-        <v>-2.349280570369523</v>
+        <v>-2.335823276659305</v>
       </c>
       <c r="N16" s="4" t="n">
-        <v>-3.239396642608064</v>
+        <v>-3.225944353887954</v>
       </c>
       <c r="O16" s="4" t="n">
-        <v>-4.275984073275616</v>
+        <v>-4.262428026924013</v>
       </c>
       <c r="P16" s="4" t="n">
-        <v>-4.33442915086065</v>
+        <v>-4.344858786558802</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>X &lt; -0.3368</t>
+          <t>X &lt; -0.3367</t>
         </is>
       </c>
       <c r="B17" t="n">
         <v>717</v>
       </c>
       <c r="C17" s="4" t="n">
-        <v>-1.16847318771346</v>
+        <v>-1.155950898037837</v>
       </c>
       <c r="D17" s="4" t="n">
-        <v>-3.756336898306728</v>
+        <v>-3.743427088730677</v>
       </c>
       <c r="E17" s="4" t="n">
-        <v>-3.732795563062318</v>
+        <v>-3.719788431644716</v>
       </c>
       <c r="F17" s="4" t="n">
-        <v>-2.905192360719809</v>
+        <v>-2.892213218321345</v>
       </c>
       <c r="G17" s="4" t="n">
-        <v>-2.606793492109972</v>
+        <v>-2.593682687735033</v>
       </c>
       <c r="H17" s="4" t="n">
-        <v>-3.285641652023315</v>
+        <v>-3.27259875572895</v>
       </c>
       <c r="I17" s="4" t="n">
-        <v>-3.788785411136594</v>
+        <v>-3.775719156836118</v>
       </c>
       <c r="J17" s="4" t="n">
-        <v>-4.813848865706106</v>
+        <v>-4.800667856410868</v>
       </c>
       <c r="K17" s="4" t="n">
-        <v>-3.06173857057739</v>
+        <v>-3.048539831622627</v>
       </c>
       <c r="L17" s="4" t="n">
-        <v>-4.330273797446324</v>
+        <v>-4.316868669793493</v>
       </c>
       <c r="M17" s="4" t="n">
-        <v>-3.419267010187895</v>
+        <v>-3.405809716477677</v>
       </c>
       <c r="N17" s="4" t="n">
-        <v>-4.500643964418472</v>
+        <v>-4.487191675698362</v>
       </c>
       <c r="O17" s="4" t="n">
-        <v>-5.199838603257376</v>
+        <v>-5.186282556905773</v>
       </c>
       <c r="P17" s="4" t="n">
-        <v>-5.229057298875098</v>
+        <v>-5.23948693457325</v>
       </c>
     </row>
     <row r="18">
@@ -4479,46 +4479,46 @@
         <v>777</v>
       </c>
       <c r="C18" s="4" t="n">
-        <v>-1.656887483659148</v>
+        <v>-1.644365193983525</v>
       </c>
       <c r="D18" s="4" t="n">
-        <v>-3.911961740124042</v>
+        <v>-3.899051930547991</v>
       </c>
       <c r="E18" s="4" t="n">
-        <v>-3.663329803219995</v>
+        <v>-3.650322671802392</v>
       </c>
       <c r="F18" s="4" t="n">
-        <v>-2.889576027111843</v>
+        <v>-2.876596884713379</v>
       </c>
       <c r="G18" s="4" t="n">
-        <v>-2.655796469983244</v>
+        <v>-2.642685665608305</v>
       </c>
       <c r="H18" s="4" t="n">
-        <v>-3.259255433168484</v>
+        <v>-3.246212536874118</v>
       </c>
       <c r="I18" s="4" t="n">
-        <v>-3.47268927914088</v>
+        <v>-3.459623024840404</v>
       </c>
       <c r="J18" s="4" t="n">
-        <v>-4.197272935322644</v>
+        <v>-4.184091926027406</v>
       </c>
       <c r="K18" s="4" t="n">
-        <v>-2.713871277103408</v>
+        <v>-2.700672538148645</v>
       </c>
       <c r="L18" s="4" t="n">
-        <v>-3.17789607603094</v>
+        <v>-3.164490948378109</v>
       </c>
       <c r="M18" s="4" t="n">
-        <v>-2.739148756847882</v>
+        <v>-2.725691463137665</v>
       </c>
       <c r="N18" s="4" t="n">
-        <v>-3.734366629103484</v>
+        <v>-3.720914340383374</v>
       </c>
       <c r="O18" s="4" t="n">
-        <v>-4.412021497448642</v>
+        <v>-4.398465451097039</v>
       </c>
       <c r="P18" s="4" t="n">
-        <v>-4.419700422572603</v>
+        <v>-4.430130058270755</v>
       </c>
     </row>
     <row r="19">
@@ -4531,46 +4531,46 @@
         <v>857</v>
       </c>
       <c r="C19" s="4" t="n">
-        <v>-0.9181757764526779</v>
+        <v>-0.9056534867770552</v>
       </c>
       <c r="D19" s="4" t="n">
-        <v>-2.87980773247412</v>
+        <v>-2.866897922898069</v>
       </c>
       <c r="E19" s="4" t="n">
-        <v>-2.807931981661135</v>
+        <v>-2.794924850243532</v>
       </c>
       <c r="F19" s="4" t="n">
-        <v>-2.327620505996464</v>
+        <v>-2.314641363598</v>
       </c>
       <c r="G19" s="4" t="n">
-        <v>-1.815866691897106</v>
+        <v>-1.802755887522167</v>
       </c>
       <c r="H19" s="4" t="n">
-        <v>-2.568599783352973</v>
+        <v>-2.555556887058607</v>
       </c>
       <c r="I19" s="4" t="n">
-        <v>-2.653333500625251</v>
+        <v>-2.640267246324775</v>
       </c>
       <c r="J19" s="4" t="n">
-        <v>-3.353889128111533</v>
+        <v>-3.340708118816295</v>
       </c>
       <c r="K19" s="4" t="n">
-        <v>-1.547911184655561</v>
+        <v>-1.534712445700798</v>
       </c>
       <c r="L19" s="4" t="n">
-        <v>-2.281350255331091</v>
+        <v>-2.26794512767826</v>
       </c>
       <c r="M19" s="4" t="n">
-        <v>-1.785986893534321</v>
+        <v>-1.772529599824104</v>
       </c>
       <c r="N19" s="4" t="n">
-        <v>-2.218348193598466</v>
+        <v>-2.204895904878356</v>
       </c>
       <c r="O19" s="4" t="n">
-        <v>-2.988661147600538</v>
+        <v>-2.975105101248936</v>
       </c>
       <c r="P19" s="4" t="n">
-        <v>-3.088998158381429</v>
+        <v>-3.099427794079581</v>
       </c>
     </row>
     <row r="20">
@@ -4583,46 +4583,46 @@
         <v>939</v>
       </c>
       <c r="C20" s="4" t="n">
-        <v>-1.375227457590171</v>
+        <v>-1.362705167914548</v>
       </c>
       <c r="D20" s="4" t="n">
-        <v>-3.093297343184879</v>
+        <v>-3.080387533608828</v>
       </c>
       <c r="E20" s="4" t="n">
-        <v>-2.742692141368273</v>
+        <v>-2.729685009950671</v>
       </c>
       <c r="F20" s="4" t="n">
-        <v>-2.186453918238932</v>
+        <v>-2.173474775840468</v>
       </c>
       <c r="G20" s="4" t="n">
-        <v>-2.085897497528357</v>
+        <v>-2.072786693153418</v>
       </c>
       <c r="H20" s="4" t="n">
-        <v>-2.853418286117282</v>
+        <v>-2.840375389822917</v>
       </c>
       <c r="I20" s="4" t="n">
-        <v>-3.577129639172306</v>
+        <v>-3.564063384871829</v>
       </c>
       <c r="J20" s="4" t="n">
-        <v>-4.150809310584258</v>
+        <v>-4.13762830128902</v>
       </c>
       <c r="K20" s="4" t="n">
-        <v>-2.720861379940153</v>
+        <v>-2.70766264098539</v>
       </c>
       <c r="L20" s="4" t="n">
-        <v>-3.145001474446254</v>
+        <v>-3.131596346793422</v>
       </c>
       <c r="M20" s="4" t="n">
-        <v>-2.391288345089706</v>
+        <v>-2.377831051379488</v>
       </c>
       <c r="N20" s="4" t="n">
-        <v>-2.782890278266109</v>
+        <v>-2.769437989545999</v>
       </c>
       <c r="O20" s="4" t="n">
-        <v>-3.416137434471921</v>
+        <v>-3.402581388120318</v>
       </c>
       <c r="P20" s="4" t="n">
-        <v>-3.37940864745655</v>
+        <v>-3.389838283154702</v>
       </c>
     </row>
     <row r="21">
@@ -4635,46 +4635,46 @@
         <v>1031</v>
       </c>
       <c r="C21" s="4" t="n">
-        <v>-0.6020707159422756</v>
+        <v>-0.5895484262666528</v>
       </c>
       <c r="D21" s="4" t="n">
-        <v>-2.310637539381801</v>
+        <v>-2.29772772980575</v>
       </c>
       <c r="E21" s="4" t="n">
-        <v>-1.735574141225726</v>
+        <v>-1.722567009808124</v>
       </c>
       <c r="F21" s="4" t="n">
-        <v>-1.411334587667689</v>
+        <v>-1.398355445269225</v>
       </c>
       <c r="G21" s="4" t="n">
-        <v>-1.85276259226459</v>
+        <v>-1.83965178788965</v>
       </c>
       <c r="H21" s="4" t="n">
-        <v>-2.622245969776856</v>
+        <v>-2.60920307348249</v>
       </c>
       <c r="I21" s="4" t="n">
-        <v>-3.482925370851277</v>
+        <v>-3.469859116550801</v>
       </c>
       <c r="J21" s="4" t="n">
-        <v>-4.241088401058576</v>
+        <v>-4.227907391763338</v>
       </c>
       <c r="K21" s="4" t="n">
-        <v>-3.041176551062406</v>
+        <v>-3.027977812107643</v>
       </c>
       <c r="L21" s="4" t="n">
-        <v>-3.503328894189274</v>
+        <v>-3.489923766536442</v>
       </c>
       <c r="M21" s="4" t="n">
-        <v>-2.932136534704711</v>
+        <v>-2.918679240994493</v>
       </c>
       <c r="N21" s="4" t="n">
-        <v>-3.091739798309817</v>
+        <v>-3.078287509589707</v>
       </c>
       <c r="O21" s="4" t="n">
-        <v>-3.996960461631048</v>
+        <v>-3.983404415279445</v>
       </c>
       <c r="P21" s="4" t="n">
-        <v>-4.038218760780566</v>
+        <v>-4.048648396478718</v>
       </c>
     </row>
     <row r="22">
@@ -4684,49 +4684,49 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>1183</v>
+        <v>1184</v>
       </c>
       <c r="C22" s="4" t="n">
-        <v>-0.63533021210187</v>
+        <v>-0.6228079224262473</v>
       </c>
       <c r="D22" s="4" t="n">
-        <v>-1.824606527768829</v>
+        <v>-1.811696718192778</v>
       </c>
       <c r="E22" s="4" t="n">
-        <v>-1.20596172085191</v>
+        <v>-1.192954589434308</v>
       </c>
       <c r="F22" s="4" t="n">
-        <v>-0.06219507473088726</v>
+        <v>-0.04921593233242305</v>
       </c>
       <c r="G22" s="4" t="n">
-        <v>-0.5161568303435971</v>
+        <v>-0.5030460259686578</v>
       </c>
       <c r="H22" s="4" t="n">
-        <v>-1.147768946681992</v>
+        <v>-1.134726050387627</v>
       </c>
       <c r="I22" s="4" t="n">
-        <v>-1.48588104233265</v>
+        <v>-1.472814788032174</v>
       </c>
       <c r="J22" s="4" t="n">
-        <v>-2.206442819492523</v>
+        <v>-2.193261810197285</v>
       </c>
       <c r="K22" s="4" t="n">
-        <v>-1.253929192161316</v>
+        <v>-1.240730453206552</v>
       </c>
       <c r="L22" s="4" t="n">
-        <v>-2.019594917729783</v>
+        <v>-2.006189790076952</v>
       </c>
       <c r="M22" s="4" t="n">
-        <v>-1.210834728533854</v>
+        <v>-1.197377434823636</v>
       </c>
       <c r="N22" s="4" t="n">
-        <v>-1.598748868485714</v>
+        <v>-1.585296579765604</v>
       </c>
       <c r="O22" s="4" t="n">
-        <v>-2.441300776727921</v>
+        <v>-2.427744730376318</v>
       </c>
       <c r="P22" s="4" t="n">
-        <v>-2.230275156224259</v>
+        <v>-2.202009080149786</v>
       </c>
     </row>
     <row r="23">
@@ -4736,49 +4736,49 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>1315</v>
+        <v>1316</v>
       </c>
       <c r="C23" s="4" t="n">
-        <v>-0.3359818478405643</v>
+        <v>-0.362913004815745</v>
       </c>
       <c r="D23" s="4" t="n">
-        <v>-1.41765387110005</v>
+        <v>-1.404744061523999</v>
       </c>
       <c r="E23" s="4" t="n">
-        <v>-1.545335185225369</v>
+        <v>-1.572414764976998</v>
       </c>
       <c r="F23" s="4" t="n">
-        <v>-0.4302335677693776</v>
+        <v>-0.4172544253709134</v>
       </c>
       <c r="G23" s="4" t="n">
-        <v>-0.9277606251922776</v>
+        <v>-0.9555439784666078</v>
       </c>
       <c r="H23" s="4" t="n">
-        <v>-1.423960350528937</v>
+        <v>-1.451240916277023</v>
       </c>
       <c r="I23" s="4" t="n">
-        <v>-1.660439136086502</v>
+        <v>-1.647372881786026</v>
       </c>
       <c r="J23" s="4" t="n">
-        <v>-2.355240137295922</v>
+        <v>-2.342059128000685</v>
       </c>
       <c r="K23" s="4" t="n">
-        <v>-1.354024545481259</v>
+        <v>-1.340825806526496</v>
       </c>
       <c r="L23" s="4" t="n">
-        <v>-2.355894798794466</v>
+        <v>-2.342489671141635</v>
       </c>
       <c r="M23" s="4" t="n">
-        <v>-1.80192278168564</v>
+        <v>-1.788465487975422</v>
       </c>
       <c r="N23" s="4" t="n">
-        <v>-2.029896131922271</v>
+        <v>-2.057577472190665</v>
       </c>
       <c r="O23" s="4" t="n">
-        <v>-2.788893810491167</v>
+        <v>-2.816245417851938</v>
       </c>
       <c r="P23" s="4" t="n">
-        <v>-2.574248234915103</v>
+        <v>-2.549602113913032</v>
       </c>
     </row>
     <row r="24">
@@ -4788,49 +4788,49 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>1486</v>
+        <v>1487</v>
       </c>
       <c r="C24" s="4" t="n">
-        <v>-0.5549356464131847</v>
+        <v>-0.577108415303897</v>
       </c>
       <c r="D24" s="4" t="n">
-        <v>-0.6601958796625311</v>
+        <v>-0.6830112145072746</v>
       </c>
       <c r="E24" s="4" t="n">
-        <v>-0.4838163827427024</v>
+        <v>-0.5069403979853249</v>
       </c>
       <c r="F24" s="4" t="n">
-        <v>0.4193878980610606</v>
+        <v>0.3956943393850807</v>
       </c>
       <c r="G24" s="4" t="n">
-        <v>-0.1493355855062717</v>
+        <v>-0.1729017490728708</v>
       </c>
       <c r="H24" s="4" t="n">
-        <v>-0.2846510501133892</v>
+        <v>-0.3080196523005299</v>
       </c>
       <c r="I24" s="4" t="n">
-        <v>-0.802723052127682</v>
+        <v>-0.8258020811603046</v>
       </c>
       <c r="J24" s="4" t="n">
-        <v>-1.337020544868913</v>
+        <v>-1.323839535573676</v>
       </c>
       <c r="K24" s="4" t="n">
-        <v>-0.6597653974941693</v>
+        <v>-0.6465666585394061</v>
       </c>
       <c r="L24" s="4" t="n">
-        <v>-1.308548300642897</v>
+        <v>-1.295143172990066</v>
       </c>
       <c r="M24" s="4" t="n">
-        <v>-0.8049301671558169</v>
+        <v>-0.8287033916529438</v>
       </c>
       <c r="N24" s="4" t="n">
-        <v>-1.338105160261364</v>
+        <v>-1.361527226127208</v>
       </c>
       <c r="O24" s="4" t="n">
-        <v>-1.654186325356569</v>
+        <v>-1.677599423779398</v>
       </c>
       <c r="P24" s="4" t="n">
-        <v>-1.434740842727436</v>
+        <v>-1.414894628778434</v>
       </c>
     </row>
     <row r="25">
@@ -4840,49 +4840,49 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>1653</v>
+        <v>1654</v>
       </c>
       <c r="C25" s="4" t="n">
-        <v>-0.6326940224908881</v>
+        <v>-0.6512819573489921</v>
       </c>
       <c r="D25" s="4" t="n">
-        <v>-1.071978900141204</v>
+        <v>-1.090901643406099</v>
       </c>
       <c r="E25" s="4" t="n">
-        <v>-0.6537267936169755</v>
+        <v>-0.6730596945394041</v>
       </c>
       <c r="F25" s="4" t="n">
-        <v>0.1703604663784688</v>
+        <v>0.1505631736966819</v>
       </c>
       <c r="G25" s="4" t="n">
-        <v>-0.09457098457003354</v>
+        <v>-0.1144207801576087</v>
       </c>
       <c r="H25" s="4" t="n">
-        <v>-0.4865851108292816</v>
+        <v>-0.506107811209823</v>
       </c>
       <c r="I25" s="4" t="n">
-        <v>-1.080882670466806</v>
+        <v>-1.100094837497657</v>
       </c>
       <c r="J25" s="4" t="n">
-        <v>-0.9732532556067639</v>
+        <v>-0.9927163852542762</v>
       </c>
       <c r="K25" s="4" t="n">
-        <v>-0.2174924236678564</v>
+        <v>-0.2374498217613663</v>
       </c>
       <c r="L25" s="4" t="n">
-        <v>-0.7326713012950066</v>
+        <v>-0.752644326640052</v>
       </c>
       <c r="M25" s="4" t="n">
-        <v>-0.3605278999661508</v>
+        <v>-0.3808170603272316</v>
       </c>
       <c r="N25" s="4" t="n">
-        <v>-0.8361641538617306</v>
+        <v>-0.8561707147701725</v>
       </c>
       <c r="O25" s="4" t="n">
-        <v>-1.404297933497745</v>
+        <v>-1.424131600630254</v>
       </c>
       <c r="P25" s="4" t="n">
-        <v>-1.423626827587945</v>
+        <v>-1.406844205480674</v>
       </c>
     </row>
     <row r="26">
@@ -4892,49 +4892,49 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>1806</v>
+        <v>1807</v>
       </c>
       <c r="C26" s="4" t="n">
-        <v>-1.03659390019898</v>
+        <v>-1.052344601962929</v>
       </c>
       <c r="D26" s="4" t="n">
-        <v>-1.299731405121435</v>
+        <v>-1.315851436407421</v>
       </c>
       <c r="E26" s="4" t="n">
-        <v>-1.11518058473505</v>
+        <v>-1.131537974799862</v>
       </c>
       <c r="F26" s="4" t="n">
-        <v>-0.5150019565025303</v>
+        <v>-0.5316621237081733</v>
       </c>
       <c r="G26" s="4" t="n">
-        <v>-0.6380762704448557</v>
+        <v>-0.6548498121336834</v>
       </c>
       <c r="H26" s="4" t="n">
-        <v>-1.192745704034714</v>
+        <v>-1.209134136159349</v>
       </c>
       <c r="I26" s="4" t="n">
-        <v>-1.799587606039211</v>
+        <v>-1.815681083213789</v>
       </c>
       <c r="J26" s="4" t="n">
-        <v>-1.575327432582441</v>
+        <v>-1.591703619353389</v>
       </c>
       <c r="K26" s="4" t="n">
-        <v>-0.9441201423605463</v>
+        <v>-0.9608769241808375</v>
       </c>
       <c r="L26" s="4" t="n">
-        <v>-1.37751637509875</v>
+        <v>-1.394313418951555</v>
       </c>
       <c r="M26" s="4" t="n">
-        <v>-1.054521699086493</v>
+        <v>-1.07157483664534</v>
       </c>
       <c r="N26" s="4" t="n">
-        <v>-1.487381970614393</v>
+        <v>-1.504198690831906</v>
       </c>
       <c r="O26" s="4" t="n">
-        <v>-1.877334070674877</v>
+        <v>-1.894080535207692</v>
       </c>
       <c r="P26" s="4" t="n">
-        <v>-2.040244554744639</v>
+        <v>-2.025424775867634</v>
       </c>
     </row>
     <row r="27">
@@ -4944,49 +4944,49 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>1972</v>
+        <v>1973</v>
       </c>
       <c r="C27" s="4" t="n">
-        <v>-0.8057808894794931</v>
+        <v>-0.8192846105947709</v>
       </c>
       <c r="D27" s="4" t="n">
-        <v>-1.433640965432296</v>
+        <v>-1.447265851557873</v>
       </c>
       <c r="E27" s="4" t="n">
-        <v>-1.247233135988672</v>
+        <v>-1.261067056740323</v>
       </c>
       <c r="F27" s="4" t="n">
-        <v>-0.3333005646809823</v>
+        <v>-0.3475712089403586</v>
       </c>
       <c r="G27" s="4" t="n">
-        <v>-0.2891693683738126</v>
+        <v>-0.3036160207868903</v>
       </c>
       <c r="H27" s="4" t="n">
-        <v>-0.7217178956309453</v>
+        <v>-0.7358778710624208</v>
       </c>
       <c r="I27" s="4" t="n">
-        <v>-1.284526959599084</v>
+        <v>-1.298435863653246</v>
       </c>
       <c r="J27" s="4" t="n">
-        <v>-1.421371221099399</v>
+        <v>-1.435345923112628</v>
       </c>
       <c r="K27" s="4" t="n">
-        <v>-1.101116098339119</v>
+        <v>-1.115279547295593</v>
       </c>
       <c r="L27" s="4" t="n">
-        <v>-1.569600388787883</v>
+        <v>-1.58376432971523</v>
       </c>
       <c r="M27" s="4" t="n">
-        <v>-1.24042761255712</v>
+        <v>-1.254823544901321</v>
       </c>
       <c r="N27" s="4" t="n">
-        <v>-1.532772938148085</v>
+        <v>-1.547022546238409</v>
       </c>
       <c r="O27" s="4" t="n">
-        <v>-2.128034520101295</v>
+        <v>-2.142105747928824</v>
       </c>
       <c r="P27" s="4" t="n">
-        <v>-2.154917528986466</v>
+        <v>-2.142164009534312</v>
       </c>
     </row>
     <row r="28">
@@ -4996,101 +4996,101 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>2133</v>
+        <v>2135</v>
       </c>
       <c r="C28" s="4" t="n">
-        <v>-1.281881936239792</v>
+        <v>-1.270487725133982</v>
       </c>
       <c r="D28" s="4" t="n">
-        <v>-1.284499112661408</v>
+        <v>-1.274216702079784</v>
       </c>
       <c r="E28" s="4" t="n">
-        <v>-1.095029893502158</v>
+        <v>-1.08519596874465</v>
       </c>
       <c r="F28" s="4" t="n">
-        <v>-0.5198841567200176</v>
+        <v>-0.5104945186110115</v>
       </c>
       <c r="G28" s="4" t="n">
-        <v>-0.2861999827396957</v>
+        <v>-0.2774006044277115</v>
       </c>
       <c r="H28" s="4" t="n">
-        <v>-0.6171457849869029</v>
+        <v>-0.6078298704933189</v>
       </c>
       <c r="I28" s="4" t="n">
-        <v>-1.471041436371543</v>
+        <v>-1.460985732085469</v>
       </c>
       <c r="J28" s="4" t="n">
-        <v>-1.679587949194456</v>
+        <v>-1.669660499872492</v>
       </c>
       <c r="K28" s="4" t="n">
-        <v>-1.388163637083316</v>
+        <v>-1.425278318829186</v>
       </c>
       <c r="L28" s="4" t="n">
-        <v>-1.838740221198911</v>
+        <v>-1.87604562066209</v>
       </c>
       <c r="M28" s="4" t="n">
-        <v>-1.643570835427255</v>
+        <v>-1.634449211932825</v>
       </c>
       <c r="N28" s="4" t="n">
-        <v>-2.051981668029995</v>
+        <v>-2.089247243110279</v>
       </c>
       <c r="O28" s="4" t="n">
-        <v>-2.493702053355996</v>
+        <v>-2.530867516083369</v>
       </c>
       <c r="P28" s="4" t="n">
-        <v>-2.452995924222535</v>
+        <v>-2.467136619867482</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>X &lt; -0.1123</t>
+          <t>X &lt; -0.1122</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>2309</v>
+        <v>2310</v>
       </c>
       <c r="C29" s="4" t="n">
-        <v>-0.9430507233107477</v>
+        <v>-0.9527197326436934</v>
       </c>
       <c r="D29" s="4" t="n">
-        <v>-1.326037353251785</v>
+        <v>-1.335857506888445</v>
       </c>
       <c r="E29" s="4" t="n">
-        <v>-1.180915122529441</v>
+        <v>-1.190880401933569</v>
       </c>
       <c r="F29" s="4" t="n">
-        <v>-0.5102053424371462</v>
+        <v>-0.5204414682131357</v>
       </c>
       <c r="G29" s="4" t="n">
-        <v>-0.2057191277574972</v>
+        <v>-0.2161970812930676</v>
       </c>
       <c r="H29" s="4" t="n">
-        <v>-0.4457384202557009</v>
+        <v>-0.4560625940063119</v>
       </c>
       <c r="I29" s="4" t="n">
-        <v>-1.500176425799012</v>
+        <v>-1.510068809425164</v>
       </c>
       <c r="J29" s="4" t="n">
-        <v>-1.642005542042291</v>
+        <v>-1.651933564853501</v>
       </c>
       <c r="K29" s="4" t="n">
-        <v>-1.334154728847523</v>
+        <v>-1.344234335058175</v>
       </c>
       <c r="L29" s="4" t="n">
-        <v>-1.771876382073508</v>
+        <v>-1.781937880431784</v>
       </c>
       <c r="M29" s="4" t="n">
-        <v>-1.30435385319484</v>
+        <v>-1.314663982071266</v>
       </c>
       <c r="N29" s="4" t="n">
-        <v>-1.76543843776075</v>
+        <v>-1.775549548997809</v>
       </c>
       <c r="O29" s="4" t="n">
-        <v>-2.162109247536385</v>
+        <v>-2.172137002354049</v>
       </c>
       <c r="P29" s="4" t="n">
-        <v>-1.8887836863722</v>
+        <v>-1.879527507668215</v>
       </c>
     </row>
     <row r="30">
@@ -5100,49 +5100,49 @@
         </is>
       </c>
       <c r="B30" t="n">
-        <v>2548</v>
+        <v>2549</v>
       </c>
       <c r="C30" s="4" t="n">
-        <v>-0.4825050910026292</v>
+        <v>-0.4902837120331824</v>
       </c>
       <c r="D30" s="4" t="n">
-        <v>-0.8237619331742323</v>
+        <v>-0.8316569849804551</v>
       </c>
       <c r="E30" s="4" t="n">
-        <v>-0.8070318707204152</v>
+        <v>-0.8149985083532201</v>
       </c>
       <c r="F30" s="4" t="n">
-        <v>-0.7730676948099173</v>
+        <v>-0.7810328899700139</v>
       </c>
       <c r="G30" s="4" t="n">
-        <v>-0.3519282685788596</v>
+        <v>-0.3601451109801772</v>
       </c>
       <c r="H30" s="4" t="n">
-        <v>-0.3852546718437679</v>
+        <v>-0.3934184052375898</v>
       </c>
       <c r="I30" s="4" t="n">
-        <v>-1.074988251302877</v>
+        <v>-1.082900225582407</v>
       </c>
       <c r="J30" s="4" t="n">
-        <v>-1.129634315608847</v>
+        <v>-1.137601208303813</v>
       </c>
       <c r="K30" s="4" t="n">
-        <v>-0.7386040844449013</v>
+        <v>-0.7467385168692786</v>
       </c>
       <c r="L30" s="4" t="n">
-        <v>-1.057974990592612</v>
+        <v>-1.06611928478906</v>
       </c>
       <c r="M30" s="4" t="n">
-        <v>-0.5747566669363877</v>
+        <v>-0.5831268205730211</v>
       </c>
       <c r="N30" s="4" t="n">
-        <v>-0.9891171779716785</v>
+        <v>-0.9973249841009562</v>
       </c>
       <c r="O30" s="4" t="n">
-        <v>-1.230770415059858</v>
+        <v>-1.238952997466939</v>
       </c>
       <c r="P30" s="4" t="n">
-        <v>-0.9985398585549063</v>
+        <v>-0.9914787184817229</v>
       </c>
     </row>
     <row r="31">
@@ -5152,101 +5152,101 @@
         </is>
       </c>
       <c r="B31" t="n">
-        <v>2773</v>
+        <v>2774</v>
       </c>
       <c r="C31" s="4" t="n">
-        <v>-1.129475649714642</v>
+        <v>-1.13538319953328</v>
       </c>
       <c r="D31" s="4" t="n">
-        <v>-1.178620550768485</v>
+        <v>-1.184708010173914</v>
       </c>
       <c r="E31" s="4" t="n">
-        <v>-1.051604777701861</v>
+        <v>-1.057789127742808</v>
       </c>
       <c r="F31" s="4" t="n">
-        <v>-1.117741053695845</v>
+        <v>-1.1238897440752</v>
       </c>
       <c r="G31" s="4" t="n">
-        <v>-0.4148783412146386</v>
+        <v>-0.4213482664052819</v>
       </c>
       <c r="H31" s="4" t="n">
-        <v>-0.6372159179250829</v>
+        <v>-0.6435739529271274</v>
       </c>
       <c r="I31" s="4" t="n">
-        <v>-1.170160645676994</v>
+        <v>-1.176341129908032</v>
       </c>
       <c r="J31" s="4" t="n">
-        <v>-1.258241784704595</v>
+        <v>-1.264450804947437</v>
       </c>
       <c r="K31" s="4" t="n">
-        <v>-1.01186071980127</v>
+        <v>-1.018169596199854</v>
       </c>
       <c r="L31" s="4" t="n">
-        <v>-1.266302914887909</v>
+        <v>-1.272626853490259</v>
       </c>
       <c r="M31" s="4" t="n">
-        <v>-0.9469901923550168</v>
+        <v>-0.9534577859706062</v>
       </c>
       <c r="N31" s="4" t="n">
-        <v>-1.144920039656888</v>
+        <v>-1.151316129574788</v>
       </c>
       <c r="O31" s="4" t="n">
-        <v>-1.292968774935211</v>
+        <v>-1.299366351997932</v>
       </c>
       <c r="P31" s="4" t="n">
-        <v>-1.131465507940291</v>
+        <v>-1.125775131709631</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>X &lt; -0.05613</t>
+          <t>X &lt; -0.05612</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>2994</v>
+        <v>2995</v>
       </c>
       <c r="C32" s="4" t="n">
-        <v>-1.113325250705493</v>
+        <v>-1.117884115640734</v>
       </c>
       <c r="D32" s="4" t="n">
-        <v>-1.177533556594057</v>
+        <v>-1.182225169823653</v>
       </c>
       <c r="E32" s="4" t="n">
-        <v>-1.155454683032048</v>
+        <v>-1.160193534966659</v>
       </c>
       <c r="F32" s="4" t="n">
-        <v>-0.8742879598930173</v>
+        <v>-0.8791109271608661</v>
       </c>
       <c r="G32" s="4" t="n">
-        <v>-0.5956944098811761</v>
+        <v>-0.6006636169284647</v>
       </c>
       <c r="H32" s="4" t="n">
-        <v>-0.8797606819215602</v>
+        <v>-0.884610175271753</v>
       </c>
       <c r="I32" s="4" t="n">
-        <v>-1.379779022285277</v>
+        <v>-1.384472781802089</v>
       </c>
       <c r="J32" s="4" t="n">
-        <v>-1.529190567240278</v>
+        <v>-1.533881378449315</v>
       </c>
       <c r="K32" s="4" t="n">
-        <v>-1.43892892180093</v>
+        <v>-1.443658381134483</v>
       </c>
       <c r="L32" s="4" t="n">
-        <v>-1.503935829689105</v>
+        <v>-1.508726671740213</v>
       </c>
       <c r="M32" s="4" t="n">
-        <v>-1.356814041179838</v>
+        <v>-1.361676156493935</v>
       </c>
       <c r="N32" s="4" t="n">
-        <v>-1.604499779610464</v>
+        <v>-1.60927889541459</v>
       </c>
       <c r="O32" s="4" t="n">
-        <v>-1.70600997674596</v>
+        <v>-1.710797810158361</v>
       </c>
       <c r="P32" s="4" t="n">
-        <v>-1.638333312548177</v>
+        <v>-1.633663188348123</v>
       </c>
     </row>
     <row r="33">
@@ -5256,49 +5256,49 @@
         </is>
       </c>
       <c r="B33" t="n">
-        <v>3226</v>
+        <v>3227</v>
       </c>
       <c r="C33" s="4" t="n">
-        <v>-0.841693954665061</v>
+        <v>-0.8451135613985485</v>
       </c>
       <c r="D33" s="4" t="n">
-        <v>-0.9549192833904101</v>
+        <v>-0.9584188880316518</v>
       </c>
       <c r="E33" s="4" t="n">
-        <v>-1.08622602129693</v>
+        <v>-1.089714768390287</v>
       </c>
       <c r="F33" s="4" t="n">
-        <v>-1.093978557843165</v>
+        <v>-1.097457756176652</v>
       </c>
       <c r="G33" s="4" t="n">
-        <v>-0.9049575321273053</v>
+        <v>-0.9085349512350831</v>
       </c>
       <c r="H33" s="4" t="n">
-        <v>-1.147403321316361</v>
+        <v>-1.150886917591777</v>
       </c>
       <c r="I33" s="4" t="n">
-        <v>-1.555841584377944</v>
+        <v>-1.559206838709933</v>
       </c>
       <c r="J33" s="4" t="n">
-        <v>-1.480593207504306</v>
+        <v>-1.484016568977104</v>
       </c>
       <c r="K33" s="4" t="n">
-        <v>-1.370227593626851</v>
+        <v>-1.373691384434807</v>
       </c>
       <c r="L33" s="4" t="n">
-        <v>-1.491605628130586</v>
+        <v>-1.495093735805412</v>
       </c>
       <c r="M33" s="4" t="n">
-        <v>-1.276853829083763</v>
+        <v>-1.280424878552189</v>
       </c>
       <c r="N33" s="4" t="n">
-        <v>-1.659136858706425</v>
+        <v>-1.662589147960936</v>
       </c>
       <c r="O33" s="4" t="n">
-        <v>-1.721602538049204</v>
+        <v>-1.725067145728467</v>
       </c>
       <c r="P33" s="4" t="n">
-        <v>-1.826827680908792</v>
+        <v>-1.823184718136694</v>
       </c>
     </row>
     <row r="34">
@@ -5308,49 +5308,49 @@
         </is>
       </c>
       <c r="B34" t="n">
-        <v>3451</v>
+        <v>3452</v>
       </c>
       <c r="C34" s="4" t="n">
-        <v>-0.2705745788704874</v>
+        <v>-0.27312382274215</v>
       </c>
       <c r="D34" s="4" t="n">
-        <v>-0.4809865216813094</v>
+        <v>-0.4835570889561538</v>
       </c>
       <c r="E34" s="4" t="n">
-        <v>-0.8025958333005718</v>
+        <v>-0.8050947038484537</v>
       </c>
       <c r="F34" s="4" t="n">
-        <v>-0.5990409714799938</v>
+        <v>-0.6015934831935041</v>
       </c>
       <c r="G34" s="4" t="n">
-        <v>-0.6016903407325955</v>
+        <v>-0.6042704807036614</v>
       </c>
       <c r="H34" s="4" t="n">
-        <v>-0.7221997304579588</v>
+        <v>-0.7247315182832708</v>
       </c>
       <c r="I34" s="4" t="n">
-        <v>-0.7913497556961033</v>
+        <v>-0.7938671934297616</v>
       </c>
       <c r="J34" s="4" t="n">
-        <v>-0.7801114041894621</v>
+        <v>-0.7826569456450514</v>
       </c>
       <c r="K34" s="4" t="n">
-        <v>-0.8253756386077598</v>
+        <v>-0.8279125514170005</v>
       </c>
       <c r="L34" s="4" t="n">
-        <v>-0.9361670615088755</v>
+        <v>-0.9387160663532299</v>
       </c>
       <c r="M34" s="4" t="n">
-        <v>-0.7485817981280576</v>
+        <v>-0.7511968113636982</v>
       </c>
       <c r="N34" s="4" t="n">
-        <v>-1.103561565631168</v>
+        <v>-1.106073508982028</v>
       </c>
       <c r="O34" s="4" t="n">
-        <v>-1.160218129770421</v>
+        <v>-1.162736237956878</v>
       </c>
       <c r="P34" s="4" t="n">
-        <v>-1.155207300067318</v>
+        <v>-1.15267614350514</v>
       </c>
     </row>
     <row r="35">
@@ -5360,49 +5360,49 @@
         </is>
       </c>
       <c r="B35" t="n">
-        <v>3731</v>
+        <v>3732</v>
       </c>
       <c r="C35" s="4" t="n">
-        <v>-0.1430109697826225</v>
+        <v>-0.1444674324035162</v>
       </c>
       <c r="D35" s="4" t="n">
-        <v>-0.3513384092629295</v>
+        <v>-0.3527858842819427</v>
       </c>
       <c r="E35" s="4" t="n">
-        <v>-0.3844343543619502</v>
+        <v>-0.3858849964643625</v>
       </c>
       <c r="F35" s="4" t="n">
-        <v>-0.4001006426885851</v>
+        <v>-0.4015441424238588</v>
       </c>
       <c r="G35" s="4" t="n">
-        <v>-0.3358562088665025</v>
+        <v>-0.3373329993895595</v>
       </c>
       <c r="H35" s="4" t="n">
-        <v>-0.4249956585503156</v>
+        <v>-0.4264408935730586</v>
       </c>
       <c r="I35" s="4" t="n">
-        <v>-0.3347198490366239</v>
+        <v>-0.3361924074274469</v>
       </c>
       <c r="J35" s="4" t="n">
-        <v>-0.4930028944189431</v>
+        <v>-0.4944472251467502</v>
       </c>
       <c r="K35" s="4" t="n">
-        <v>-0.3252368488544164</v>
+        <v>-0.3267285800462716</v>
       </c>
       <c r="L35" s="4" t="n">
-        <v>-0.5716409396553246</v>
+        <v>-0.5730918098697657</v>
       </c>
       <c r="M35" s="4" t="n">
-        <v>-0.3598163293097727</v>
+        <v>-0.3613305445598698</v>
       </c>
       <c r="N35" s="4" t="n">
-        <v>-0.4979703844029189</v>
+        <v>-0.4994474070792663</v>
       </c>
       <c r="O35" s="4" t="n">
-        <v>-0.474563138768417</v>
+        <v>-0.4760592517018267</v>
       </c>
       <c r="P35" s="4" t="n">
-        <v>-0.5046087026028374</v>
+        <v>-0.5032242824903932</v>
       </c>
     </row>
   </sheetData>

--- a/workspaces/btc_daily_14days/drawdown/drawdown_120.xlsx
+++ b/workspaces/btc_daily_14days/drawdown/drawdown_120.xlsx
@@ -568,365 +568,365 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>X ≈ -0.5332</t>
+          <t>X ≈ -0.5331</t>
         </is>
       </c>
       <c r="B6" t="n">
         <v>22</v>
       </c>
       <c r="C6" s="4" t="n">
-        <v>-2.47275013901033</v>
+        <v>-2.501868459133718</v>
       </c>
       <c r="D6" s="4" t="n">
-        <v>-8.611380065522816</v>
+        <v>-8.612635609272907</v>
       </c>
       <c r="E6" s="4" t="n">
-        <v>-22.60600670247096</v>
+        <v>-22.60633251104543</v>
       </c>
       <c r="F6" s="4" t="n">
-        <v>-8.879640621230699</v>
+        <v>-8.880195980811955</v>
       </c>
       <c r="G6" s="4" t="n">
-        <v>-13.95436644404093</v>
+        <v>-13.90602230254556</v>
       </c>
       <c r="H6" s="4" t="n">
-        <v>-9.124731330021056</v>
+        <v>-9.100874714899874</v>
       </c>
       <c r="I6" s="4" t="n">
-        <v>-9.211566401583106</v>
+        <v>-9.163687908192834</v>
       </c>
       <c r="J6" s="4" t="n">
-        <v>-9.680425553349437</v>
+        <v>-9.631295046902878</v>
       </c>
       <c r="K6" s="4" t="n">
-        <v>-5.203843956079083</v>
+        <v>-5.1307013892052</v>
       </c>
       <c r="L6" s="4" t="n">
-        <v>3.027392945665632</v>
+        <v>3.126644804895925</v>
       </c>
       <c r="M6" s="4" t="n">
-        <v>2.82367215058342</v>
+        <v>2.923507652061808</v>
       </c>
       <c r="N6" s="4" t="n">
-        <v>2.858859102825051</v>
+        <v>2.982494467617826</v>
       </c>
       <c r="O6" s="4" t="n">
-        <v>6.983867002340084</v>
+        <v>7.132522158995812</v>
       </c>
       <c r="P6" s="4" t="n">
-        <v>7.211381583238818</v>
+        <v>7.383380342807541</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>X ≈ -0.5145</t>
+          <t>X ≈ -0.5144</t>
         </is>
       </c>
       <c r="B7" t="n">
         <v>20</v>
       </c>
       <c r="C7" s="4" t="n">
-        <v>-12.43974356331218</v>
+        <v>-12.46895274666829</v>
       </c>
       <c r="D7" s="4" t="n">
-        <v>-4.079463016822103</v>
+        <v>-4.080681676349421</v>
       </c>
       <c r="E7" s="4" t="n">
-        <v>5.497937846076212</v>
+        <v>5.497826632851876</v>
       </c>
       <c r="F7" s="4" t="n">
-        <v>-4.345466138954869</v>
+        <v>-4.345990787328191</v>
       </c>
       <c r="G7" s="4" t="n">
-        <v>5.093324396401087</v>
+        <v>5.141786567739224</v>
       </c>
       <c r="H7" s="4" t="n">
-        <v>5.39141399180204</v>
+        <v>5.41535105397729</v>
       </c>
       <c r="I7" s="4" t="n">
-        <v>5.308237785927155</v>
+        <v>5.356186223710424</v>
       </c>
       <c r="J7" s="4" t="n">
-        <v>-0.1493467329476204</v>
+        <v>-0.1001774669245989</v>
       </c>
       <c r="K7" s="4" t="n">
-        <v>9.777194411306112</v>
+        <v>9.850388538693672</v>
       </c>
       <c r="L7" s="4" t="n">
-        <v>8.930449895294743</v>
+        <v>9.029717538878558</v>
       </c>
       <c r="M7" s="4" t="n">
-        <v>13.72443009848551</v>
+        <v>13.82428803442465</v>
       </c>
       <c r="N7" s="4" t="n">
-        <v>8.764933131871992</v>
+        <v>8.888576248729827</v>
       </c>
       <c r="O7" s="4" t="n">
-        <v>-1.650321970945001</v>
+        <v>-1.501673239238478</v>
       </c>
       <c r="P7" s="4" t="n">
-        <v>3.57501794687952</v>
+        <v>3.747016706446182</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>X ≈ -0.4958</t>
+          <t>X ≈ -0.4957</t>
         </is>
       </c>
       <c r="B8" t="n">
         <v>39</v>
       </c>
       <c r="C8" s="4" t="n">
-        <v>9.027727994477438</v>
+        <v>8.998717765426626</v>
       </c>
       <c r="D8" s="4" t="n">
-        <v>-0.244925476335986</v>
+        <v>-0.246112018805178</v>
       </c>
       <c r="E8" s="4" t="n">
-        <v>12.14561027952269</v>
+        <v>12.14555301500685</v>
       </c>
       <c r="F8" s="4" t="n">
-        <v>7.163631472176114</v>
+        <v>7.163188810534592</v>
       </c>
       <c r="G8" s="4" t="n">
-        <v>14.3026472762896</v>
+        <v>14.35116841334384</v>
       </c>
       <c r="H8" s="4" t="n">
-        <v>17.16195562548631</v>
+        <v>17.18596072426168</v>
       </c>
       <c r="I8" s="4" t="n">
-        <v>17.08181760011371</v>
+        <v>17.12982490904962</v>
       </c>
       <c r="J8" s="4" t="n">
-        <v>14.05954577682413</v>
+        <v>14.108775345468</v>
       </c>
       <c r="K8" s="4" t="n">
-        <v>19.12398752381434</v>
+        <v>19.19721494477425</v>
       </c>
       <c r="L8" s="4" t="n">
-        <v>23.40263379484898</v>
+        <v>23.50194240219618</v>
       </c>
       <c r="M8" s="4" t="n">
-        <v>23.20415101963742</v>
+        <v>23.30402917759614</v>
       </c>
       <c r="N8" s="4" t="n">
-        <v>20.68182599367284</v>
+        <v>20.80548570079474</v>
       </c>
       <c r="O8" s="4" t="n">
-        <v>25.39402628510122</v>
+        <v>25.54269391258173</v>
       </c>
       <c r="P8" s="4" t="n">
-        <v>25.62629999815812</v>
+        <v>25.79829875772479</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>X ≈ -0.477</t>
+          <t>X ≈ -0.4769</t>
         </is>
       </c>
       <c r="B9" t="n">
         <v>56</v>
       </c>
       <c r="C9" s="4" t="n">
-        <v>8.205597220102966</v>
+        <v>8.176585731843822</v>
       </c>
       <c r="D9" s="4" t="n">
-        <v>1.26138284375557</v>
+        <v>1.260209632230691</v>
       </c>
       <c r="E9" s="4" t="n">
-        <v>7.989999157987647</v>
+        <v>7.989912776446047</v>
       </c>
       <c r="F9" s="4" t="n">
-        <v>11.68437909928449</v>
+        <v>11.68397251671382</v>
       </c>
       <c r="G9" s="4" t="n">
-        <v>5.805253595695383</v>
+        <v>5.853719735971261</v>
       </c>
       <c r="H9" s="4" t="n">
-        <v>-2.806486167026392</v>
+        <v>-2.78259592378302</v>
       </c>
       <c r="I9" s="4" t="n">
-        <v>6.020628610892999</v>
+        <v>6.068580521238786</v>
       </c>
       <c r="J9" s="4" t="n">
-        <v>-1.575912015215572</v>
+        <v>-1.52675098492093</v>
       </c>
       <c r="K9" s="4" t="n">
-        <v>-1.637142543727592</v>
+        <v>-1.563991190529386</v>
       </c>
       <c r="L9" s="4" t="n">
-        <v>1.080956083503381</v>
+        <v>1.180199138681601</v>
       </c>
       <c r="M9" s="4" t="n">
-        <v>4.445461396621127</v>
+        <v>4.545298287636825</v>
       </c>
       <c r="N9" s="4" t="n">
-        <v>0.9116362556124713</v>
+        <v>1.035266425297898</v>
       </c>
       <c r="O9" s="4" t="n">
-        <v>0.4919229042491082</v>
+        <v>0.64057194381909</v>
       </c>
       <c r="P9" s="4" t="n">
-        <v>-2.853553481693375</v>
+        <v>-2.681554722128332</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>X ≈ -0.4584</t>
+          <t>X ≈ -0.4583</t>
         </is>
       </c>
       <c r="B10" t="n">
         <v>60</v>
       </c>
       <c r="C10" s="4" t="n">
-        <v>0.8490862664495396</v>
+        <v>0.8200097384542175</v>
       </c>
       <c r="D10" s="4" t="n">
-        <v>-0.7561357760017842</v>
+        <v>-0.7573267649319462</v>
       </c>
       <c r="E10" s="4" t="n">
-        <v>-11.12177548266827</v>
+        <v>-11.12201859292657</v>
       </c>
       <c r="F10" s="4" t="n">
-        <v>-14.31920780576192</v>
+        <v>-14.31980798664628</v>
       </c>
       <c r="G10" s="4" t="n">
-        <v>-4.884020602985537</v>
+        <v>-4.83562928015008</v>
       </c>
       <c r="H10" s="4" t="n">
-        <v>-6.251413647215585</v>
+        <v>-6.227547030135113</v>
       </c>
       <c r="I10" s="4" t="n">
-        <v>-11.32855337529146</v>
+        <v>-11.28069528108283</v>
       </c>
       <c r="J10" s="4" t="n">
-        <v>-15.12577712248648</v>
+        <v>-15.07668118851347</v>
       </c>
       <c r="K10" s="4" t="n">
-        <v>-10.19719747568304</v>
+        <v>-10.12408230310093</v>
       </c>
       <c r="L10" s="4" t="n">
-        <v>-17.70874055078287</v>
+        <v>-17.60955813687449</v>
       </c>
       <c r="M10" s="4" t="n">
-        <v>-16.25252070863516</v>
+        <v>-16.15273324911153</v>
       </c>
       <c r="N10" s="4" t="n">
-        <v>-16.22217784046382</v>
+        <v>-16.09857592114059</v>
       </c>
       <c r="O10" s="4" t="n">
-        <v>-18.31263411370316</v>
+        <v>-18.16400071707321</v>
       </c>
       <c r="P10" s="4" t="n">
-        <v>-18.09164871979018</v>
+        <v>-17.919649960222</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>X ≈ -0.4396</t>
+          <t>X ≈ -0.4395</t>
         </is>
       </c>
       <c r="B11" t="n">
         <v>64</v>
       </c>
       <c r="C11" s="4" t="n">
-        <v>-2.472740288110309</v>
+        <v>-2.50184669729736</v>
       </c>
       <c r="D11" s="4" t="n">
-        <v>-0.963711132996977</v>
+        <v>-0.9649044906033808</v>
       </c>
       <c r="E11" s="4" t="n">
-        <v>-7.589502461786005</v>
+        <v>-7.589720911761248</v>
       </c>
       <c r="F11" s="4" t="n">
-        <v>-2.786485742624144</v>
+        <v>-2.787001800465518</v>
       </c>
       <c r="G11" s="4" t="n">
-        <v>-6.442383123907213</v>
+        <v>-6.394009109685463</v>
       </c>
       <c r="H11" s="4" t="n">
-        <v>-4.587899742101754</v>
+        <v>-4.56402685569897</v>
       </c>
       <c r="I11" s="4" t="n">
-        <v>-4.673739182268164</v>
+        <v>-4.625851280108051</v>
       </c>
       <c r="J11" s="4" t="n">
-        <v>-3.581126395832833</v>
+        <v>-3.53198291497042</v>
       </c>
       <c r="K11" s="4" t="n">
-        <v>-0.5222739617265972</v>
+        <v>-0.4491264448818058</v>
       </c>
       <c r="L11" s="4" t="n">
-        <v>-4.493189469072945</v>
+        <v>-4.393972402855141</v>
       </c>
       <c r="M11" s="4" t="n">
-        <v>-7.821411000992398</v>
+        <v>-7.721608708522041</v>
       </c>
       <c r="N11" s="4" t="n">
-        <v>-10.91225508241406</v>
+        <v>-10.78864871090602</v>
       </c>
       <c r="O11" s="4" t="n">
-        <v>-16.02142539079234</v>
+        <v>-15.87279251048168</v>
       </c>
       <c r="P11" s="4" t="n">
-        <v>-12.67498205312204</v>
+        <v>-12.50298329355609</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>X ≈ -0.421</t>
+          <t>X ≈ -0.4209</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="C12" s="4" t="n">
-        <v>-5.094735845566781</v>
+        <v>-5.034967145695759</v>
       </c>
       <c r="D12" s="4" t="n">
-        <v>-4.952713313259103</v>
+        <v>-4.924298880796577</v>
       </c>
       <c r="E12" s="4" t="n">
-        <v>3.397951566746357</v>
+        <v>3.131003800584317</v>
       </c>
       <c r="F12" s="4" t="n">
-        <v>0.02953844163410224</v>
+        <v>-1.809536877480049</v>
       </c>
       <c r="G12" s="4" t="n">
-        <v>-7.508343144975939</v>
+        <v>-9.061754371842831</v>
       </c>
       <c r="H12" s="4" t="n">
-        <v>-10.71453955912523</v>
+        <v>-12.17423082942404</v>
       </c>
       <c r="I12" s="4" t="n">
-        <v>-14.30416097959297</v>
+        <v>-15.6215400320688</v>
       </c>
       <c r="J12" s="4" t="n">
-        <v>-25.28329867275902</v>
+        <v>-26.24359462124183</v>
       </c>
       <c r="K12" s="4" t="n">
-        <v>-23.59928240652057</v>
+        <v>-24.59523150095268</v>
       </c>
       <c r="L12" s="4" t="n">
-        <v>-24.45477559139727</v>
+        <v>-23.73185180541423</v>
       </c>
       <c r="M12" s="4" t="n">
-        <v>-24.66595714279237</v>
+        <v>-25.63578765839928</v>
       </c>
       <c r="N12" s="4" t="n">
-        <v>-17.62440387579992</v>
+        <v>-18.80844965390411</v>
       </c>
       <c r="O12" s="4" t="n">
-        <v>-18.0492382111812</v>
+        <v>-19.20860573231622</v>
       </c>
       <c r="P12" s="4" t="n">
-        <v>-19.58287678996565</v>
+        <v>-20.65976295457304</v>
       </c>
     </row>
     <row r="13">
@@ -936,205 +936,205 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="C13" s="4" t="n">
-        <v>-1.194590931895497</v>
+        <v>-1.190058046323614</v>
       </c>
       <c r="D13" s="4" t="n">
-        <v>-4.077826333519518</v>
+        <v>-4.079046262809449</v>
       </c>
       <c r="E13" s="4" t="n">
-        <v>-0.638609073400076</v>
+        <v>-0.5378556400049064</v>
       </c>
       <c r="F13" s="4" t="n">
-        <v>-3.065725664094153</v>
+        <v>-1.720382321983053</v>
       </c>
       <c r="G13" s="4" t="n">
-        <v>-8.719190773830228</v>
+        <v>-7.459235468139745</v>
       </c>
       <c r="H13" s="4" t="n">
-        <v>-8.424575932933408</v>
+        <v>-7.188795989122738</v>
       </c>
       <c r="I13" s="4" t="n">
-        <v>-4.672833377238881</v>
+        <v>-3.311669042611442</v>
       </c>
       <c r="J13" s="4" t="n">
-        <v>-6.419944843228954</v>
+        <v>-5.090863739610604</v>
       </c>
       <c r="K13" s="4" t="n">
-        <v>-3.922435157994265</v>
+        <v>-2.501618978284931</v>
       </c>
       <c r="L13" s="4" t="n">
-        <v>-2.211408630264685</v>
+        <v>-2.01109048069349</v>
       </c>
       <c r="M13" s="4" t="n">
-        <v>1.426305659571014</v>
+        <v>3.043099018150485</v>
       </c>
       <c r="N13" s="4" t="n">
-        <v>2.742456602139633</v>
+        <v>4.417188709848887</v>
       </c>
       <c r="O13" s="4" t="n">
-        <v>-1.521950294369915</v>
+        <v>0.07703712532237006</v>
       </c>
       <c r="P13" s="4" t="n">
-        <v>-6.42498205312188</v>
+        <v>-4.937193819872178</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>X ≈ -0.3836</t>
+          <t>X ≈ -0.3834</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="C14" s="4" t="n">
-        <v>-0.04170459846839236</v>
+        <v>0.5001338720609638</v>
       </c>
       <c r="D14" s="4" t="n">
-        <v>-0.4311400649571624</v>
+        <v>0.1240966673964863</v>
       </c>
       <c r="E14" s="4" t="n">
-        <v>-0.8255423455585174</v>
+        <v>-0.2691171246642199</v>
       </c>
       <c r="F14" s="4" t="n">
-        <v>1.736469023778277</v>
+        <v>2.2634295847703</v>
       </c>
       <c r="G14" s="4" t="n">
-        <v>-0.01636565223545006</v>
+        <v>0.5742801692814226</v>
       </c>
       <c r="H14" s="4" t="n">
-        <v>3.93079747934182</v>
+        <v>4.453135646950834</v>
       </c>
       <c r="I14" s="4" t="n">
-        <v>0.1959095001346398</v>
+        <v>0.786363733502796</v>
       </c>
       <c r="J14" s="4" t="n">
-        <v>3.382411163753531</v>
+        <v>3.930278266240805</v>
       </c>
       <c r="K14" s="4" t="n">
-        <v>0.8864715765831761</v>
+        <v>1.487800473004576</v>
       </c>
       <c r="L14" s="4" t="n">
-        <v>-4.83492939504211</v>
+        <v>-4.148683560602976</v>
       </c>
       <c r="M14" s="4" t="n">
-        <v>-1.385591376177409</v>
+        <v>-0.7426131791638966</v>
       </c>
       <c r="N14" s="4" t="n">
-        <v>-5.008022384404072</v>
+        <v>-4.297035027715587</v>
       </c>
       <c r="O14" s="4" t="n">
-        <v>-12.74448425564632</v>
+        <v>-11.92017363998734</v>
       </c>
       <c r="P14" s="4" t="n">
-        <v>-11.30303083361083</v>
+        <v>-10.46985076343533</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>X ≈ -0.3649</t>
+          <t>X ≈ -0.3648</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="C15" s="4" t="n">
-        <v>-5.269783128003589</v>
+        <v>-5.896793706791044</v>
       </c>
       <c r="D15" s="4" t="n">
-        <v>-10.2348406258385</v>
+        <v>-10.8723652042838</v>
       </c>
       <c r="E15" s="4" t="n">
-        <v>-11.75207307985226</v>
+        <v>-12.40147855589996</v>
       </c>
       <c r="F15" s="4" t="n">
-        <v>-14.98644559270481</v>
+        <v>-15.6745896149305</v>
       </c>
       <c r="G15" s="4" t="n">
-        <v>-13.28634135304158</v>
+        <v>-13.90029763613941</v>
       </c>
       <c r="H15" s="4" t="n">
-        <v>-12.99347307026567</v>
+        <v>-13.63210793187859</v>
       </c>
       <c r="I15" s="4" t="n">
-        <v>-17.56702801068664</v>
+        <v>-18.23283420989764</v>
       </c>
       <c r="J15" s="4" t="n">
-        <v>-12.42997297141947</v>
+        <v>-13.03096097838237</v>
       </c>
       <c r="K15" s="4" t="n">
-        <v>-11.37293260228378</v>
+        <v>-11.93735325565335</v>
       </c>
       <c r="L15" s="4" t="n">
-        <v>-11.1029800906834</v>
+        <v>-11.62873811293797</v>
       </c>
       <c r="M15" s="4" t="n">
-        <v>-14.67884951445972</v>
+        <v>-15.24246045607073</v>
       </c>
       <c r="N15" s="4" t="n">
-        <v>-15.77163324623845</v>
+        <v>-16.32437700998244</v>
       </c>
       <c r="O15" s="4" t="n">
-        <v>-9.456685703467365</v>
+        <v>-9.907988856702318</v>
       </c>
       <c r="P15" s="4" t="n">
-        <v>-8.110375311549717</v>
+        <v>-8.525710566283365</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>X ≈ -0.3461</t>
+          <t>X ≈ -0.346</t>
         </is>
       </c>
       <c r="B16" t="n">
         <v>68</v>
       </c>
       <c r="C16" s="4" t="n">
-        <v>-11.26008416604732</v>
+        <v>-11.28928878541564</v>
       </c>
       <c r="D16" s="4" t="n">
-        <v>-15.79806215382964</v>
+        <v>-15.7994422243362</v>
       </c>
       <c r="E16" s="4" t="n">
-        <v>-20.59428529105889</v>
+        <v>-20.59466793660189</v>
       </c>
       <c r="F16" s="4" t="n">
-        <v>-14.60546226347972</v>
+        <v>-14.60610823742956</v>
       </c>
       <c r="G16" s="4" t="n">
-        <v>-7.81361499803824</v>
+        <v>-7.76530633456148</v>
       </c>
       <c r="H16" s="4" t="n">
-        <v>-13.38763437812587</v>
+        <v>-13.36386074704038</v>
       </c>
       <c r="I16" s="4" t="n">
-        <v>-9.0735105932132</v>
+        <v>-9.025693369656786</v>
       </c>
       <c r="J16" s="4" t="n">
-        <v>-11.01043491591749</v>
+        <v>-10.96136938926751</v>
       </c>
       <c r="K16" s="4" t="n">
-        <v>-9.60675736771789</v>
+        <v>-9.533687030961978</v>
       </c>
       <c r="L16" s="4" t="n">
-        <v>-17.80285823287985</v>
+        <v>-17.70373066800295</v>
       </c>
       <c r="M16" s="4" t="n">
-        <v>-13.60517448124518</v>
+        <v>-13.50541900870214</v>
       </c>
       <c r="N16" s="4" t="n">
-        <v>-16.51429884450019</v>
+        <v>-16.3907281343391</v>
       </c>
       <c r="O16" s="4" t="n">
-        <v>-13.99913745430481</v>
+        <v>-13.85051806217197</v>
       </c>
       <c r="P16" s="4" t="n">
-        <v>-13.77792322959334</v>
+        <v>-13.60592447002634</v>
       </c>
     </row>
     <row r="17">
@@ -1147,46 +1147,46 @@
         <v>60</v>
       </c>
       <c r="C17" s="4" t="n">
-        <v>-7.449912654462182</v>
+        <v>-7.479073183324871</v>
       </c>
       <c r="D17" s="4" t="n">
-        <v>-5.734516717055975</v>
+        <v>-5.735789500445868</v>
       </c>
       <c r="E17" s="4" t="n">
-        <v>-2.808049973829796</v>
+        <v>-2.808252112079771</v>
       </c>
       <c r="F17" s="4" t="n">
-        <v>-2.679238825353657</v>
+        <v>-2.679775604391104</v>
       </c>
       <c r="G17" s="4" t="n">
-        <v>-3.217494420401621</v>
+        <v>-3.169155911526737</v>
       </c>
       <c r="H17" s="4" t="n">
-        <v>-2.921637274664839</v>
+        <v>-2.897790153223646</v>
       </c>
       <c r="I17" s="4" t="n">
-        <v>0.3190277531440771</v>
+        <v>0.366901504920925</v>
       </c>
       <c r="J17" s="4" t="n">
-        <v>3.1801456363875</v>
+        <v>3.229287787998537</v>
       </c>
       <c r="K17" s="4" t="n">
-        <v>1.455424123000448</v>
+        <v>1.528541395721774</v>
       </c>
       <c r="L17" s="4" t="n">
-        <v>10.59477602012106</v>
+        <v>10.69400758497321</v>
       </c>
       <c r="M17" s="4" t="n">
-        <v>5.397564303390617</v>
+        <v>5.497370134295302</v>
       </c>
       <c r="N17" s="4" t="n">
-        <v>5.433519805573297</v>
+        <v>5.557128897321817</v>
       </c>
       <c r="O17" s="4" t="n">
-        <v>5.014855021786481</v>
+        <v>5.163490434895415</v>
       </c>
       <c r="P17" s="4" t="n">
-        <v>5.241684613543917</v>
+        <v>5.413683373110203</v>
       </c>
     </row>
     <row r="18">
@@ -1196,101 +1196,101 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="C18" s="4" t="n">
-        <v>6.245855527331543</v>
+        <v>6.00431276465099</v>
       </c>
       <c r="D18" s="4" t="n">
-        <v>7.134994518894523</v>
+        <v>5.645522621767817</v>
       </c>
       <c r="E18" s="4" t="n">
-        <v>5.497291851983938</v>
+        <v>4.038753229146401</v>
       </c>
       <c r="F18" s="4" t="n">
-        <v>3.136407196698258</v>
+        <v>2.953565542189338</v>
       </c>
       <c r="G18" s="4" t="n">
-        <v>6.339456209417492</v>
+        <v>6.114242430875869</v>
       </c>
       <c r="H18" s="4" t="n">
-        <v>4.144452124037002</v>
+        <v>2.73898156810921</v>
       </c>
       <c r="I18" s="4" t="n">
-        <v>5.30818111142618</v>
+        <v>5.112707862261999</v>
       </c>
       <c r="J18" s="4" t="n">
-        <v>4.843528328983098</v>
+        <v>4.649224944136257</v>
       </c>
       <c r="K18" s="4" t="n">
-        <v>9.775729053563481</v>
+        <v>9.483590999133334</v>
       </c>
       <c r="L18" s="4" t="n">
-        <v>6.432797883022687</v>
+        <v>6.227505125414687</v>
       </c>
       <c r="M18" s="4" t="n">
-        <v>7.478766622837135</v>
+        <v>7.243518403764696</v>
       </c>
       <c r="N18" s="4" t="n">
-        <v>12.512320262709</v>
+        <v>12.17890407993392</v>
       </c>
       <c r="O18" s="4" t="n">
-        <v>10.84631991406259</v>
+        <v>10.56826106361972</v>
       </c>
       <c r="P18" s="4" t="n">
-        <v>9.825017946877246</v>
+        <v>9.600675243029279</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>X ≈ -0.29</t>
+          <t>X ≈ -0.2899</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="C19" s="4" t="n">
-        <v>-6.112410487522446</v>
+        <v>-4.994407423401157</v>
       </c>
       <c r="D19" s="4" t="n">
-        <v>-5.28794129498732</v>
+        <v>-2.906996088054427</v>
       </c>
       <c r="E19" s="4" t="n">
-        <v>-2.037947640249229</v>
+        <v>0.3872628511324194</v>
       </c>
       <c r="F19" s="4" t="n">
-        <v>-0.6931464015507274</v>
+        <v>0.5177317406949555</v>
       </c>
       <c r="G19" s="4" t="n">
-        <v>-4.87900326386773</v>
+        <v>-4.8999043907776</v>
       </c>
       <c r="H19" s="4" t="n">
-        <v>-5.799984107023278</v>
+        <v>-3.943965588082136</v>
       </c>
       <c r="I19" s="4" t="n">
-        <v>-13.18741644569739</v>
+        <v>-13.86070511618954</v>
       </c>
       <c r="J19" s="4" t="n">
-        <v>-12.44068664644782</v>
+        <v>-11.86570100567649</v>
       </c>
       <c r="K19" s="4" t="n">
-        <v>-14.94149414649547</v>
+        <v>-14.3724202836356</v>
       </c>
       <c r="L19" s="4" t="n">
-        <v>-12.14131893140184</v>
+        <v>-11.50087340209701</v>
       </c>
       <c r="M19" s="4" t="n">
-        <v>-8.69503742283046</v>
+        <v>-8.008670013868915</v>
       </c>
       <c r="N19" s="4" t="n">
-        <v>-8.663503435557686</v>
+        <v>-7.953130550378255</v>
       </c>
       <c r="O19" s="4" t="n">
-        <v>-7.86734999847895</v>
+        <v>-7.116695289158258</v>
       </c>
       <c r="P19" s="4" t="n">
-        <v>-6.424982053122754</v>
+        <v>-5.635699342939091</v>
       </c>
     </row>
     <row r="20">
@@ -1303,46 +1303,46 @@
         <v>92</v>
       </c>
       <c r="C20" s="4" t="n">
-        <v>7.27284079010446</v>
+        <v>7.061435522660965</v>
       </c>
       <c r="D20" s="4" t="n">
-        <v>5.672118976069697</v>
+        <v>5.350054720818839</v>
       </c>
       <c r="E20" s="4" t="n">
-        <v>8.528701580564352</v>
+        <v>9.28654767195664</v>
       </c>
       <c r="F20" s="4" t="n">
-        <v>6.494438232260016</v>
+        <v>8.338332888947676</v>
       </c>
       <c r="G20" s="4" t="n">
-        <v>0.540591585222181</v>
+        <v>1.912116779075852</v>
       </c>
       <c r="H20" s="4" t="n">
-        <v>-0.2463319304363409</v>
+        <v>2.186600546870004</v>
       </c>
       <c r="I20" s="4" t="n">
-        <v>-2.499810782641838</v>
+        <v>0.5476076586598282</v>
       </c>
       <c r="J20" s="4" t="n">
-        <v>-5.136603762606761</v>
+        <v>-3.672169764492459</v>
       </c>
       <c r="K20" s="4" t="n">
-        <v>-6.285210112123188</v>
+        <v>-5.263995477753745</v>
       </c>
       <c r="L20" s="4" t="n">
-        <v>-7.136376816220604</v>
+        <v>-6.572648200822215</v>
       </c>
       <c r="M20" s="4" t="n">
-        <v>-8.429675802745159</v>
+        <v>-8.329946183559855</v>
       </c>
       <c r="N20" s="4" t="n">
-        <v>-6.225738949886328</v>
+        <v>-6.102178523889954</v>
       </c>
       <c r="O20" s="4" t="n">
-        <v>-9.907868272875362</v>
+        <v>-9.75926238567871</v>
       </c>
       <c r="P20" s="4" t="n">
-        <v>-10.77280814007928</v>
+        <v>-10.60080938051262</v>
       </c>
     </row>
     <row r="21">
@@ -1352,205 +1352,205 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="C21" s="4" t="n">
-        <v>-0.8415603566054202</v>
+        <v>-1.229538658649339</v>
       </c>
       <c r="D21" s="4" t="n">
-        <v>1.461069879139743</v>
+        <v>1.104351877618257</v>
       </c>
       <c r="E21" s="4" t="n">
-        <v>2.36915019385544</v>
+        <v>2.024530844019395</v>
       </c>
       <c r="F21" s="4" t="n">
-        <v>9.013233691604427</v>
+        <v>8.43353205113938</v>
       </c>
       <c r="G21" s="4" t="n">
-        <v>8.479721127472516</v>
+        <v>7.940802370648299</v>
       </c>
       <c r="H21" s="4" t="n">
-        <v>8.779717700334707</v>
+        <v>8.213781252774986</v>
       </c>
       <c r="I21" s="4" t="n">
-        <v>11.95848067539684</v>
+        <v>11.43858133764127</v>
       </c>
       <c r="J21" s="4" t="n">
-        <v>11.49644773630212</v>
+        <v>11.62632059987518</v>
       </c>
       <c r="K21" s="4" t="n">
-        <v>10.78616761603715</v>
+        <v>10.93306888181255</v>
       </c>
       <c r="L21" s="4" t="n">
-        <v>7.982761312652059</v>
+        <v>8.131701625371633</v>
       </c>
       <c r="M21" s="4" t="n">
-        <v>10.39205288636312</v>
+        <v>10.55712496961698</v>
       </c>
       <c r="N21" s="4" t="n">
-        <v>8.470334880063668</v>
+        <v>8.36188208249235</v>
       </c>
       <c r="O21" s="4" t="n">
-        <v>8.052955387384841</v>
+        <v>7.969457757098148</v>
       </c>
       <c r="P21" s="4" t="n">
-        <v>10.2416846135439</v>
+        <v>9.536490390654585</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>X ≈ -0.2339</t>
+          <t>X ≈ -0.2338</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>132</v>
+        <v>137</v>
       </c>
       <c r="C22" s="4" t="n">
-        <v>1.929285082479851</v>
+        <v>2.534601322221256</v>
       </c>
       <c r="D22" s="4" t="n">
-        <v>2.156425422057701</v>
+        <v>2.038425254683425</v>
       </c>
       <c r="E22" s="4" t="n">
-        <v>-5.043091607727149</v>
+        <v>-5.251126153054123</v>
       </c>
       <c r="F22" s="4" t="n">
-        <v>-3.730988248195423</v>
+        <v>-4.388940621646746</v>
       </c>
       <c r="G22" s="4" t="n">
-        <v>-5.045212901240028</v>
+        <v>-5.612171134689497</v>
       </c>
       <c r="H22" s="4" t="n">
-        <v>-4.329444091733606</v>
+        <v>-5.339145632742344</v>
       </c>
       <c r="I22" s="4" t="n">
-        <v>-3.242103678352002</v>
+        <v>-4.671099978700113</v>
       </c>
       <c r="J22" s="4" t="n">
-        <v>-3.719901303831492</v>
+        <v>-5.141492418521892</v>
       </c>
       <c r="K22" s="4" t="n">
-        <v>-2.266925713836557</v>
+        <v>-3.717941760455595</v>
       </c>
       <c r="L22" s="4" t="n">
-        <v>-5.404305055908935</v>
+        <v>-6.737954862462644</v>
       </c>
       <c r="M22" s="4" t="n">
-        <v>-7.124160955474906</v>
+        <v>-7.671037036394488</v>
       </c>
       <c r="N22" s="4" t="n">
-        <v>-6.339017583920835</v>
+        <v>-6.884888505147273</v>
       </c>
       <c r="O22" s="4" t="n">
-        <v>-6.332625414454206</v>
+        <v>-7.593688659527757</v>
       </c>
       <c r="P22" s="4" t="n">
-        <v>-5.667406295546996</v>
+        <v>-7.347873804504992</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>X ≈ -0.2152</t>
+          <t>X ≈ -0.215</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>171</v>
+        <v>175</v>
       </c>
       <c r="C23" s="4" t="n">
-        <v>-2.251399717533175</v>
+        <v>-2.526209867157363</v>
       </c>
       <c r="D23" s="4" t="n">
-        <v>4.853130490887942</v>
+        <v>5.021630340100202</v>
       </c>
       <c r="E23" s="4" t="n">
-        <v>7.693270527626105</v>
+        <v>7.482958042183583</v>
       </c>
       <c r="F23" s="4" t="n">
-        <v>6.662405528202129</v>
+        <v>6.472477540634564</v>
       </c>
       <c r="G23" s="4" t="n">
-        <v>5.852829515019451</v>
+        <v>5.407853211439374</v>
       </c>
       <c r="H23" s="4" t="n">
-        <v>8.48704322994648</v>
+        <v>7.966560732647174</v>
       </c>
       <c r="I23" s="4" t="n">
-        <v>5.480613713100837</v>
+        <v>4.476710064826761</v>
       </c>
       <c r="J23" s="4" t="n">
-        <v>6.503331212181678</v>
+        <v>5.149787830485863</v>
       </c>
       <c r="K23" s="4" t="n">
-        <v>4.692579264839345</v>
+        <v>3.971412095213303</v>
       </c>
       <c r="L23" s="4" t="n">
-        <v>6.760309847993476</v>
+        <v>5.997871721283964</v>
       </c>
       <c r="M23" s="4" t="n">
-        <v>6.558050555720705</v>
+        <v>5.222718135668238</v>
       </c>
       <c r="N23" s="4" t="n">
-        <v>4.003351278619093</v>
+        <v>2.42249571584361</v>
       </c>
       <c r="O23" s="4" t="n">
-        <v>7.09197235513038</v>
+        <v>5.450924017664448</v>
       </c>
       <c r="P23" s="4" t="n">
-        <v>7.317708005356913</v>
+        <v>6.604159563586762</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>X ≈ -0.1965</t>
+          <t>X ≈ -0.1963</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>167</v>
+        <v>169</v>
       </c>
       <c r="C24" s="4" t="n">
-        <v>-1.337008194033452</v>
+        <v>-1.030821884058582</v>
       </c>
       <c r="D24" s="4" t="n">
-        <v>-4.773890720317652</v>
+        <v>-4.980862874539881</v>
       </c>
       <c r="E24" s="4" t="n">
-        <v>-2.17813694421443</v>
+        <v>-2.416020981197775</v>
       </c>
       <c r="F24" s="4" t="n">
-        <v>-2.040938170247195</v>
+        <v>-2.286136939983095</v>
       </c>
       <c r="G24" s="4" t="n">
-        <v>0.4008369919470098</v>
+        <v>0.1831938007217886</v>
       </c>
       <c r="H24" s="4" t="n">
-        <v>-2.292314139276165</v>
+        <v>-2.502600562116086</v>
       </c>
       <c r="I24" s="4" t="n">
-        <v>-3.580208193264589</v>
+        <v>-3.154972627672912</v>
       </c>
       <c r="J24" s="4" t="n">
-        <v>1.928891943400068</v>
+        <v>2.296354375257494</v>
       </c>
       <c r="K24" s="4" t="n">
-        <v>3.402313752268689</v>
+        <v>2.85109774245192</v>
       </c>
       <c r="L24" s="4" t="n">
-        <v>4.077755216023739</v>
+        <v>3.21070111429966</v>
       </c>
       <c r="M24" s="4" t="n">
-        <v>3.615294518567019</v>
+        <v>3.006560666763569</v>
       </c>
       <c r="N24" s="4" t="n">
-        <v>3.6496726709222</v>
+        <v>3.064727404128462</v>
       </c>
       <c r="O24" s="4" t="n">
-        <v>0.8343122367703373</v>
+        <v>0.3027055722389278</v>
       </c>
       <c r="P24" s="4" t="n">
-        <v>-1.335161693841449</v>
+        <v>-2.406829447402245</v>
       </c>
     </row>
     <row r="25">
@@ -1560,49 +1560,49 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="C25" s="4" t="n">
-        <v>-5.422092501122592</v>
+        <v>-5.107514422289583</v>
       </c>
       <c r="D25" s="4" t="n">
-        <v>-3.765304737977409</v>
+        <v>-3.443938260692335</v>
       </c>
       <c r="E25" s="4" t="n">
-        <v>-6.120860436457946</v>
+        <v>-6.435078846409489</v>
       </c>
       <c r="F25" s="4" t="n">
-        <v>-7.951419606594776</v>
+        <v>-7.603896103896112</v>
       </c>
       <c r="G25" s="4" t="n">
-        <v>-6.528924845965278</v>
+        <v>-6.794443946146728</v>
       </c>
       <c r="H25" s="4" t="n">
-        <v>-8.84592990129736</v>
+        <v>-8.469710375379599</v>
       </c>
       <c r="I25" s="4" t="n">
-        <v>-9.584235031805505</v>
+        <v>-9.829067763306512</v>
       </c>
       <c r="J25" s="4" t="n">
-        <v>-8.090519361866612</v>
+        <v>-8.346848575637907</v>
       </c>
       <c r="K25" s="4" t="n">
-        <v>-8.805096289631066</v>
+        <v>-9.033171834125199</v>
       </c>
       <c r="L25" s="4" t="n">
-        <v>-8.347825543477263</v>
+        <v>-8.558299116239034</v>
       </c>
       <c r="M25" s="4" t="n">
-        <v>-8.552526701737605</v>
+        <v>-8.762439563775125</v>
       </c>
       <c r="N25" s="4" t="n">
-        <v>-8.518148549382133</v>
+        <v>-8.054922177059581</v>
       </c>
       <c r="O25" s="4" t="n">
-        <v>-6.977515088970051</v>
+        <v>-6.502028155571317</v>
       </c>
       <c r="P25" s="4" t="n">
-        <v>-8.712563752469158</v>
+        <v>-8.201035241608039</v>
       </c>
     </row>
     <row r="26">
@@ -1612,153 +1612,153 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="C26" s="4" t="n">
-        <v>1.735951439345165</v>
+        <v>1.429282114506961</v>
       </c>
       <c r="D26" s="4" t="n">
-        <v>-2.887282846489477</v>
+        <v>-3.184198000951653</v>
       </c>
       <c r="E26" s="4" t="n">
-        <v>-2.679644592690437</v>
+        <v>-2.365814777145417</v>
       </c>
       <c r="F26" s="4" t="n">
-        <v>1.667448020777172</v>
+        <v>1.400432900432904</v>
       </c>
       <c r="G26" s="4" t="n">
-        <v>3.538797021898489</v>
+        <v>3.941486789783866</v>
       </c>
       <c r="H26" s="4" t="n">
-        <v>4.43858069008779</v>
+        <v>4.214272308602794</v>
       </c>
       <c r="I26" s="4" t="n">
-        <v>4.353870330821756</v>
+        <v>4.759676825438085</v>
       </c>
       <c r="J26" s="4" t="n">
-        <v>0.272343855709444</v>
+        <v>0.6574804286909597</v>
       </c>
       <c r="K26" s="4" t="n">
-        <v>-2.80068649358455</v>
+        <v>-2.409795210748996</v>
       </c>
       <c r="L26" s="4" t="n">
-        <v>-3.650605289914147</v>
+        <v>-3.233623791563566</v>
       </c>
       <c r="M26" s="4" t="n">
-        <v>-3.252896809620111</v>
+        <v>-2.83170363303919</v>
       </c>
       <c r="N26" s="4" t="n">
-        <v>-2.013699380156496</v>
+        <v>-2.167476289613688</v>
       </c>
       <c r="O26" s="4" t="n">
-        <v>-4.843488787686503</v>
+        <v>-4.986876640419801</v>
       </c>
       <c r="P26" s="4" t="n">
-        <v>-3.412933860351806</v>
+        <v>-3.5257105662835</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>X ≈ -0.1404</t>
+          <t>X ≈ -0.1402</t>
         </is>
       </c>
       <c r="B27" t="n">
         <v>162</v>
       </c>
       <c r="C27" s="4" t="n">
-        <v>-6.80190368485534</v>
+        <v>-6.831099479207971</v>
       </c>
       <c r="D27" s="4" t="n">
-        <v>0.846169481339949</v>
+        <v>0.8449826948952932</v>
       </c>
       <c r="E27" s="4" t="n">
-        <v>1.068682047202195</v>
+        <v>1.068528657197874</v>
       </c>
       <c r="F27" s="4" t="n">
-        <v>-2.504796512912868</v>
+        <v>-2.505291005290871</v>
       </c>
       <c r="G27" s="4" t="n">
-        <v>0.04333368707786178</v>
+        <v>0.09187960684363361</v>
       </c>
       <c r="H27" s="4" t="n">
-        <v>0.9579916673300914</v>
+        <v>0.9819490762797045</v>
       </c>
       <c r="I27" s="4" t="n">
-        <v>-3.447706346257206</v>
+        <v>-3.399694667266886</v>
       </c>
       <c r="J27" s="4" t="n">
-        <v>-4.532058940660953</v>
+        <v>-4.482811378267236</v>
       </c>
       <c r="K27" s="4" t="n">
-        <v>-5.210325047800872</v>
+        <v>-5.137067938021175</v>
       </c>
       <c r="L27" s="4" t="n">
-        <v>-5.442959893513724</v>
+        <v>-5.34361256821915</v>
       </c>
       <c r="M27" s="4" t="n">
-        <v>-6.264945002391201</v>
+        <v>-6.165036966372526</v>
       </c>
       <c r="N27" s="4" t="n">
-        <v>-8.69970265250501</v>
+        <v>-8.576006031476766</v>
       </c>
       <c r="O27" s="4" t="n">
-        <v>-7.268001653966714</v>
+        <v>-7.119312106188886</v>
       </c>
       <c r="P27" s="4" t="n">
-        <v>-6.424982053122754</v>
+        <v>-6.252983293556092</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>X ≈ -0.1216</t>
+          <t>X ≈ -0.1215</t>
         </is>
       </c>
       <c r="B28" t="n">
         <v>175</v>
       </c>
       <c r="C28" s="4" t="n">
-        <v>2.947655398037078</v>
+        <v>2.918459603684447</v>
       </c>
       <c r="D28" s="4" t="n">
-        <v>-2.092102123598245</v>
+        <v>-2.093288910042901</v>
       </c>
       <c r="E28" s="4" t="n">
-        <v>-2.486873508353085</v>
+        <v>-2.487026898357406</v>
       </c>
       <c r="F28" s="4" t="n">
-        <v>-0.6423626504792068</v>
+        <v>-0.6428571428572099</v>
       </c>
       <c r="G28" s="4" t="n">
-        <v>0.533633510710942</v>
+        <v>0.5821794304767138</v>
       </c>
       <c r="H28" s="4" t="n">
-        <v>1.402436111774598</v>
+        <v>1.426393520724211</v>
       </c>
       <c r="I28" s="4" t="n">
-        <v>-2.110845676062929</v>
+        <v>-2.062833997072609</v>
       </c>
       <c r="J28" s="4" t="n">
-        <v>-1.435057176992657</v>
+        <v>-1.385809614598941</v>
       </c>
       <c r="K28" s="4" t="n">
-        <v>-0.3531821906584227</v>
+        <v>-0.2799250808787264</v>
       </c>
       <c r="L28" s="4" t="n">
-        <v>-0.6316724155598337</v>
+        <v>-0.5323250902652603</v>
       </c>
       <c r="M28" s="4" t="n">
-        <v>2.592197854751653</v>
+        <v>2.692105890770328</v>
       </c>
       <c r="N28" s="4" t="n">
-        <v>2.055147435678407</v>
+        <v>2.178844056706652</v>
       </c>
       <c r="O28" s="4" t="n">
-        <v>2.206425153793703</v>
+        <v>2.35511470157153</v>
       </c>
       <c r="P28" s="4" t="n">
-        <v>5.289303661163089</v>
+        <v>5.461302420729751</v>
       </c>
     </row>
     <row r="29">
@@ -1768,205 +1768,205 @@
         </is>
       </c>
       <c r="B29" t="n">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="C29" s="4" t="n">
-        <v>4.004439618001207</v>
+        <v>4.156554841779638</v>
       </c>
       <c r="D29" s="4" t="n">
-        <v>4.066893692301491</v>
+        <v>4.240044423290591</v>
       </c>
       <c r="E29" s="4" t="n">
-        <v>2.835302223864353</v>
+        <v>3.012973101642451</v>
       </c>
       <c r="F29" s="4" t="n">
-        <v>-3.310623260162394</v>
+        <v>-3.107142857142911</v>
       </c>
       <c r="G29" s="4" t="n">
-        <v>-1.756862604053069</v>
+        <v>-1.513058664761537</v>
       </c>
       <c r="H29" s="4" t="n">
-        <v>0.214151592946088</v>
+        <v>0.4263935207240976</v>
       </c>
       <c r="I29" s="4" t="n">
-        <v>3.058311526566939</v>
+        <v>3.282404098165401</v>
       </c>
       <c r="J29" s="4" t="n">
-        <v>3.846473008303221</v>
+        <v>4.066571337782008</v>
       </c>
       <c r="K29" s="4" t="n">
-        <v>5.040720977303458</v>
+        <v>5.279598728645212</v>
       </c>
       <c r="L29" s="4" t="n">
-        <v>5.864442348337704</v>
+        <v>6.122436814496986</v>
       </c>
       <c r="M29" s="4" t="n">
-        <v>6.496561273759426</v>
+        <v>6.751629700294139</v>
       </c>
       <c r="N29" s="4" t="n">
-        <v>6.530939426114706</v>
+        <v>6.809796437659031</v>
       </c>
       <c r="O29" s="4" t="n">
-        <v>7.784428740165254</v>
+        <v>8.081305177761784</v>
       </c>
       <c r="P29" s="4" t="n">
-        <v>7.591754348550886</v>
+        <v>7.913683373110523</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>X ≈ -0.08418</t>
+          <t>X ≈ -0.08416</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="C30" s="4" t="n">
-        <v>-8.480916030534303</v>
+        <v>-8.760111824886884</v>
       </c>
       <c r="D30" s="4" t="n">
-        <v>-5.203213234709345</v>
+        <v>-5.432574624328602</v>
       </c>
       <c r="E30" s="4" t="n">
-        <v>-3.820206841686549</v>
+        <v>-4.040598326928972</v>
       </c>
       <c r="F30" s="4" t="n">
-        <v>-5.023315031431522</v>
+        <v>-5.250000000000007</v>
       </c>
       <c r="G30" s="4" t="n">
-        <v>-1.117160140082774</v>
+        <v>-1.274963426666154</v>
       </c>
       <c r="H30" s="4" t="n">
-        <v>-3.486452777114401</v>
+        <v>-3.680749336418714</v>
       </c>
       <c r="I30" s="4" t="n">
-        <v>-2.237829803047184</v>
+        <v>-2.402119711358509</v>
       </c>
       <c r="J30" s="4" t="n">
-        <v>-2.704898446833923</v>
+        <v>-2.867952471741795</v>
       </c>
       <c r="K30" s="4" t="n">
-        <v>-4.099213936690042</v>
+        <v>-4.244210795164314</v>
       </c>
       <c r="L30" s="4" t="n">
-        <v>-3.615799399686559</v>
+        <v>-3.728753661693574</v>
       </c>
       <c r="M30" s="4" t="n">
-        <v>-5.153833891280094</v>
+        <v>-5.272179823515387</v>
       </c>
       <c r="N30" s="4" t="n">
-        <v>-2.897233516702492</v>
+        <v>-2.981870229007633</v>
       </c>
       <c r="O30" s="4" t="n">
-        <v>-1.984051036682665</v>
+        <v>-2.037742441285793</v>
       </c>
       <c r="P30" s="4" t="n">
-        <v>-2.647204275344976</v>
+        <v>-2.681554722127466</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>X ≈ -0.06548</t>
+          <t>X ≈ -0.06546</t>
         </is>
       </c>
       <c r="B31" t="n">
         <v>221</v>
       </c>
       <c r="C31" s="4" t="n">
-        <v>-0.8972056232945818</v>
+        <v>-0.9264014176472131</v>
       </c>
       <c r="D31" s="4" t="n">
-        <v>-1.150925653009942</v>
+        <v>-1.152112439454598</v>
       </c>
       <c r="E31" s="4" t="n">
-        <v>-2.450674413330646</v>
+        <v>-2.450827803334967</v>
       </c>
       <c r="F31" s="4" t="n">
-        <v>2.204437608085819</v>
+        <v>2.203943115707816</v>
       </c>
       <c r="G31" s="4" t="n">
-        <v>-2.858738822837921</v>
+        <v>-2.810192903072149</v>
       </c>
       <c r="H31" s="4" t="n">
-        <v>-3.918830856551203</v>
+        <v>-3.89487344760159</v>
       </c>
       <c r="I31" s="4" t="n">
-        <v>-4.003541215817428</v>
+        <v>-3.955529536827108</v>
       </c>
       <c r="J31" s="4" t="n">
-        <v>-4.923098547386971</v>
+        <v>-4.873850984993254</v>
       </c>
       <c r="K31" s="4" t="n">
-        <v>-6.794035455041019</v>
+        <v>-6.720778345261323</v>
       </c>
       <c r="L31" s="4" t="n">
-        <v>-4.476533436891181</v>
+        <v>-4.377186111596608</v>
       </c>
       <c r="M31" s="4" t="n">
-        <v>-6.491189346282603</v>
+        <v>-6.391281310263928</v>
       </c>
       <c r="N31" s="4" t="n">
-        <v>-7.361788569492894</v>
+        <v>-7.23809194846465</v>
       </c>
       <c r="O31" s="4" t="n">
-        <v>-6.876962047240639</v>
+        <v>-6.728272499462811</v>
       </c>
       <c r="P31" s="4" t="n">
-        <v>-8.008692460362575</v>
+        <v>-7.836693700795912</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>X ≈ -0.04677</t>
+          <t>X ≈ -0.04676</t>
         </is>
       </c>
       <c r="B32" t="n">
         <v>232</v>
       </c>
       <c r="C32" s="4" t="n">
-        <v>2.691497762569092</v>
+        <v>2.662301968216461</v>
       </c>
       <c r="D32" s="4" t="n">
-        <v>1.942380635022502</v>
+        <v>1.941193848577846</v>
       </c>
       <c r="E32" s="4" t="n">
-        <v>-0.1765286807669639</v>
+        <v>-0.1766820707712853</v>
       </c>
       <c r="F32" s="4" t="n">
-        <v>-3.925613882006239</v>
+        <v>-3.926108374384242</v>
       </c>
       <c r="G32" s="4" t="n">
-        <v>-4.894937917860553</v>
+        <v>-4.846391998094781</v>
       </c>
       <c r="H32" s="4" t="n">
-        <v>-4.597563888225537</v>
+        <v>-4.573606479275924</v>
       </c>
       <c r="I32" s="4" t="n">
-        <v>-3.820205281974395</v>
+        <v>-3.772193602984075</v>
       </c>
       <c r="J32" s="4" t="n">
-        <v>-0.8389980636921663</v>
+        <v>-0.7897505012984496</v>
       </c>
       <c r="K32" s="4" t="n">
-        <v>-0.4689457374562735</v>
+        <v>-0.3956886276765772</v>
       </c>
       <c r="L32" s="4" t="n">
-        <v>-1.318864533786183</v>
+        <v>-1.219517208491609</v>
       </c>
       <c r="M32" s="4" t="n">
-        <v>-0.2304622437705177</v>
+        <v>-0.1305542077518425</v>
       </c>
       <c r="N32" s="4" t="n">
-        <v>-2.351256505208283</v>
+        <v>-2.227559884180039</v>
       </c>
       <c r="O32" s="4" t="n">
-        <v>-1.909338393004411</v>
+        <v>-1.760648845226584</v>
       </c>
       <c r="P32" s="4" t="n">
-        <v>-4.269809639329651</v>
+        <v>-4.097810879762989</v>
       </c>
     </row>
     <row r="33">
@@ -1979,52 +1979,52 @@
         <v>225</v>
       </c>
       <c r="C33" s="4" t="n">
-        <v>7.96352841391009</v>
+        <v>7.934332619557459</v>
       </c>
       <c r="D33" s="4" t="n">
-        <v>6.352342320846262</v>
+        <v>6.351155534401606</v>
       </c>
       <c r="E33" s="4" t="n">
-        <v>3.290904269424587</v>
+        <v>3.290750879420266</v>
       </c>
       <c r="F33" s="4" t="n">
-        <v>6.532240524124035</v>
+        <v>6.531746031746032</v>
       </c>
       <c r="G33" s="4" t="n">
-        <v>3.771728748806133</v>
+        <v>3.820274668571905</v>
       </c>
       <c r="H33" s="4" t="n">
-        <v>5.402436111774556</v>
+        <v>5.426393520724169</v>
       </c>
       <c r="I33" s="4" t="n">
-        <v>10.20661464139725</v>
+        <v>10.25462632038757</v>
       </c>
       <c r="J33" s="4" t="n">
-        <v>9.29510155316607</v>
+        <v>9.344349115559787</v>
       </c>
       <c r="K33" s="4" t="n">
-        <v>7.011897174421073</v>
+        <v>7.085154284200769</v>
       </c>
       <c r="L33" s="4" t="n">
-        <v>7.050867266980099</v>
+        <v>7.150214592274672</v>
       </c>
       <c r="M33" s="4" t="n">
-        <v>6.846166108719906</v>
+        <v>6.946074144738581</v>
       </c>
       <c r="N33" s="4" t="n">
-        <v>6.880544261075229</v>
+        <v>7.004240882103474</v>
       </c>
       <c r="O33" s="4" t="n">
-        <v>6.904837852206192</v>
+        <v>7.05352739998402</v>
       </c>
       <c r="P33" s="4" t="n">
-        <v>8.463906835766103</v>
+        <v>8.635905595332765</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>X ≈ -0.009355</t>
+          <t>X ≈ -0.00935</t>
         </is>
       </c>
       <c r="B34" t="n">
@@ -2182,573 +2182,573 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>X &gt; -0.5425</t>
+          <t>X &gt; -0.5424</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>3978</v>
+        <v>3989</v>
       </c>
       <c r="C6" s="4" t="n">
-        <v>0.01219346583247471</v>
+        <v>0.01362630604754145</v>
       </c>
       <c r="D6" s="4" t="n">
-        <v>0.01817356562487049</v>
+        <v>0.01818322192416844</v>
       </c>
       <c r="E6" s="4" t="n">
-        <v>-0.0622056718027082</v>
+        <v>-0.06202689835753716</v>
       </c>
       <c r="F6" s="4" t="n">
-        <v>0.006440903038551937</v>
+        <v>0.006448040581574332</v>
       </c>
       <c r="G6" s="4" t="n">
-        <v>-0.1169093249335447</v>
+        <v>-0.1190283162538535</v>
       </c>
       <c r="H6" s="4" t="n">
-        <v>-0.08175856961031513</v>
+        <v>-0.08273832816251314</v>
       </c>
       <c r="I6" s="4" t="n">
-        <v>-0.07750636794332166</v>
+        <v>-0.07970801394675675</v>
       </c>
       <c r="J6" s="4" t="n">
-        <v>-0.2045637748125131</v>
+        <v>-0.2064783076080587</v>
       </c>
       <c r="K6" s="4" t="n">
-        <v>-0.07600418413054655</v>
+        <v>-0.0794815584520947</v>
       </c>
       <c r="L6" s="4" t="n">
-        <v>-0.2089128546784664</v>
+        <v>-0.2133382919393725</v>
       </c>
       <c r="M6" s="4" t="n">
-        <v>-0.1986300061590995</v>
+        <v>-0.2031131186771304</v>
       </c>
       <c r="N6" s="4" t="n">
-        <v>-0.07478795556351514</v>
+        <v>-0.08081159708580543</v>
       </c>
       <c r="O6" s="4" t="n">
-        <v>-0.05358274481699254</v>
+        <v>-0.06092539867923108</v>
       </c>
       <c r="P6" s="4" t="n">
-        <v>-0.06500216373110135</v>
+        <v>-0.07348968613568729</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>X &gt; -0.5238</t>
+          <t>X &gt; -0.5237</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>3956</v>
+        <v>3967</v>
       </c>
       <c r="C7" s="4" t="n">
-        <v>0.02601266687053538</v>
+        <v>0.02757661732406547</v>
       </c>
       <c r="D7" s="4" t="n">
-        <v>0.06616400543408218</v>
+        <v>0.06604760666990472</v>
       </c>
       <c r="E7" s="4" t="n">
-        <v>0.06316430359535019</v>
+        <v>0.062998239902889</v>
       </c>
       <c r="F7" s="4" t="n">
-        <v>0.05585793881557066</v>
+        <v>0.05573116850461446</v>
       </c>
       <c r="G7" s="4" t="n">
-        <v>-0.03995683337127076</v>
+        <v>-0.04256906046902742</v>
       </c>
       <c r="H7" s="4" t="n">
-        <v>-0.03146903454231875</v>
+        <v>-0.03272597613120354</v>
       </c>
       <c r="I7" s="4" t="n">
-        <v>-0.02671028079973325</v>
+        <v>-0.02933051012185217</v>
       </c>
       <c r="J7" s="4" t="n">
-        <v>-0.1518668690673692</v>
+        <v>-0.1542106070120184</v>
       </c>
       <c r="K7" s="4" t="n">
-        <v>-0.04748738054539814</v>
+        <v>-0.05146874366092646</v>
       </c>
       <c r="L7" s="4" t="n">
-        <v>-0.2269105107976728</v>
+        <v>-0.2318610114075739</v>
       </c>
       <c r="M7" s="4" t="n">
-        <v>-0.2154375510145883</v>
+        <v>-0.2204525835009932</v>
       </c>
       <c r="N7" s="4" t="n">
-        <v>-0.09110247408843009</v>
+        <v>-0.09779993422305466</v>
       </c>
       <c r="O7" s="4" t="n">
-        <v>-0.09271921964951702</v>
+        <v>-0.1008184781521066</v>
       </c>
       <c r="P7" s="4" t="n">
-        <v>-0.1054673918487339</v>
+        <v>-0.1148436414260203</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>X &gt; -0.5051</t>
+          <t>X &gt; -0.505</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>3936</v>
+        <v>3947</v>
       </c>
       <c r="C8" s="4" t="n">
-        <v>0.08935492413771584</v>
+        <v>0.09089827612312007</v>
       </c>
       <c r="D8" s="4" t="n">
-        <v>0.08722918339270791</v>
+        <v>0.08705966282910538</v>
       </c>
       <c r="E8" s="4" t="n">
-        <v>0.03554858437543373</v>
+        <v>0.03545920573542816</v>
       </c>
       <c r="F8" s="4" t="n">
-        <v>0.07822239043026968</v>
+        <v>0.07803530813386317</v>
       </c>
       <c r="G8" s="4" t="n">
-        <v>-0.06604057945751407</v>
+        <v>-0.06883891417162147</v>
       </c>
       <c r="H8" s="4" t="n">
-        <v>-0.0590243344729231</v>
+        <v>-0.06033214299266376</v>
       </c>
       <c r="I8" s="4" t="n">
-        <v>-0.05381875674854797</v>
+        <v>-0.05661967522867428</v>
       </c>
       <c r="J8" s="4" t="n">
-        <v>-0.1518796746370796</v>
+        <v>-0.1544844004758517</v>
       </c>
       <c r="K8" s="4" t="n">
-        <v>-0.09740954412187364</v>
+        <v>-0.1016428368068816</v>
       </c>
       <c r="L8" s="4" t="n">
-        <v>-0.273441813674161</v>
+        <v>-0.2787907228354243</v>
       </c>
       <c r="M8" s="4" t="n">
-        <v>-0.2862702118352161</v>
+        <v>-0.2916192448535355</v>
       </c>
       <c r="N8" s="4" t="n">
-        <v>-0.1361026550130262</v>
+        <v>-0.1433351568374661</v>
       </c>
       <c r="O8" s="4" t="n">
-        <v>-0.08480457152302279</v>
+        <v>-0.09372015151877378</v>
       </c>
       <c r="P8" s="4" t="n">
-        <v>-0.1241690449926764</v>
+        <v>-0.1344122269232102</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>X &gt; -0.4864</t>
+          <t>X &gt; -0.4863</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>3897</v>
+        <v>3908</v>
       </c>
       <c r="C9" s="4" t="n">
-        <v>-9.76162121020252e-05</v>
+        <v>0.002002431680217853</v>
       </c>
       <c r="D9" s="4" t="n">
-        <v>0.09055328699275833</v>
+        <v>0.09038455934491196</v>
       </c>
       <c r="E9" s="4" t="n">
-        <v>-0.08564525860910521</v>
+        <v>-0.08539382869691536</v>
       </c>
       <c r="F9" s="4" t="n">
-        <v>0.007313754508246006</v>
+        <v>0.007328812076131896</v>
       </c>
       <c r="G9" s="4" t="n">
-        <v>-0.2098380714703794</v>
+        <v>-0.2127437979416058</v>
       </c>
       <c r="H9" s="4" t="n">
-        <v>-0.2313667051268666</v>
+        <v>-0.2324420257518511</v>
       </c>
       <c r="I9" s="4" t="n">
-        <v>-0.2253070343768826</v>
+        <v>-0.2281323003020788</v>
       </c>
       <c r="J9" s="4" t="n">
-        <v>-0.2941033319650188</v>
+        <v>-0.2968250171830746</v>
       </c>
       <c r="K9" s="4" t="n">
-        <v>-0.2897714855253923</v>
+        <v>-0.2942363510038177</v>
       </c>
       <c r="L9" s="4" t="n">
-        <v>-0.5103848336208827</v>
+        <v>-0.5161112427628183</v>
       </c>
       <c r="M9" s="4" t="n">
-        <v>-0.5213552588014636</v>
+        <v>-0.5270927065924198</v>
       </c>
       <c r="N9" s="4" t="n">
-        <v>-0.3444422026904093</v>
+        <v>-0.3523945256828185</v>
       </c>
       <c r="O9" s="4" t="n">
-        <v>-0.3397890219742266</v>
+        <v>-0.3495594935095525</v>
       </c>
       <c r="P9" s="4" t="n">
-        <v>-0.3818719684422263</v>
+        <v>-0.3932084726758447</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>X &gt; -0.4677</t>
+          <t>X &gt; -0.4676</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>3841</v>
+        <v>3852</v>
       </c>
       <c r="C10" s="4" t="n">
-        <v>-0.1197328442343988</v>
+        <v>-0.1168388624031564</v>
       </c>
       <c r="D10" s="4" t="n">
-        <v>0.07348313464215295</v>
+        <v>0.07337775662382739</v>
       </c>
       <c r="E10" s="4" t="n">
-        <v>-0.2033844117800072</v>
+        <v>-0.2027918478786432</v>
       </c>
       <c r="F10" s="4" t="n">
-        <v>-0.1629324468214719</v>
+        <v>-0.1624250943256698</v>
       </c>
       <c r="G10" s="4" t="n">
-        <v>-0.2975353204579534</v>
+        <v>-0.3009374526402411</v>
       </c>
       <c r="H10" s="4" t="n">
-        <v>-0.1938226567367636</v>
+        <v>-0.1953681373069429</v>
       </c>
       <c r="I10" s="4" t="n">
-        <v>-0.3163698815872706</v>
+        <v>-0.3196732966692295</v>
       </c>
       <c r="J10" s="4" t="n">
-        <v>-0.2754151553802728</v>
+        <v>-0.2789444735191822</v>
       </c>
       <c r="K10" s="4" t="n">
-        <v>-0.2701274398968323</v>
+        <v>-0.2757767790896395</v>
       </c>
       <c r="L10" s="4" t="n">
-        <v>-0.5335858467317891</v>
+        <v>-0.5407720375086313</v>
       </c>
       <c r="M10" s="4" t="n">
-        <v>-0.5937691439104498</v>
+        <v>-0.600834631742174</v>
       </c>
       <c r="N10" s="4" t="n">
-        <v>-0.3627552445193487</v>
+        <v>-0.372568205136325</v>
       </c>
       <c r="O10" s="4" t="n">
-        <v>-0.3519149964258048</v>
+        <v>-0.3639539276970822</v>
       </c>
       <c r="P10" s="4" t="n">
-        <v>-0.3458359974080949</v>
+        <v>-0.3599407182705221</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>X &gt; -0.449</t>
+          <t>X &gt; -0.4489</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>3781</v>
+        <v>3792</v>
       </c>
       <c r="C11" s="4" t="n">
-        <v>-0.1351068581569166</v>
+        <v>-0.1316624162141835</v>
       </c>
       <c r="D11" s="4" t="n">
-        <v>0.08664820595625855</v>
+        <v>0.08652181550920801</v>
       </c>
       <c r="E11" s="4" t="n">
-        <v>-0.03012245350089415</v>
+        <v>-0.03001927279876782</v>
       </c>
       <c r="F11" s="4" t="n">
-        <v>0.06171090719504235</v>
+        <v>0.06158412865408991</v>
       </c>
       <c r="G11" s="4" t="n">
-        <v>-0.2247532212906265</v>
+        <v>-0.2291859996733123</v>
       </c>
       <c r="H11" s="4" t="n">
-        <v>-0.09769584916502794</v>
+        <v>-0.09992226874953758</v>
       </c>
       <c r="I11" s="4" t="n">
-        <v>-0.1416195484420086</v>
+        <v>-0.1462394045107871</v>
       </c>
       <c r="J11" s="4" t="n">
-        <v>-0.03975746746004205</v>
+        <v>-0.04480306980092053</v>
       </c>
       <c r="K11" s="4" t="n">
-        <v>-0.1125965744783741</v>
+        <v>-0.1199491600388285</v>
       </c>
       <c r="L11" s="4" t="n">
-        <v>-0.2610364465088111</v>
+        <v>-0.2706963080882829</v>
       </c>
       <c r="M11" s="4" t="n">
-        <v>-0.3452832687759795</v>
+        <v>-0.3547602865306274</v>
       </c>
       <c r="N11" s="4" t="n">
-        <v>-0.1110849573581092</v>
+        <v>-0.1237389691236075</v>
       </c>
       <c r="O11" s="4" t="n">
-        <v>-0.06689961768032759</v>
+        <v>-0.08230761773860706</v>
       </c>
       <c r="P11" s="4" t="n">
-        <v>-0.06423092908148931</v>
+        <v>-0.08209721760672295</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>X &gt; -0.4303</t>
+          <t>X &gt; -0.4302</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>3717</v>
+        <v>3728</v>
       </c>
       <c r="C12" s="4" t="n">
-        <v>-0.09485704930111183</v>
+        <v>-0.09097255731147413</v>
       </c>
       <c r="D12" s="4" t="n">
-        <v>0.1047334891666338</v>
+        <v>0.1045720525240128</v>
       </c>
       <c r="E12" s="4" t="n">
-        <v>0.1000363628914158</v>
+        <v>0.0997610128486599</v>
       </c>
       <c r="F12" s="4" t="n">
-        <v>0.1107516888976008</v>
+        <v>0.1104868913857615</v>
       </c>
       <c r="G12" s="4" t="n">
-        <v>-0.1176969087354891</v>
+        <v>-0.1233521265400555</v>
       </c>
       <c r="H12" s="4" t="n">
-        <v>-0.02038268017177103</v>
+        <v>-0.0232852801323844</v>
       </c>
       <c r="I12" s="4" t="n">
-        <v>-0.06358466639603932</v>
+        <v>-0.06933619634602906</v>
       </c>
       <c r="J12" s="4" t="n">
-        <v>0.02121848395665182</v>
+        <v>0.01506267861400801</v>
       </c>
       <c r="K12" s="4" t="n">
-        <v>-0.1055426727339892</v>
+        <v>-0.1142980478526852</v>
       </c>
       <c r="L12" s="4" t="n">
-        <v>-0.1881664455822261</v>
+        <v>-0.1999104523841311</v>
       </c>
       <c r="M12" s="4" t="n">
-        <v>-0.2165579056170159</v>
+        <v>-0.2282907857239067</v>
       </c>
       <c r="N12" s="4" t="n">
-        <v>0.07489160653847904</v>
+        <v>0.05934961013446127</v>
       </c>
       <c r="O12" s="4" t="n">
-        <v>0.2078083859460378</v>
+        <v>0.1887736679737273</v>
       </c>
       <c r="P12" s="4" t="n">
-        <v>0.1529033383219627</v>
+        <v>0.1311368781177293</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>X &gt; -0.4116</t>
+          <t>X &gt; -0.4115</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>3660</v>
+        <v>3669</v>
       </c>
       <c r="C13" s="4" t="n">
-        <v>-0.01699008444123962</v>
+        <v>-0.01146978251870223</v>
       </c>
       <c r="D13" s="4" t="n">
-        <v>0.1834970049421258</v>
+        <v>0.1854396963141269</v>
       </c>
       <c r="E13" s="4" t="n">
-        <v>0.04867538840515806</v>
+        <v>0.05101657990332598</v>
       </c>
       <c r="F13" s="4" t="n">
-        <v>0.1120164853713774</v>
+        <v>0.1413621713975033</v>
       </c>
       <c r="G13" s="4" t="n">
-        <v>-0.002596680466169232</v>
+        <v>0.02038342332990339</v>
       </c>
       <c r="H13" s="4" t="n">
-        <v>0.1461656646643945</v>
+        <v>0.1721101375313339</v>
       </c>
       <c r="I13" s="4" t="n">
-        <v>0.1581948007767053</v>
+        <v>0.1807537535879149</v>
       </c>
       <c r="J13" s="4" t="n">
-        <v>0.4153052265612374</v>
+        <v>0.4373196371017443</v>
       </c>
       <c r="K13" s="4" t="n">
-        <v>0.2603434378741625</v>
+        <v>0.2793719095561187</v>
       </c>
       <c r="L13" s="4" t="n">
-        <v>0.1897561558689915</v>
+        <v>0.1784990705999903</v>
       </c>
       <c r="M13" s="4" t="n">
-        <v>0.1642114267652204</v>
+        <v>0.1802789377669143</v>
       </c>
       <c r="N13" s="4" t="n">
-        <v>0.3505363722470278</v>
+        <v>0.3627565756777358</v>
       </c>
       <c r="O13" s="4" t="n">
-        <v>0.4921394395078522</v>
+        <v>0.5006966400688668</v>
       </c>
       <c r="P13" s="4" t="n">
-        <v>0.4602638485165969</v>
+        <v>0.465468600693022</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>X &gt; -0.3929</t>
+          <t>X &gt; -0.3928</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>3582</v>
+        <v>3593</v>
       </c>
       <c r="C14" s="4" t="n">
-        <v>0.008652815084566612</v>
+        <v>0.01345999984956592</v>
       </c>
       <c r="D14" s="4" t="n">
-        <v>0.2762896404530153</v>
+        <v>0.2756431287921117</v>
       </c>
       <c r="E14" s="4" t="n">
-        <v>0.06364138171079503</v>
+        <v>0.06347254670350111</v>
       </c>
       <c r="F14" s="4" t="n">
-        <v>0.1812135506026209</v>
+        <v>0.1807422386106765</v>
       </c>
       <c r="G14" s="4" t="n">
-        <v>0.18721190113137</v>
+        <v>0.1785941207280928</v>
       </c>
       <c r="H14" s="4" t="n">
-        <v>0.3327982287661797</v>
+        <v>0.3278097939815794</v>
       </c>
       <c r="I14" s="4" t="n">
-        <v>0.2633930693097071</v>
+        <v>0.2546263203875725</v>
       </c>
       <c r="J14" s="4" t="n">
-        <v>0.5641465178632075</v>
+        <v>0.5542531012348277</v>
       </c>
       <c r="K14" s="4" t="n">
-        <v>0.3514257188562198</v>
+        <v>0.3381960975538689</v>
       </c>
       <c r="L14" s="4" t="n">
-        <v>0.2420428262538152</v>
+        <v>0.2248137953142475</v>
       </c>
       <c r="M14" s="4" t="n">
-        <v>0.1367286377761587</v>
+        <v>0.1197238790112394</v>
       </c>
       <c r="N14" s="4" t="n">
-        <v>0.2984510071069835</v>
+        <v>0.2769962522162857</v>
       </c>
       <c r="O14" s="4" t="n">
-        <v>0.5359973399105513</v>
+        <v>0.509657988001166</v>
       </c>
       <c r="P14" s="4" t="n">
-        <v>0.6101938262742266</v>
+        <v>0.5797470153779543</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>X &gt; -0.3742</t>
+          <t>X &gt; -0.3741</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>3500</v>
+        <v>3510</v>
       </c>
       <c r="C15" s="4" t="n">
-        <v>0.009832617344947892</v>
+        <v>0.001951757287301348</v>
       </c>
       <c r="D15" s="4" t="n">
-        <v>0.2928637078369007</v>
+        <v>0.2792267060843656</v>
       </c>
       <c r="E15" s="4" t="n">
-        <v>0.08447368617824935</v>
+        <v>0.07133720275009381</v>
       </c>
       <c r="F15" s="4" t="n">
-        <v>0.1447761366596438</v>
+        <v>0.1314935064935057</v>
       </c>
       <c r="G15" s="4" t="n">
-        <v>0.1919814323816809</v>
+        <v>0.1692374420870877</v>
       </c>
       <c r="H15" s="4" t="n">
-        <v>0.2485022463241293</v>
+        <v>0.2302593535837261</v>
       </c>
       <c r="I15" s="4" t="n">
-        <v>0.264974112930382</v>
+        <v>0.2420524727270035</v>
       </c>
       <c r="J15" s="4" t="n">
-        <v>0.4981186033023448</v>
+        <v>0.4744211671335421</v>
       </c>
       <c r="K15" s="4" t="n">
-        <v>0.3388903587609065</v>
+        <v>0.3110117205845242</v>
       </c>
       <c r="L15" s="4" t="n">
-        <v>0.3609890325813154</v>
+        <v>0.3282326786592975</v>
       </c>
       <c r="M15" s="4" t="n">
-        <v>0.1723944209602166</v>
+        <v>0.1401153251162341</v>
       </c>
       <c r="N15" s="4" t="n">
-        <v>0.4227740979938162</v>
+        <v>0.3851571058443</v>
       </c>
       <c r="O15" s="4" t="n">
-        <v>0.847140051577874</v>
+        <v>0.803582781483513</v>
       </c>
       <c r="P15" s="4" t="n">
-        <v>0.8893036611629626</v>
+        <v>0.8410338004609983</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>X &gt; -0.3555</t>
+          <t>X &gt; -0.3554</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>3411</v>
+        <v>3422</v>
       </c>
       <c r="C16" s="4" t="n">
-        <v>0.147588642362841</v>
+        <v>0.1536436336282989</v>
       </c>
       <c r="D16" s="4" t="n">
-        <v>0.5675531495540298</v>
+        <v>0.5660005483147614</v>
       </c>
       <c r="E16" s="4" t="n">
-        <v>0.393313516778278</v>
+        <v>0.3920875787761631</v>
       </c>
       <c r="F16" s="4" t="n">
-        <v>0.5395808079916478</v>
+        <v>0.537962037962032</v>
       </c>
       <c r="G16" s="4" t="n">
-        <v>0.5436585733675159</v>
+        <v>0.5310489812115478</v>
       </c>
       <c r="H16" s="4" t="n">
-        <v>0.5940125961266816</v>
+        <v>0.5867433749515527</v>
       </c>
       <c r="I16" s="4" t="n">
-        <v>0.7302476951648913</v>
+        <v>0.7171518380312065</v>
       </c>
       <c r="J16" s="4" t="n">
-        <v>0.8354390812121224</v>
+        <v>0.8217249744992401</v>
       </c>
       <c r="K16" s="4" t="n">
-        <v>0.6444758889669941</v>
+        <v>0.6259901302598365</v>
       </c>
       <c r="L16" s="4" t="n">
-        <v>0.6601075467913873</v>
+        <v>0.6357176084256793</v>
       </c>
       <c r="M16" s="4" t="n">
-        <v>0.5598938962614071</v>
+        <v>0.5356929606347762</v>
       </c>
       <c r="N16" s="4" t="n">
-        <v>0.8453194669872701</v>
+        <v>0.8148587429549821</v>
       </c>
       <c r="O16" s="4" t="n">
-        <v>1.11598804108214</v>
+        <v>1.079041081939494</v>
       </c>
       <c r="P16" s="4" t="n">
-        <v>1.124123780943506</v>
+        <v>1.081908582539761</v>
       </c>
     </row>
     <row r="17">
@@ -2758,49 +2758,49 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>3343</v>
+        <v>3354</v>
       </c>
       <c r="C17" s="4" t="n">
-        <v>0.3796322412177275</v>
+        <v>0.3856410708659155</v>
       </c>
       <c r="D17" s="4" t="n">
-        <v>0.9004463115732051</v>
+        <v>0.8977984339856846</v>
       </c>
       <c r="E17" s="4" t="n">
-        <v>0.8202224964172089</v>
+        <v>0.8175793423556854</v>
       </c>
       <c r="F17" s="4" t="n">
-        <v>0.8476462967323073</v>
+        <v>0.8449974520129047</v>
       </c>
       <c r="G17" s="4" t="n">
-        <v>0.7136539675809743</v>
+        <v>0.6992517723482763</v>
       </c>
       <c r="H17" s="4" t="n">
-        <v>0.8784134319774637</v>
+        <v>0.8695820989513905</v>
       </c>
       <c r="I17" s="4" t="n">
-        <v>0.9296660510158361</v>
+        <v>0.9146811982347813</v>
       </c>
       <c r="J17" s="4" t="n">
-        <v>1.076396135296719</v>
+        <v>1.060618956829629</v>
       </c>
       <c r="K17" s="4" t="n">
-        <v>0.8529963381008798</v>
+        <v>0.8319704662655312</v>
       </c>
       <c r="L17" s="4" t="n">
-        <v>1.035662938061996</v>
+        <v>1.007537072587027</v>
       </c>
       <c r="M17" s="4" t="n">
-        <v>0.8480257089058725</v>
+        <v>0.8203666678246719</v>
       </c>
       <c r="N17" s="4" t="n">
-        <v>1.198431655195812</v>
+        <v>1.163689961695589</v>
       </c>
       <c r="O17" s="4" t="n">
-        <v>1.423444976076546</v>
+        <v>1.381727433102164</v>
       </c>
       <c r="P17" s="4" t="n">
-        <v>1.427246484119244</v>
+        <v>1.379694106563164</v>
       </c>
     </row>
     <row r="18">
@@ -2810,569 +2810,569 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>3283</v>
+        <v>3294</v>
       </c>
       <c r="C18" s="4" t="n">
-        <v>0.5227247461646698</v>
+        <v>0.5288963396125652</v>
       </c>
       <c r="D18" s="4" t="n">
-        <v>1.021706677615775</v>
+        <v>1.018628815305014</v>
       </c>
       <c r="E18" s="4" t="n">
-        <v>0.886532684725104</v>
+        <v>0.8836236311432089</v>
       </c>
       <c r="F18" s="4" t="n">
-        <v>0.9121035332005292</v>
+        <v>0.9092009685230025</v>
       </c>
       <c r="G18" s="4" t="n">
-        <v>0.7854995061977732</v>
+        <v>0.7697145716902583</v>
       </c>
       <c r="H18" s="4" t="n">
-        <v>0.947863033682772</v>
+        <v>0.938204544346199</v>
       </c>
       <c r="I18" s="4" t="n">
-        <v>0.9408260564597342</v>
+        <v>0.924658970426286</v>
       </c>
       <c r="J18" s="4" t="n">
-        <v>1.037948078621291</v>
+        <v>1.021116792327462</v>
       </c>
       <c r="K18" s="4" t="n">
-        <v>0.8419863877219669</v>
+        <v>0.8192824711934676</v>
       </c>
       <c r="L18" s="4" t="n">
-        <v>0.8609609018379558</v>
+        <v>0.8310986297384559</v>
       </c>
       <c r="M18" s="4" t="n">
-        <v>0.764878491218056</v>
+        <v>0.7351753478525254</v>
       </c>
       <c r="N18" s="4" t="n">
-        <v>1.121031323480103</v>
+        <v>1.083663751574889</v>
       </c>
       <c r="O18" s="4" t="n">
-        <v>1.357808484226837</v>
+        <v>1.312842861120501</v>
       </c>
       <c r="P18" s="4" t="n">
-        <v>1.35753393834846</v>
+        <v>1.306215249249007</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>X &gt; -0.2993</t>
+          <t>X &gt; -0.2992</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>3203</v>
+        <v>3212</v>
       </c>
       <c r="C19" s="4" t="n">
-        <v>0.3797804868785803</v>
+        <v>0.3891129813145682</v>
       </c>
       <c r="D19" s="4" t="n">
-        <v>0.8690176275682262</v>
+        <v>0.9005076160117582</v>
       </c>
       <c r="E19" s="4" t="n">
-        <v>0.7713716689958758</v>
+        <v>0.803075490720957</v>
       </c>
       <c r="F19" s="4" t="n">
-        <v>0.8565480249021178</v>
+        <v>0.8570098430433504</v>
       </c>
       <c r="G19" s="4" t="n">
-        <v>0.6467806375566312</v>
+        <v>0.6332727023088154</v>
       </c>
       <c r="H19" s="4" t="n">
-        <v>0.8680231563089507</v>
+        <v>0.8922320300409154</v>
       </c>
       <c r="I19" s="4" t="n">
-        <v>0.8317444440971542</v>
+        <v>0.8177411593644806</v>
       </c>
       <c r="J19" s="4" t="n">
-        <v>0.9428976821089776</v>
+        <v>0.928493856945046</v>
       </c>
       <c r="K19" s="4" t="n">
-        <v>0.6188520095554537</v>
+        <v>0.5980890405299917</v>
       </c>
       <c r="L19" s="4" t="n">
-        <v>0.7217954449241901</v>
+        <v>0.6933323368849571</v>
       </c>
       <c r="M19" s="4" t="n">
-        <v>0.5971884972968837</v>
+        <v>0.5690221316057062</v>
       </c>
       <c r="N19" s="4" t="n">
-        <v>0.8365158332714557</v>
+        <v>0.8004104181610003</v>
       </c>
       <c r="O19" s="4" t="n">
-        <v>1.120817877175057</v>
+        <v>1.076558834780236</v>
       </c>
       <c r="P19" s="4" t="n">
-        <v>1.146045108912837</v>
+        <v>1.094463779918378</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>X &gt; -0.2806</t>
+          <t>X &gt; -0.2805</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>3121</v>
+        <v>3131</v>
       </c>
       <c r="C20" s="4" t="n">
-        <v>0.5503539120310563</v>
+        <v>0.528386425192565</v>
       </c>
       <c r="D20" s="4" t="n">
-        <v>1.030783289743667</v>
+        <v>0.9990089893842722</v>
       </c>
       <c r="E20" s="4" t="n">
-        <v>0.8451826857719382</v>
+        <v>0.8138327004963273</v>
       </c>
       <c r="F20" s="4" t="n">
-        <v>0.8972641232581324</v>
+        <v>0.865787079162871</v>
       </c>
       <c r="G20" s="4" t="n">
-        <v>0.7919630406059071</v>
+        <v>0.7764178139472691</v>
       </c>
       <c r="H20" s="4" t="n">
-        <v>1.04321591362816</v>
+        <v>1.017346053377864</v>
       </c>
       <c r="I20" s="4" t="n">
-        <v>1.200078693684837</v>
+        <v>1.19747739325777</v>
       </c>
       <c r="J20" s="4" t="n">
-        <v>1.294533028133209</v>
+        <v>1.259483886926631</v>
       </c>
       <c r="K20" s="4" t="n">
-        <v>1.027678790970441</v>
+        <v>0.9853810415703776</v>
       </c>
       <c r="L20" s="4" t="n">
-        <v>1.059756155868996</v>
+        <v>1.008800450860534</v>
       </c>
       <c r="M20" s="4" t="n">
-        <v>0.8413290052912572</v>
+        <v>0.7909298491986334</v>
       </c>
       <c r="N20" s="4" t="n">
-        <v>1.086115826877347</v>
+        <v>1.026867402655306</v>
       </c>
       <c r="O20" s="4" t="n">
-        <v>1.3569696765354</v>
+        <v>1.288521014288058</v>
       </c>
       <c r="P20" s="4" t="n">
-        <v>1.344963477156</v>
+        <v>1.268575313917566</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>X &gt; -0.2619</t>
+          <t>X &gt; -0.2618</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>3029</v>
+        <v>3039</v>
       </c>
       <c r="C21" s="4" t="n">
-        <v>0.3461714119377035</v>
+        <v>0.3306106710079249</v>
       </c>
       <c r="D21" s="4" t="n">
-        <v>0.8898117205320446</v>
+        <v>0.8672892765537483</v>
       </c>
       <c r="E21" s="4" t="n">
-        <v>0.611810702173095</v>
+        <v>0.5573372160032903</v>
       </c>
       <c r="F21" s="4" t="n">
-        <v>0.727260815886666</v>
+        <v>0.639569831877516</v>
       </c>
       <c r="G21" s="4" t="n">
-        <v>0.7995979610071302</v>
+        <v>0.7420366672569614</v>
       </c>
       <c r="H21" s="4" t="n">
-        <v>1.082383428205226</v>
+        <v>0.9819490762797045</v>
       </c>
       <c r="I21" s="4" t="n">
-        <v>1.312455660281756</v>
+        <v>1.21715097521993</v>
       </c>
       <c r="J21" s="4" t="n">
-        <v>1.489866334421784</v>
+        <v>1.408780410760315</v>
       </c>
       <c r="K21" s="4" t="n">
-        <v>1.249793607439457</v>
+        <v>1.174569142846394</v>
       </c>
       <c r="L21" s="4" t="n">
-        <v>1.308697797807667</v>
+        <v>1.238314526528463</v>
       </c>
       <c r="M21" s="4" t="n">
-        <v>1.122917794442579</v>
+        <v>1.06704718878855</v>
       </c>
       <c r="N21" s="4" t="n">
-        <v>1.308199233764853</v>
+        <v>1.242685838075566</v>
       </c>
       <c r="O21" s="4" t="n">
-        <v>1.699117280149061</v>
+        <v>1.622971844428548</v>
       </c>
       <c r="P21" s="4" t="n">
-        <v>1.71301728659332</v>
+        <v>1.627898575479783</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>X &gt; -0.2432</t>
+          <t>X &gt; -0.2431</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>2876</v>
+        <v>2887</v>
       </c>
       <c r="C22" s="4" t="n">
-        <v>0.4093574204867636</v>
+        <v>0.4127522359916114</v>
       </c>
       <c r="D22" s="4" t="n">
-        <v>0.8594214221081913</v>
+        <v>0.8548079757703064</v>
       </c>
       <c r="E22" s="4" t="n">
-        <v>0.5183221965307396</v>
+        <v>0.4800897510020974</v>
       </c>
       <c r="F22" s="4" t="n">
-        <v>0.2864562783397844</v>
+        <v>0.2292192058547116</v>
       </c>
       <c r="G22" s="4" t="n">
-        <v>0.3910239538898779</v>
+        <v>0.3630230244043489</v>
       </c>
       <c r="H22" s="4" t="n">
-        <v>0.6728938094166921</v>
+        <v>0.6011944899176385</v>
       </c>
       <c r="I22" s="4" t="n">
-        <v>0.7460989748462126</v>
+        <v>0.6789946139147531</v>
       </c>
       <c r="J22" s="4" t="n">
-        <v>0.9575273377292604</v>
+        <v>0.8708288663386057</v>
       </c>
       <c r="K22" s="4" t="n">
-        <v>0.7424691208902701</v>
+        <v>0.6607859906735953</v>
       </c>
       <c r="L22" s="4" t="n">
-        <v>0.9536450447578773</v>
+        <v>0.8753790090278741</v>
       </c>
       <c r="M22" s="4" t="n">
-        <v>0.6298101209155078</v>
+        <v>0.5673964015748609</v>
       </c>
       <c r="N22" s="4" t="n">
-        <v>0.9271815863783033</v>
+        <v>0.8678615120792514</v>
       </c>
       <c r="O22" s="4" t="n">
-        <v>1.361100162483176</v>
+        <v>1.288830570190314</v>
       </c>
       <c r="P22" s="4" t="n">
-        <v>1.259301674276415</v>
+        <v>1.211512723070165</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>X &gt; -0.2245</t>
+          <t>X &gt; -0.2244</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>2744</v>
+        <v>2750</v>
       </c>
       <c r="C23" s="4" t="n">
-        <v>0.3362413667757167</v>
+        <v>0.3070455724230854</v>
       </c>
       <c r="D23" s="4" t="n">
-        <v>0.7970291014109137</v>
+        <v>0.7958423149662579</v>
       </c>
       <c r="E23" s="4" t="n">
-        <v>0.7858537643740533</v>
+        <v>0.7656085069496186</v>
       </c>
       <c r="F23" s="4" t="n">
-        <v>0.4797152715987778</v>
+        <v>0.4592875318066163</v>
       </c>
       <c r="G23" s="4" t="n">
-        <v>0.6525338900696056</v>
+        <v>0.6606963334210292</v>
       </c>
       <c r="H23" s="4" t="n">
-        <v>0.9135310553903935</v>
+        <v>0.8971314342101522</v>
       </c>
       <c r="I23" s="4" t="n">
-        <v>0.9379512890671222</v>
+        <v>0.9455265990741069</v>
       </c>
       <c r="J23" s="4" t="n">
-        <v>1.182534837979269</v>
+        <v>1.170351781257111</v>
       </c>
       <c r="K23" s="4" t="n">
-        <v>0.8872359278086108</v>
+        <v>0.8789262459116642</v>
       </c>
       <c r="L23" s="4" t="n">
-        <v>1.259493956305988</v>
+        <v>1.254661460080321</v>
       </c>
       <c r="M23" s="4" t="n">
-        <v>1.002814560450325</v>
+        <v>0.9778201764846131</v>
       </c>
       <c r="N23" s="4" t="n">
-        <v>1.276721779701731</v>
+        <v>1.254089422028358</v>
       </c>
       <c r="O23" s="4" t="n">
-        <v>1.73120649490145</v>
+        <v>1.731341528179911</v>
       </c>
       <c r="P23" s="4" t="n">
-        <v>1.592510658247512</v>
+        <v>1.637925797352999</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>X &gt; -0.2058</t>
+          <t>X &gt; -0.2057</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>2573</v>
+        <v>2575</v>
       </c>
       <c r="C24" s="4" t="n">
-        <v>0.5082144042482497</v>
+        <v>0.499596912977097</v>
       </c>
       <c r="D24" s="4" t="n">
-        <v>0.5274630937931306</v>
+        <v>0.5086528375299793</v>
       </c>
       <c r="E24" s="4" t="n">
-        <v>0.3267910879200713</v>
+        <v>0.3090896064968263</v>
       </c>
       <c r="F24" s="4" t="n">
-        <v>0.06881747374445268</v>
+        <v>0.05062413314840342</v>
       </c>
       <c r="G24" s="4" t="n">
-        <v>0.3069254361767122</v>
+        <v>0.3380740213226971</v>
       </c>
       <c r="H24" s="4" t="n">
-        <v>0.4102000869298124</v>
+        <v>0.4166847828600737</v>
       </c>
       <c r="I24" s="4" t="n">
-        <v>0.63604873387483</v>
+        <v>0.7055432567414002</v>
       </c>
       <c r="J24" s="4" t="n">
-        <v>0.8289179782868459</v>
+        <v>0.8999046711153511</v>
       </c>
       <c r="K24" s="4" t="n">
-        <v>0.6343351463736084</v>
+        <v>0.6687573046969888</v>
       </c>
       <c r="L24" s="4" t="n">
-        <v>0.8939131100259488</v>
+        <v>0.9323073646587119</v>
       </c>
       <c r="M24" s="4" t="n">
-        <v>0.6336169875038706</v>
+        <v>0.6893319656663124</v>
       </c>
       <c r="N24" s="4" t="n">
-        <v>1.095511657542829</v>
+        <v>1.174683169050617</v>
       </c>
       <c r="O24" s="4" t="n">
-        <v>1.374933287711734</v>
+        <v>1.478554368700379</v>
       </c>
       <c r="P24" s="4" t="n">
-        <v>1.21201755822586</v>
+        <v>1.300414764696335</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>X &gt; -0.1871</t>
+          <t>X &gt; -0.187</t>
         </is>
       </c>
       <c r="B25" t="n">
         <v>2406</v>
       </c>
       <c r="C25" s="4" t="n">
-        <v>0.6362909520092899</v>
+        <v>0.6070951576566586</v>
       </c>
       <c r="D25" s="4" t="n">
-        <v>0.895429048471641</v>
+        <v>0.8942422620269852</v>
       </c>
       <c r="E25" s="4" t="n">
-        <v>0.500657663716602</v>
+        <v>0.5005042737122807</v>
       </c>
       <c r="F25" s="4" t="n">
-        <v>0.2152552096324811</v>
+        <v>0.2147607172544781</v>
       </c>
       <c r="G25" s="4" t="n">
-        <v>0.3004070530455181</v>
+        <v>0.3489529728112899</v>
       </c>
       <c r="H25" s="4" t="n">
-        <v>0.5977810826806049</v>
+        <v>0.621738491630218</v>
       </c>
       <c r="I25" s="4" t="n">
-        <v>0.9286983210869195</v>
+        <v>0.9767100000772402</v>
       </c>
       <c r="J25" s="4" t="n">
-        <v>0.7525689956709201</v>
+        <v>0.8018165580646368</v>
       </c>
       <c r="K25" s="4" t="n">
-        <v>0.4422102805446499</v>
+        <v>0.5154673903243463</v>
       </c>
       <c r="L25" s="4" t="n">
-        <v>0.6729232381632571</v>
+        <v>0.7722705634578304</v>
       </c>
       <c r="M25" s="4" t="n">
-        <v>0.426659320135812</v>
+        <v>0.5265673561544872</v>
       </c>
       <c r="N25" s="4" t="n">
-        <v>0.9182278299308777</v>
+        <v>1.041924450959122</v>
       </c>
       <c r="O25" s="4" t="n">
-        <v>1.41245769149694</v>
+        <v>1.561147239274767</v>
       </c>
       <c r="P25" s="4" t="n">
-        <v>1.388816783119971</v>
+        <v>1.560815542686633</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>X &gt; -0.1684</t>
+          <t>X &gt; -0.1683</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>2253</v>
+        <v>2252</v>
       </c>
       <c r="C26" s="4" t="n">
-        <v>1.047712464805194</v>
+        <v>0.9978810703172769</v>
       </c>
       <c r="D26" s="4" t="n">
-        <v>1.211936935434224</v>
+        <v>1.190902919442074</v>
       </c>
       <c r="E26" s="4" t="n">
-        <v>0.9503213429561512</v>
+        <v>0.974784824555428</v>
       </c>
       <c r="F26" s="4" t="n">
-        <v>0.769849637898254</v>
+        <v>0.7494290789139768</v>
       </c>
       <c r="G26" s="4" t="n">
-        <v>0.7641832539104243</v>
+        <v>0.8374445916032656</v>
       </c>
       <c r="H26" s="4" t="n">
-        <v>1.23909833991479</v>
+        <v>1.243445030493234</v>
       </c>
       <c r="I26" s="4" t="n">
-        <v>1.642625885664167</v>
+        <v>1.715648621551971</v>
       </c>
       <c r="J26" s="4" t="n">
-        <v>1.353098298246707</v>
+        <v>1.427435754596694</v>
       </c>
       <c r="K26" s="4" t="n">
-        <v>1.070189821262318</v>
+        <v>1.168438278674813</v>
       </c>
       <c r="L26" s="4" t="n">
-        <v>1.285517363148166</v>
+        <v>1.410329058428218</v>
       </c>
       <c r="M26" s="4" t="n">
-        <v>1.036430940795661</v>
+        <v>1.161783637535109</v>
       </c>
       <c r="N26" s="4" t="n">
-        <v>1.559046998166515</v>
+        <v>1.664000108470162</v>
       </c>
       <c r="O26" s="4" t="n">
-        <v>1.982216162607216</v>
+        <v>2.112536675689647</v>
       </c>
       <c r="P26" s="4" t="n">
-        <v>2.074796020556789</v>
+        <v>2.228366617633959</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>X &gt; -0.1497</t>
+          <t>X &gt; -0.1496</t>
         </is>
       </c>
       <c r="B27" t="n">
         <v>2087</v>
       </c>
       <c r="C27" s="4" t="n">
-        <v>0.9929699301748016</v>
+        <v>0.9637741358221703</v>
       </c>
       <c r="D27" s="4" t="n">
-        <v>1.53798891617182</v>
+        <v>1.536802129727164</v>
       </c>
       <c r="E27" s="4" t="n">
-        <v>1.239048868263936</v>
+        <v>1.238895478259614</v>
       </c>
       <c r="F27" s="4" t="n">
-        <v>0.6984546539222549</v>
+        <v>0.6979601615442519</v>
       </c>
       <c r="G27" s="4" t="n">
-        <v>0.5434904482151595</v>
+        <v>0.5920363679809313</v>
       </c>
       <c r="H27" s="4" t="n">
-        <v>0.9846114831209647</v>
+        <v>1.008568892070578</v>
       </c>
       <c r="I27" s="4" t="n">
-        <v>1.426973476514114</v>
+        <v>1.474985155504434</v>
       </c>
       <c r="J27" s="4" t="n">
-        <v>1.439061516963129</v>
+        <v>1.488309079356846</v>
       </c>
       <c r="K27" s="4" t="n">
-        <v>1.378079360440353</v>
+        <v>1.451336470220049</v>
       </c>
       <c r="L27" s="4" t="n">
-        <v>1.678136606276269</v>
+        <v>1.777483931570842</v>
       </c>
       <c r="M27" s="4" t="n">
-        <v>1.377604111168935</v>
+        <v>1.47751214718761</v>
       </c>
       <c r="N27" s="4" t="n">
-        <v>1.843223279336428</v>
+        <v>1.966919900364672</v>
       </c>
       <c r="O27" s="4" t="n">
-        <v>2.525132799765224</v>
+        <v>2.673822347543052</v>
       </c>
       <c r="P27" s="4" t="n">
-        <v>2.511290107873897</v>
+        <v>2.683288867440559</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>X &gt; -0.131</t>
+          <t>X &gt; -0.1309</t>
         </is>
       </c>
       <c r="B28" t="n">
         <v>1925</v>
       </c>
       <c r="C28" s="4" t="n">
-        <v>1.648954099335775</v>
+        <v>1.619758304983144</v>
       </c>
       <c r="D28" s="4" t="n">
-        <v>1.596209564713504</v>
+        <v>1.595022778268849</v>
       </c>
       <c r="E28" s="4" t="n">
-        <v>1.253386231906525</v>
+        <v>1.253232841902204</v>
       </c>
       <c r="F28" s="4" t="n">
-        <v>0.9680269599104605</v>
+        <v>0.9675324675324575</v>
       </c>
       <c r="G28" s="4" t="n">
-        <v>0.5855815626589305</v>
+        <v>0.6341274824247023</v>
       </c>
       <c r="H28" s="4" t="n">
-        <v>0.986851696190115</v>
+        <v>1.010809105139728</v>
       </c>
       <c r="I28" s="4" t="n">
-        <v>1.83720627198889</v>
+        <v>1.885217950979211</v>
       </c>
       <c r="J28" s="4" t="n">
-        <v>1.941566199630721</v>
+        <v>1.990813762024437</v>
       </c>
       <c r="K28" s="4" t="n">
-        <v>1.93253209505599</v>
+        <v>2.005789204835686</v>
       </c>
       <c r="L28" s="4" t="n">
-        <v>2.277418493531322</v>
+        <v>2.376765818825895</v>
       </c>
       <c r="M28" s="4" t="n">
-        <v>2.020769283323084</v>
+        <v>2.120677319341759</v>
       </c>
       <c r="N28" s="4" t="n">
-        <v>2.730472111003081</v>
+        <v>2.854168732031326</v>
       </c>
       <c r="O28" s="4" t="n">
-        <v>3.349282296650713</v>
+        <v>3.497971844428541</v>
       </c>
       <c r="P28" s="4" t="n">
-        <v>3.263329635188938</v>
+        <v>3.435328394755601</v>
       </c>
     </row>
     <row r="29">
@@ -3385,306 +3385,306 @@
         <v>1750</v>
       </c>
       <c r="C29" s="4" t="n">
-        <v>1.519083969465647</v>
+        <v>1.489888175113016</v>
       </c>
       <c r="D29" s="4" t="n">
-        <v>1.965040733544683</v>
+        <v>1.963853947100027</v>
       </c>
       <c r="E29" s="4" t="n">
-        <v>1.627412205932494</v>
+        <v>1.627258815928172</v>
       </c>
       <c r="F29" s="4" t="n">
-        <v>1.129065920949422</v>
+        <v>1.128571428571419</v>
       </c>
       <c r="G29" s="4" t="n">
-        <v>0.5907763678537279</v>
+        <v>0.6393222876194997</v>
       </c>
       <c r="H29" s="4" t="n">
-        <v>0.9452932546316717</v>
+        <v>0.9692506635812848</v>
       </c>
       <c r="I29" s="4" t="n">
-        <v>2.232011466794084</v>
+        <v>2.280023145784405</v>
       </c>
       <c r="J29" s="4" t="n">
-        <v>2.279228537293058</v>
+        <v>2.328476099686775</v>
       </c>
       <c r="K29" s="4" t="n">
-        <v>2.161103523627425</v>
+        <v>2.234360633407121</v>
       </c>
       <c r="L29" s="4" t="n">
-        <v>2.568327584440425</v>
+        <v>2.667674909734998</v>
       </c>
       <c r="M29" s="4" t="n">
-        <v>1.963626426180227</v>
+        <v>2.063534462198902</v>
       </c>
       <c r="N29" s="4" t="n">
-        <v>2.798004578535554</v>
+        <v>2.921701199563799</v>
       </c>
       <c r="O29" s="4" t="n">
-        <v>3.46356801093642</v>
+        <v>3.612257558714248</v>
       </c>
       <c r="P29" s="4" t="n">
-        <v>3.060732232591533</v>
+        <v>3.232730992158196</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>X &gt; -0.09354</t>
+          <t>X &gt; -0.09351</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>1511</v>
+        <v>1510</v>
       </c>
       <c r="C30" s="4" t="n">
-        <v>1.125966828499401</v>
+        <v>1.066047115510372</v>
       </c>
       <c r="D30" s="4" t="n">
-        <v>1.632583515051714</v>
+        <v>1.602075328367754</v>
       </c>
       <c r="E30" s="4" t="n">
-        <v>1.436356140885692</v>
+        <v>1.407012836741792</v>
       </c>
       <c r="F30" s="4" t="n">
-        <v>1.831306631926076</v>
+        <v>1.801797540208135</v>
       </c>
       <c r="G30" s="4" t="n">
-        <v>0.9621103945153564</v>
+        <v>0.981422571441648</v>
       </c>
       <c r="H30" s="4" t="n">
-        <v>1.060940413561426</v>
+        <v>1.055532593571826</v>
       </c>
       <c r="I30" s="4" t="n">
-        <v>2.101312780966339</v>
+        <v>2.120704318915898</v>
       </c>
       <c r="J30" s="4" t="n">
-        <v>2.031332158357628</v>
+        <v>2.052222551910042</v>
       </c>
       <c r="K30" s="4" t="n">
-        <v>1.705624654382838</v>
+        <v>1.750349280521597</v>
       </c>
       <c r="L30" s="4" t="n">
-        <v>2.046969921587063</v>
+        <v>2.118573679839059</v>
       </c>
       <c r="M30" s="4" t="n">
-        <v>1.246636731559825</v>
+        <v>1.318406742236746</v>
       </c>
       <c r="N30" s="4" t="n">
-        <v>2.207553599997219</v>
+        <v>2.303725797482436</v>
       </c>
       <c r="O30" s="4" t="n">
-        <v>2.78012279962887</v>
+        <v>2.901945354362311</v>
       </c>
       <c r="P30" s="4" t="n">
-        <v>2.34404508122536</v>
+        <v>2.488738560748551</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>X &gt; -0.07483</t>
+          <t>X &gt; -0.07481</t>
         </is>
       </c>
       <c r="B31" t="n">
         <v>1286</v>
       </c>
       <c r="C31" s="4" t="n">
-        <v>2.806797810834226</v>
+        <v>2.777602016481595</v>
       </c>
       <c r="D31" s="4" t="n">
-        <v>2.828582168781296</v>
+        <v>2.82739538233664</v>
       </c>
       <c r="E31" s="4" t="n">
-        <v>2.356050286359064</v>
+        <v>2.355896896354743</v>
       </c>
       <c r="F31" s="4" t="n">
-        <v>3.030598913617723</v>
+        <v>3.03010442123972</v>
       </c>
       <c r="G31" s="4" t="n">
-        <v>1.325901895514249</v>
+        <v>1.374447815280021</v>
       </c>
       <c r="H31" s="4" t="n">
-        <v>1.856557418150892</v>
+        <v>1.880514827100505</v>
       </c>
       <c r="I31" s="4" t="n">
-        <v>2.860494026225318</v>
+        <v>2.908505705215639</v>
       </c>
       <c r="J31" s="4" t="n">
-        <v>2.859988368441691</v>
+        <v>2.909235930835408</v>
       </c>
       <c r="K31" s="4" t="n">
-        <v>2.721245714251729</v>
+        <v>2.794502824031426</v>
       </c>
       <c r="L31" s="4" t="n">
-        <v>3.037734382929649</v>
+        <v>3.137081708224223</v>
       </c>
       <c r="M31" s="4" t="n">
-        <v>2.366470238666338</v>
+        <v>2.466378274685013</v>
       </c>
       <c r="N31" s="4" t="n">
-        <v>3.100692870026336</v>
+        <v>3.224389491054581</v>
       </c>
       <c r="O31" s="4" t="n">
-        <v>3.613667988719151</v>
+        <v>3.762357536496978</v>
       </c>
       <c r="P31" s="4" t="n">
-        <v>3.217319657608193</v>
+        <v>3.389318417174856</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>X &gt; -0.05612</t>
+          <t>X &gt; -0.05611</t>
         </is>
       </c>
       <c r="B32" t="n">
         <v>1065</v>
       </c>
       <c r="C32" s="4" t="n">
-        <v>3.575421997634663</v>
+        <v>3.546226203282032</v>
       </c>
       <c r="D32" s="4" t="n">
-        <v>3.654376749641258</v>
+        <v>3.653189963196603</v>
       </c>
       <c r="E32" s="4" t="n">
-        <v>3.353502078501243</v>
+        <v>3.353348688496922</v>
       </c>
       <c r="F32" s="4" t="n">
-        <v>3.202037081244534</v>
+        <v>3.201542588866531</v>
       </c>
       <c r="G32" s="4" t="n">
-        <v>2.194263960073719</v>
+        <v>2.242809879839491</v>
       </c>
       <c r="H32" s="4" t="n">
-        <v>3.055018271398943</v>
+        <v>3.078975680348556</v>
       </c>
       <c r="I32" s="4" t="n">
-        <v>4.28486190274311</v>
+        <v>4.332873581733431</v>
       </c>
       <c r="J32" s="4" t="n">
-        <v>4.475070254261531</v>
+        <v>4.524317816655248</v>
       </c>
       <c r="K32" s="4" t="n">
-        <v>4.695778238583834</v>
+        <v>4.769035348363531</v>
       </c>
       <c r="L32" s="4" t="n">
-        <v>4.597033151174159</v>
+        <v>4.696380476468732</v>
       </c>
       <c r="M32" s="4" t="n">
-        <v>4.204538565683919</v>
+        <v>4.304446601702594</v>
       </c>
       <c r="N32" s="4" t="n">
-        <v>5.271780567804498</v>
+        <v>5.395477188832743</v>
       </c>
       <c r="O32" s="4" t="n">
-        <v>5.790596850641329</v>
+        <v>5.939286398419156</v>
       </c>
       <c r="P32" s="4" t="n">
-        <v>5.546848932792734</v>
+        <v>5.718847692359397</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>X &gt; -0.03742</t>
+          <t>X &gt; -0.03741</t>
         </is>
       </c>
       <c r="B33" t="n">
         <v>833</v>
       </c>
       <c r="C33" s="4" t="n">
-        <v>3.821604977869008</v>
+        <v>3.792409183516376</v>
       </c>
       <c r="D33" s="4" t="n">
-        <v>4.13118719212811</v>
+        <v>4.130000405683454</v>
       </c>
       <c r="E33" s="4" t="n">
-        <v>4.33665590341149</v>
+        <v>4.336502513407169</v>
       </c>
       <c r="F33" s="4" t="n">
-        <v>5.187169162245944</v>
+        <v>5.186674669867941</v>
       </c>
       <c r="G33" s="4" t="n">
-        <v>4.168687532319517</v>
+        <v>4.217233452085289</v>
       </c>
       <c r="H33" s="4" t="n">
-        <v>5.18634967720071</v>
+        <v>5.210307086150323</v>
       </c>
       <c r="I33" s="4" t="n">
-        <v>6.542215548426732</v>
+        <v>6.590227227417053</v>
       </c>
       <c r="J33" s="4" t="n">
-        <v>5.955098885432314</v>
+        <v>6.00434644782603</v>
       </c>
       <c r="K33" s="4" t="n">
-        <v>6.134212767324904</v>
+        <v>6.2074698771046</v>
       </c>
       <c r="L33" s="4" t="n">
-        <v>6.24467812465651</v>
+        <v>6.344025449951083</v>
       </c>
       <c r="M33" s="4" t="n">
-        <v>5.439736870357898</v>
+        <v>5.539644906376573</v>
       </c>
       <c r="N33" s="4" t="n">
-        <v>7.394883330036151</v>
+        <v>7.518579951064396</v>
       </c>
       <c r="O33" s="4" t="n">
-        <v>7.935116630384201</v>
+        <v>8.083806178162028</v>
       </c>
       <c r="P33" s="4" t="n">
-        <v>8.28090029981842</v>
+        <v>8.452899059385082</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>X &gt; -0.01871</t>
+          <t>X &gt; -0.0187</t>
         </is>
       </c>
       <c r="B34" t="n">
         <v>608</v>
       </c>
       <c r="C34" s="4" t="n">
-        <v>2.288820811570915</v>
+        <v>2.259625017218283</v>
       </c>
       <c r="D34" s="4" t="n">
-        <v>3.309213665875504</v>
+        <v>3.308026879430848</v>
       </c>
       <c r="E34" s="4" t="n">
-        <v>4.723652807436245</v>
+        <v>4.723499417431924</v>
       </c>
       <c r="F34" s="4" t="n">
-        <v>4.689404266814094</v>
+        <v>4.688909774436091</v>
       </c>
       <c r="G34" s="4" t="n">
-        <v>4.315588397928913</v>
+        <v>4.364134317694685</v>
       </c>
       <c r="H34" s="4" t="n">
-        <v>5.106383480195582</v>
+        <v>5.130340889145195</v>
       </c>
       <c r="I34" s="4" t="n">
-        <v>5.186146805139948</v>
+        <v>5.234158484130269</v>
       </c>
       <c r="J34" s="4" t="n">
-        <v>4.71907816135321</v>
+        <v>4.768325723746926</v>
       </c>
       <c r="K34" s="4" t="n">
-        <v>5.809411794304118</v>
+        <v>5.882668904083815</v>
       </c>
       <c r="L34" s="4" t="n">
-        <v>5.946335103237409</v>
+        <v>6.045682428531983</v>
       </c>
       <c r="M34" s="4" t="n">
-        <v>4.919265523924587</v>
+        <v>5.019173559943262</v>
       </c>
       <c r="N34" s="4" t="n">
-        <v>7.585222623648335</v>
+        <v>7.708919244676579</v>
       </c>
       <c r="O34" s="4" t="n">
-        <v>8.316387559808618</v>
+        <v>8.465077107586445</v>
       </c>
       <c r="P34" s="4" t="n">
-        <v>8.213175841614095</v>
+        <v>8.385174601180758</v>
       </c>
     </row>
     <row r="35">
@@ -3848,573 +3848,573 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>X &lt; -0.5425</t>
+          <t>X &lt; -0.5424</t>
         </is>
       </c>
       <c r="B6" t="n">
         <v>82</v>
       </c>
       <c r="C6" s="4" t="n">
-        <v>4.836157140197351</v>
+        <v>4.806961345844719</v>
       </c>
       <c r="D6" s="4" t="n">
-        <v>3.224971047133522</v>
+        <v>3.223784260688866</v>
       </c>
       <c r="E6" s="4" t="n">
-        <v>4.049711857500434</v>
+        <v>4.049558467496112</v>
       </c>
       <c r="F6" s="4" t="n">
-        <v>9.057985781576605</v>
+        <v>9.057491289198602</v>
       </c>
       <c r="G6" s="4" t="n">
-        <v>12.17823281384677</v>
+        <v>12.22677873361254</v>
       </c>
       <c r="H6" s="4" t="n">
-        <v>11.25609464835991</v>
+        <v>11.28005205730952</v>
       </c>
       <c r="I6" s="4" t="n">
-        <v>8.732359898849829</v>
+        <v>8.78037157784015</v>
       </c>
       <c r="J6" s="4" t="n">
-        <v>11.92382784042895</v>
+        <v>11.97307540282267</v>
       </c>
       <c r="K6" s="4" t="n">
-        <v>11.86284568390617</v>
+        <v>11.93610279368587</v>
       </c>
       <c r="L6" s="4" t="n">
-        <v>14.67146347294216</v>
+        <v>14.77081079823674</v>
       </c>
       <c r="M6" s="4" t="n">
-        <v>14.46676231468197</v>
+        <v>14.56667035070065</v>
       </c>
       <c r="N6" s="4" t="n">
-        <v>13.28162827191533</v>
+        <v>13.40532489294358</v>
       </c>
       <c r="O6" s="4" t="n">
-        <v>15.30050180884584</v>
+        <v>15.44919135662366</v>
       </c>
       <c r="P6" s="4" t="n">
-        <v>15.52623745907237</v>
+        <v>15.69823621863903</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>X &lt; -0.5238</t>
+          <t>X &lt; -0.5237</t>
         </is>
       </c>
       <c r="B7" t="n">
         <v>104</v>
       </c>
       <c r="C7" s="4" t="n">
-        <v>3.288314738696421</v>
+        <v>3.25911894434379</v>
       </c>
       <c r="D7" s="4" t="n">
-        <v>0.7155901840941326</v>
+        <v>0.7144033976494768</v>
       </c>
       <c r="E7" s="4" t="n">
-        <v>-1.602258123737833</v>
+        <v>-1.602411513742155</v>
       </c>
       <c r="F7" s="4" t="n">
-        <v>5.258736250619755</v>
+        <v>5.258241758241752</v>
       </c>
       <c r="G7" s="4" t="n">
-        <v>6.643523620600988</v>
+        <v>6.692069540366759</v>
       </c>
       <c r="H7" s="4" t="n">
-        <v>6.940897650236074</v>
+        <v>6.964855059185687</v>
       </c>
       <c r="I7" s="4" t="n">
-        <v>4.933110367892979</v>
+        <v>4.9811220468833</v>
       </c>
       <c r="J7" s="4" t="n">
-        <v>7.350657108721627</v>
+        <v>7.399904671115344</v>
       </c>
       <c r="K7" s="4" t="n">
-        <v>8.251213413737311</v>
+        <v>8.324470523517007</v>
       </c>
       <c r="L7" s="4" t="n">
-        <v>12.20898692509977</v>
+        <v>12.30833425039434</v>
       </c>
       <c r="M7" s="4" t="n">
-        <v>12.00428576683957</v>
+        <v>12.10419380285825</v>
       </c>
       <c r="N7" s="4" t="n">
-        <v>11.07712545765643</v>
+        <v>11.20082207868467</v>
       </c>
       <c r="O7" s="4" t="n">
-        <v>13.54158998895841</v>
+        <v>13.69027953673623</v>
       </c>
       <c r="P7" s="4" t="n">
-        <v>13.76732563918494</v>
+        <v>13.9393243987516</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>X &lt; -0.5051</t>
+          <t>X &lt; -0.505</t>
         </is>
       </c>
       <c r="B8" t="n">
         <v>124</v>
       </c>
       <c r="C8" s="4" t="n">
-        <v>0.7448904210785443</v>
+        <v>0.715694626725913</v>
       </c>
       <c r="D8" s="4" t="n">
-        <v>-0.05984405908205304</v>
+        <v>-0.06103084552670879</v>
       </c>
       <c r="E8" s="4" t="n">
-        <v>-0.454615443837092</v>
+        <v>-0.4547688338414133</v>
       </c>
       <c r="F8" s="4" t="n">
-        <v>3.707867764267405</v>
+        <v>3.707373271889402</v>
       </c>
       <c r="G8" s="4" t="n">
-        <v>6.395384662784608</v>
+        <v>6.443930582550379</v>
       </c>
       <c r="H8" s="4" t="n">
-        <v>6.692758692419694</v>
+        <v>6.716716101369308</v>
       </c>
       <c r="I8" s="4" t="n">
-        <v>4.995145107347078</v>
+        <v>5.043156786337399</v>
       </c>
       <c r="J8" s="4" t="n">
-        <v>6.140979689366787</v>
+        <v>6.190227251760504</v>
       </c>
       <c r="K8" s="4" t="n">
-        <v>8.499352371553691</v>
+        <v>8.572609481333387</v>
       </c>
       <c r="L8" s="4" t="n">
-        <v>11.68169163973995</v>
+        <v>11.78103896503453</v>
       </c>
       <c r="M8" s="4" t="n">
-        <v>12.28344209438299</v>
+        <v>12.38335013040167</v>
       </c>
       <c r="N8" s="4" t="n">
-        <v>10.70491702093187</v>
+        <v>10.82861364196011</v>
       </c>
       <c r="O8" s="4" t="n">
-        <v>11.09121778052167</v>
+        <v>11.2399073282995</v>
       </c>
       <c r="P8" s="4" t="n">
-        <v>12.12340504365144</v>
+        <v>12.2954038032181</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>X &lt; -0.4864</t>
+          <t>X &lt; -0.4863</t>
         </is>
       </c>
       <c r="B9" t="n">
         <v>163</v>
       </c>
       <c r="C9" s="4" t="n">
-        <v>2.73380789584602</v>
+        <v>2.704612101493389</v>
       </c>
       <c r="D9" s="4" t="n">
-        <v>-0.1043720622484869</v>
+        <v>-0.1055588486931427</v>
       </c>
       <c r="E9" s="4" t="n">
-        <v>2.568341215573163</v>
+        <v>2.568187825568842</v>
       </c>
       <c r="F9" s="4" t="n">
-        <v>4.539057156707536</v>
+        <v>4.538562664329532</v>
       </c>
       <c r="G9" s="4" t="n">
-        <v>8.295246131219201</v>
+        <v>8.343792050984973</v>
       </c>
       <c r="H9" s="4" t="n">
-        <v>9.206117093369627</v>
+        <v>9.230074502319241</v>
       </c>
       <c r="I9" s="4" t="n">
-        <v>7.894412869072788</v>
+        <v>7.942424548063109</v>
       </c>
       <c r="J9" s="4" t="n">
-        <v>8.040841157801381</v>
+        <v>8.090088720195098</v>
       </c>
       <c r="K9" s="4" t="n">
-        <v>11.04734366385529</v>
+        <v>11.12060077363498</v>
       </c>
       <c r="L9" s="4" t="n">
-        <v>14.49190339513279</v>
+        <v>14.59125072042737</v>
       </c>
       <c r="M9" s="4" t="n">
-        <v>14.90069916938793</v>
+        <v>15.00060720540661</v>
       </c>
       <c r="N9" s="4" t="n">
-        <v>13.09458652419725</v>
+        <v>13.21828314522549</v>
       </c>
       <c r="O9" s="4" t="n">
-        <v>14.51492646842985</v>
+        <v>14.66361601620768</v>
       </c>
       <c r="P9" s="4" t="n">
-        <v>15.35415905117173</v>
+        <v>15.52615781073839</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>X &lt; -0.4677</t>
+          <t>X &lt; -0.4676</t>
         </is>
       </c>
       <c r="B10" t="n">
         <v>219</v>
       </c>
       <c r="C10" s="4" t="n">
-        <v>4.140088535675687</v>
+        <v>4.110892741323056</v>
       </c>
       <c r="D10" s="4" t="n">
-        <v>0.2457974197808142</v>
+        <v>0.2446106333361584</v>
       </c>
       <c r="E10" s="4" t="n">
-        <v>3.960615076121663</v>
+        <v>3.960461686117341</v>
       </c>
       <c r="F10" s="4" t="n">
-        <v>6.373945242541083</v>
+        <v>6.37345075016308</v>
       </c>
       <c r="G10" s="4" t="n">
-        <v>7.662139707710224</v>
+        <v>7.710685627475996</v>
       </c>
       <c r="H10" s="4" t="n">
-        <v>6.133029719080476</v>
+        <v>6.156987128030089</v>
       </c>
       <c r="I10" s="4" t="n">
-        <v>7.418182373512927</v>
+        <v>7.466194052503248</v>
       </c>
       <c r="J10" s="4" t="n">
-        <v>5.581250716027569</v>
+        <v>5.630498278421285</v>
       </c>
       <c r="K10" s="4" t="n">
-        <v>7.803373582335837</v>
+        <v>7.876630692115533</v>
       </c>
       <c r="L10" s="4" t="n">
-        <v>11.06304382710186</v>
+        <v>11.16239115239644</v>
       </c>
       <c r="M10" s="4" t="n">
-        <v>12.22820568254031</v>
+        <v>12.32811371855898</v>
       </c>
       <c r="N10" s="4" t="n">
-        <v>9.979478812064578</v>
+        <v>10.10317543309282</v>
       </c>
       <c r="O10" s="4" t="n">
-        <v>10.9291909724498</v>
+        <v>11.07788052022763</v>
       </c>
       <c r="P10" s="4" t="n">
-        <v>10.69830561811012</v>
+        <v>10.87030437767678</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>X &lt; -0.449</t>
+          <t>X &lt; -0.4489</t>
         </is>
       </c>
       <c r="B11" t="n">
         <v>279</v>
       </c>
       <c r="C11" s="4" t="n">
-        <v>3.433062464089296</v>
+        <v>3.403866669736665</v>
       </c>
       <c r="D11" s="4" t="n">
-        <v>0.02976167568497345</v>
+        <v>0.0285748892403177</v>
       </c>
       <c r="E11" s="4" t="n">
-        <v>0.7102591081342311</v>
+        <v>0.7101057181299097</v>
       </c>
       <c r="F11" s="4" t="n">
-        <v>1.915753068926897</v>
+        <v>1.915258576548894</v>
       </c>
       <c r="G11" s="4" t="n">
-        <v>4.961692906512205</v>
+        <v>5.010238826277977</v>
       </c>
       <c r="H11" s="4" t="n">
-        <v>3.466952240806798</v>
+        <v>3.490909649756411</v>
       </c>
       <c r="I11" s="4" t="n">
-        <v>3.382241881540629</v>
+        <v>3.43025356053095</v>
       </c>
       <c r="J11" s="4" t="n">
-        <v>1.123058542413382</v>
+        <v>1.172306104807099</v>
       </c>
       <c r="K11" s="4" t="n">
-        <v>3.929459898435411</v>
+        <v>4.002717008215107</v>
       </c>
       <c r="L11" s="4" t="n">
-        <v>4.871655797446053</v>
+        <v>4.971003122740626</v>
       </c>
       <c r="M11" s="4" t="n">
-        <v>6.100646395458263</v>
+        <v>6.200554431476938</v>
       </c>
       <c r="N11" s="4" t="n">
-        <v>4.342909852473092</v>
+        <v>4.466606473501336</v>
       </c>
       <c r="O11" s="4" t="n">
-        <v>4.639604877295874</v>
+        <v>4.788294425073701</v>
       </c>
       <c r="P11" s="4" t="n">
-        <v>4.506917588454307</v>
+        <v>4.678916348020969</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>X &lt; -0.4303</t>
+          <t>X &lt; -0.4302</t>
         </is>
       </c>
       <c r="B12" t="n">
         <v>343</v>
       </c>
       <c r="C12" s="4" t="n">
-        <v>2.3295795962878</v>
+        <v>2.300383801935169</v>
       </c>
       <c r="D12" s="4" t="n">
-        <v>-0.1562420652891419</v>
+        <v>-0.1574288517337976</v>
       </c>
       <c r="E12" s="4" t="n">
-        <v>-0.8425586395485567</v>
+        <v>-0.8427120295528781</v>
       </c>
       <c r="F12" s="4" t="n">
-        <v>1.036937641066054</v>
+        <v>1.036443148688051</v>
       </c>
       <c r="G12" s="4" t="n">
-        <v>2.831009604005345</v>
+        <v>2.879555523771117</v>
       </c>
       <c r="H12" s="4" t="n">
-        <v>1.962202875622928</v>
+        <v>1.986160284572541</v>
       </c>
       <c r="I12" s="4" t="n">
-        <v>1.87749251635676</v>
+        <v>1.925504195347081</v>
       </c>
       <c r="J12" s="4" t="n">
-        <v>0.244243114552539</v>
+        <v>0.2934906769462557</v>
       </c>
       <c r="K12" s="4" t="n">
-        <v>3.098712853073486</v>
+        <v>3.171969962853183</v>
       </c>
       <c r="L12" s="4" t="n">
-        <v>3.123429625256747</v>
+        <v>3.222776950551321</v>
       </c>
       <c r="M12" s="4" t="n">
-        <v>3.5018188460053</v>
+        <v>3.601726882023975</v>
       </c>
       <c r="N12" s="4" t="n">
-        <v>1.49538067183002</v>
+        <v>1.619077292858265</v>
       </c>
       <c r="O12" s="4" t="n">
-        <v>0.7836846290122281</v>
+        <v>0.9323741767900557</v>
       </c>
       <c r="P12" s="4" t="n">
-        <v>1.300965468743144</v>
+        <v>1.472964228309806</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>X &lt; -0.4116</t>
+          <t>X &lt; -0.4115</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>400</v>
+        <v>402</v>
       </c>
       <c r="C13" s="4" t="n">
-        <v>1.269083969465647</v>
+        <v>1.221231458695108</v>
       </c>
       <c r="D13" s="4" t="n">
-        <v>-0.8421021235981812</v>
+        <v>-0.859458064271692</v>
       </c>
       <c r="E13" s="4" t="n">
-        <v>-0.2368735083532201</v>
+        <v>-0.2581711769645096</v>
       </c>
       <c r="F13" s="4" t="n">
-        <v>0.8933516352351418</v>
+        <v>0.6179815209665946</v>
       </c>
       <c r="G13" s="4" t="n">
-        <v>1.355062082139447</v>
+        <v>1.123757255636555</v>
       </c>
       <c r="H13" s="4" t="n">
-        <v>0.1524361117745343</v>
+        <v>-0.09599453897734378</v>
       </c>
       <c r="I13" s="4" t="n">
-        <v>-0.4322742474916339</v>
+        <v>-0.6541630660137443</v>
       </c>
       <c r="J13" s="4" t="n">
-        <v>-3.39934289127838</v>
+        <v>-3.607558015451815</v>
       </c>
       <c r="K13" s="4" t="n">
-        <v>-0.7103250478011418</v>
+        <v>-0.9082122166284208</v>
       </c>
       <c r="L13" s="4" t="n">
-        <v>-0.8102438441310085</v>
+        <v>-0.7370159218215093</v>
       </c>
       <c r="M13" s="4" t="n">
-        <v>-0.514945002391201</v>
+        <v>-0.69240015045213</v>
       </c>
       <c r="N13" s="4" t="n">
-        <v>-1.230566850035871</v>
+        <v>-1.380502069803661</v>
       </c>
       <c r="O13" s="4" t="n">
-        <v>-1.900717703349287</v>
+        <v>-2.02441621527295</v>
       </c>
       <c r="P13" s="4" t="n">
-        <v>-1.674982053122754</v>
+        <v>-1.775371353257583</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>X &lt; -0.3929</t>
+          <t>X &lt; -0.3928</t>
         </is>
       </c>
       <c r="B14" t="n">
         <v>478</v>
       </c>
       <c r="C14" s="4" t="n">
-        <v>0.8663643041936808</v>
+        <v>0.8371685098410495</v>
       </c>
       <c r="D14" s="4" t="n">
-        <v>-1.372436851631647</v>
+        <v>-1.373623638076303</v>
       </c>
       <c r="E14" s="4" t="n">
-        <v>-0.3027730899431802</v>
+        <v>-0.3029264799475015</v>
       </c>
       <c r="F14" s="4" t="n">
-        <v>0.2458620954861814</v>
+        <v>0.2453676031081784</v>
       </c>
       <c r="G14" s="4" t="n">
-        <v>-0.2924274576095129</v>
+        <v>-0.2438815378437411</v>
       </c>
       <c r="H14" s="4" t="n">
-        <v>-1.250283553497432</v>
+        <v>-1.226326144547819</v>
       </c>
       <c r="I14" s="4" t="n">
-        <v>-1.125788891843101</v>
+        <v>-1.07777721285278</v>
       </c>
       <c r="J14" s="4" t="n">
-        <v>-3.894112765755359</v>
+        <v>-3.844865203361643</v>
       </c>
       <c r="K14" s="4" t="n">
-        <v>-1.235429650311609</v>
+        <v>-1.162172540531913</v>
       </c>
       <c r="L14" s="4" t="n">
-        <v>-1.039323342038955</v>
+        <v>-0.9399760167443816</v>
       </c>
       <c r="M14" s="4" t="n">
-        <v>-0.197999395696641</v>
+        <v>-0.09809135967796578</v>
       </c>
       <c r="N14" s="4" t="n">
-        <v>-0.5820312851823246</v>
+        <v>-0.45833466415408</v>
       </c>
       <c r="O14" s="4" t="n">
-        <v>-1.839002222177733</v>
+        <v>-1.690312674399905</v>
       </c>
       <c r="P14" s="4" t="n">
-        <v>-2.450086655633214</v>
+        <v>-2.278087896066552</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>X &lt; -0.3742</t>
+          <t>X &lt; -0.3741</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>560</v>
+        <v>561</v>
       </c>
       <c r="C15" s="4" t="n">
-        <v>0.7333696837513628</v>
+        <v>0.7875708845604308</v>
       </c>
       <c r="D15" s="4" t="n">
-        <v>-1.23495926645532</v>
+        <v>-1.152112439454598</v>
       </c>
       <c r="E15" s="4" t="n">
-        <v>-0.379730651210366</v>
+        <v>-0.2980785917621773</v>
       </c>
       <c r="F15" s="4" t="n">
-        <v>0.4647802066637183</v>
+        <v>0.5448179271708682</v>
       </c>
       <c r="G15" s="4" t="n">
-        <v>-0.2520807750034137</v>
+        <v>-0.1226843332106426</v>
       </c>
       <c r="H15" s="4" t="n">
-        <v>-0.4904210310826116</v>
+        <v>-0.3846581726804885</v>
       </c>
       <c r="I15" s="4" t="n">
-        <v>-0.9322742474916339</v>
+        <v>-0.8018205007651247</v>
       </c>
       <c r="J15" s="4" t="n">
-        <v>-2.827914319849796</v>
+        <v>-2.693678216585191</v>
       </c>
       <c r="K15" s="4" t="n">
-        <v>-0.9246107620868642</v>
+        <v>-0.7698665119964971</v>
       </c>
       <c r="L15" s="4" t="n">
-        <v>-1.5959581298453</v>
+        <v>-1.415441973381895</v>
       </c>
       <c r="M15" s="4" t="n">
-        <v>-0.3720878595340551</v>
+        <v>-0.1935574654812626</v>
       </c>
       <c r="N15" s="4" t="n">
-        <v>-1.230566850035871</v>
+        <v>-1.026656325264319</v>
       </c>
       <c r="O15" s="4" t="n">
-        <v>-3.436431989063571</v>
+        <v>-3.204345446124044</v>
       </c>
       <c r="P15" s="4" t="n">
-        <v>-3.746410624551324</v>
+        <v>-3.490059942397451</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>X &lt; -0.3555</t>
+          <t>X &lt; -0.3554</t>
         </is>
       </c>
       <c r="B16" t="n">
         <v>649</v>
       </c>
       <c r="C16" s="4" t="n">
-        <v>-0.09262635410907905</v>
+        <v>-0.1218221484617104</v>
       </c>
       <c r="D16" s="4" t="n">
-        <v>-2.474228471826223</v>
+        <v>-2.475415258270878</v>
       </c>
       <c r="E16" s="4" t="n">
-        <v>-1.944500626997282</v>
+        <v>-1.944654017001604</v>
       </c>
       <c r="F16" s="4" t="n">
-        <v>-1.66019227847827</v>
+        <v>-1.660686770856273</v>
       </c>
       <c r="G16" s="4" t="n">
-        <v>-2.044398626643293</v>
+        <v>-1.995852706877521</v>
       </c>
       <c r="H16" s="4" t="n">
-        <v>-2.209274211800192</v>
+        <v>-2.185316802850579</v>
       </c>
       <c r="I16" s="4" t="n">
-        <v>-3.21848380065034</v>
+        <v>-3.170472121660019</v>
       </c>
       <c r="J16" s="4" t="n">
-        <v>-4.147802059229065</v>
+        <v>-4.098554496835348</v>
       </c>
       <c r="K16" s="4" t="n">
-        <v>-2.359785756583889</v>
+        <v>-2.286528646804193</v>
       </c>
       <c r="L16" s="4" t="n">
-        <v>-2.901538143052427</v>
+        <v>-2.802190817757854</v>
       </c>
       <c r="M16" s="4" t="n">
-        <v>-2.335823276659305</v>
+        <v>-2.23591524064063</v>
       </c>
       <c r="N16" s="4" t="n">
-        <v>-3.225944353887954</v>
+        <v>-3.102247732859709</v>
       </c>
       <c r="O16" s="4" t="n">
-        <v>-4.262428026924013</v>
+        <v>-4.113738479146186</v>
       </c>
       <c r="P16" s="4" t="n">
-        <v>-4.344858786558802</v>
+        <v>-4.17286002699214</v>
       </c>
     </row>
     <row r="17">
@@ -4427,46 +4427,46 @@
         <v>717</v>
       </c>
       <c r="C17" s="4" t="n">
-        <v>-1.155950898037837</v>
+        <v>-1.185146692390468</v>
       </c>
       <c r="D17" s="4" t="n">
-        <v>-3.743427088730677</v>
+        <v>-3.744613875175332</v>
       </c>
       <c r="E17" s="4" t="n">
-        <v>-3.719788431644716</v>
+        <v>-3.719941821649037</v>
       </c>
       <c r="F17" s="4" t="n">
-        <v>-2.892213218321345</v>
+        <v>-2.892707710699348</v>
       </c>
       <c r="G17" s="4" t="n">
-        <v>-2.593682687735033</v>
+        <v>-2.545136767969261</v>
       </c>
       <c r="H17" s="4" t="n">
-        <v>-3.27259875572895</v>
+        <v>-3.248641346779337</v>
       </c>
       <c r="I17" s="4" t="n">
-        <v>-3.775719156836118</v>
+        <v>-3.727707477845797</v>
       </c>
       <c r="J17" s="4" t="n">
-        <v>-4.800667856410868</v>
+        <v>-4.751420294017151</v>
       </c>
       <c r="K17" s="4" t="n">
-        <v>-3.048539831622627</v>
+        <v>-2.97528272184293</v>
       </c>
       <c r="L17" s="4" t="n">
-        <v>-4.316868669793493</v>
+        <v>-4.21752134449892</v>
       </c>
       <c r="M17" s="4" t="n">
-        <v>-3.405809716477677</v>
+        <v>-3.305901680459002</v>
       </c>
       <c r="N17" s="4" t="n">
-        <v>-4.487191675698362</v>
+        <v>-4.363495054670118</v>
       </c>
       <c r="O17" s="4" t="n">
-        <v>-5.186282556905773</v>
+        <v>-5.037593009127946</v>
       </c>
       <c r="P17" s="4" t="n">
-        <v>-5.23948693457325</v>
+        <v>-5.067488175006588</v>
       </c>
     </row>
     <row r="18">
@@ -4479,566 +4479,566 @@
         <v>777</v>
       </c>
       <c r="C18" s="4" t="n">
-        <v>-1.644365193983525</v>
+        <v>-1.673560988336156</v>
       </c>
       <c r="D18" s="4" t="n">
-        <v>-3.899051930547991</v>
+        <v>-3.900238716992646</v>
       </c>
       <c r="E18" s="4" t="n">
-        <v>-3.650322671802392</v>
+        <v>-3.650476061806714</v>
       </c>
       <c r="F18" s="4" t="n">
-        <v>-2.876596884713379</v>
+        <v>-2.877091377091382</v>
       </c>
       <c r="G18" s="4" t="n">
-        <v>-2.642685665608305</v>
+        <v>-2.594139745842533</v>
       </c>
       <c r="H18" s="4" t="n">
-        <v>-3.246212536874118</v>
+        <v>-3.222255127924505</v>
       </c>
       <c r="I18" s="4" t="n">
-        <v>-3.459623024840404</v>
+        <v>-3.411611345850083</v>
       </c>
       <c r="J18" s="4" t="n">
-        <v>-4.184091926027406</v>
+        <v>-4.13484436363369</v>
       </c>
       <c r="K18" s="4" t="n">
-        <v>-2.700672538148645</v>
+        <v>-2.627415428368948</v>
       </c>
       <c r="L18" s="4" t="n">
-        <v>-3.164490948378109</v>
+        <v>-3.065143623083536</v>
       </c>
       <c r="M18" s="4" t="n">
-        <v>-2.725691463137665</v>
+        <v>-2.625783427118989</v>
       </c>
       <c r="N18" s="4" t="n">
-        <v>-3.720914340383374</v>
+        <v>-3.597217719355129</v>
       </c>
       <c r="O18" s="4" t="n">
-        <v>-4.398465451097039</v>
+        <v>-4.249775903319211</v>
       </c>
       <c r="P18" s="4" t="n">
-        <v>-4.430130058270755</v>
+        <v>-4.258131298704093</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>X &lt; -0.2993</t>
+          <t>X &lt; -0.2992</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>857</v>
+        <v>859</v>
       </c>
       <c r="C19" s="4" t="n">
-        <v>-0.9056534867770552</v>
+        <v>-0.9385169471221388</v>
       </c>
       <c r="D19" s="4" t="n">
-        <v>-2.866897922898069</v>
+        <v>-2.987351773837943</v>
       </c>
       <c r="E19" s="4" t="n">
-        <v>-2.794924850243532</v>
+        <v>-2.915432020592696</v>
       </c>
       <c r="F19" s="4" t="n">
-        <v>-2.314641363598</v>
+        <v>-2.319890237818072</v>
       </c>
       <c r="G19" s="4" t="n">
-        <v>-1.802755887522167</v>
+        <v>-1.76140946026009</v>
       </c>
       <c r="H19" s="4" t="n">
-        <v>-2.555556887058607</v>
+        <v>-2.652768295341048</v>
       </c>
       <c r="I19" s="4" t="n">
-        <v>-2.640267246324775</v>
+        <v>-2.597009949176524</v>
       </c>
       <c r="J19" s="4" t="n">
-        <v>-3.340708118816295</v>
+        <v>-3.295671580339842</v>
       </c>
       <c r="K19" s="4" t="n">
-        <v>-1.534712445700798</v>
+        <v>-1.470013223236819</v>
       </c>
       <c r="L19" s="4" t="n">
-        <v>-2.26794512767826</v>
+        <v>-2.17742736866181</v>
       </c>
       <c r="M19" s="4" t="n">
-        <v>-1.772529599824104</v>
+        <v>-1.683081203857967</v>
       </c>
       <c r="N19" s="4" t="n">
-        <v>-2.204895904878356</v>
+        <v>-2.090572208053032</v>
       </c>
       <c r="O19" s="4" t="n">
-        <v>-2.975105101248936</v>
+        <v>-2.834973440786825</v>
       </c>
       <c r="P19" s="4" t="n">
-        <v>-3.099427794079581</v>
+        <v>-2.935171884941425</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>X &lt; -0.2806</t>
+          <t>X &lt; -0.2805</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>939</v>
+        <v>940</v>
       </c>
       <c r="C20" s="4" t="n">
-        <v>-1.362705167914548</v>
+        <v>-1.288007680359883</v>
       </c>
       <c r="D20" s="4" t="n">
-        <v>-3.080387533608828</v>
+        <v>-2.977454691126795</v>
       </c>
       <c r="E20" s="4" t="n">
-        <v>-2.729685009950671</v>
+        <v>-2.627303200164128</v>
       </c>
       <c r="F20" s="4" t="n">
-        <v>-2.173474775840468</v>
+        <v>-2.072339456505233</v>
       </c>
       <c r="G20" s="4" t="n">
-        <v>-2.072786693153418</v>
+        <v>-2.0302389694019</v>
       </c>
       <c r="H20" s="4" t="n">
-        <v>-2.840375389822917</v>
+        <v>-2.765095840977978</v>
       </c>
       <c r="I20" s="4" t="n">
-        <v>-3.564063384871829</v>
+        <v>-3.570432781267272</v>
       </c>
       <c r="J20" s="4" t="n">
-        <v>-4.13762830128902</v>
+        <v>-4.036265541650614</v>
       </c>
       <c r="K20" s="4" t="n">
-        <v>-2.70766264098539</v>
+        <v>-2.583876448659744</v>
       </c>
       <c r="L20" s="4" t="n">
-        <v>-3.131596346793422</v>
+        <v>-2.982173114581109</v>
       </c>
       <c r="M20" s="4" t="n">
-        <v>-2.377831051379488</v>
+        <v>-2.228866753606567</v>
       </c>
       <c r="N20" s="4" t="n">
-        <v>-2.769437989545999</v>
+        <v>-2.596231931135293</v>
       </c>
       <c r="O20" s="4" t="n">
-        <v>-3.402581388120318</v>
+        <v>-3.204155815145924</v>
       </c>
       <c r="P20" s="4" t="n">
-        <v>-3.389838283154702</v>
+        <v>-3.16787691057737</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>X &lt; -0.2619</t>
+          <t>X &lt; -0.2618</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>1031</v>
+        <v>1032</v>
       </c>
       <c r="C21" s="4" t="n">
-        <v>-0.5895484262666528</v>
+        <v>-0.5370608142998847</v>
       </c>
       <c r="D21" s="4" t="n">
-        <v>-2.29772772980575</v>
+        <v>-2.21648429021608</v>
       </c>
       <c r="E21" s="4" t="n">
-        <v>-1.722567009808124</v>
+        <v>-1.551511980166978</v>
       </c>
       <c r="F21" s="4" t="n">
-        <v>-1.398355445269225</v>
+        <v>-1.13288876667125</v>
       </c>
       <c r="G21" s="4" t="n">
-        <v>-1.83965178788965</v>
+        <v>-1.667201246649697</v>
       </c>
       <c r="H21" s="4" t="n">
-        <v>-2.60920307348249</v>
+        <v>-2.307454116691481</v>
       </c>
       <c r="I21" s="4" t="n">
-        <v>-3.469859116550801</v>
+        <v>-3.18638612062486</v>
       </c>
       <c r="J21" s="4" t="n">
-        <v>-4.227907391763338</v>
+        <v>-3.988984217773549</v>
       </c>
       <c r="K21" s="4" t="n">
-        <v>-3.027977812107643</v>
+        <v>-2.815984765874454</v>
       </c>
       <c r="L21" s="4" t="n">
-        <v>-3.489923766536442</v>
+        <v>-3.298747438487936</v>
       </c>
       <c r="M21" s="4" t="n">
-        <v>-2.918679240994493</v>
+        <v>-2.773564098155475</v>
       </c>
       <c r="N21" s="4" t="n">
-        <v>-3.078287509589707</v>
+        <v>-2.909195810402984</v>
       </c>
       <c r="O21" s="4" t="n">
-        <v>-3.983404415279445</v>
+        <v>-3.788849860997807</v>
       </c>
       <c r="P21" s="4" t="n">
-        <v>-4.048648396478718</v>
+        <v>-3.83050267340105</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>X &lt; -0.2432</t>
+          <t>X &lt; -0.2431</t>
         </is>
       </c>
       <c r="B22" t="n">
         <v>1184</v>
       </c>
       <c r="C22" s="4" t="n">
-        <v>-0.6228079224262473</v>
+        <v>-0.6241101484410478</v>
       </c>
       <c r="D22" s="4" t="n">
-        <v>-1.811696718192778</v>
+        <v>-1.788175749942248</v>
       </c>
       <c r="E22" s="4" t="n">
-        <v>-1.192954589434308</v>
+        <v>-1.092223880754851</v>
       </c>
       <c r="F22" s="4" t="n">
-        <v>-0.04921593233242305</v>
+        <v>0.08916586768935275</v>
       </c>
       <c r="G22" s="4" t="n">
-        <v>-0.5030460259686578</v>
+        <v>-0.4383315446942717</v>
       </c>
       <c r="H22" s="4" t="n">
-        <v>-1.134726050387627</v>
+        <v>-0.9601611011245907</v>
       </c>
       <c r="I22" s="4" t="n">
-        <v>-1.472814788032174</v>
+        <v>-1.312143140410484</v>
       </c>
       <c r="J22" s="4" t="n">
-        <v>-2.193261810197285</v>
+        <v>-1.985617214406538</v>
       </c>
       <c r="K22" s="4" t="n">
-        <v>-1.240730453206552</v>
+        <v>-1.051137019740075</v>
       </c>
       <c r="L22" s="4" t="n">
-        <v>-2.006189790076952</v>
+        <v>-1.82936194885329</v>
       </c>
       <c r="M22" s="4" t="n">
-        <v>-1.197377434823636</v>
+        <v>-1.059551734305018</v>
       </c>
       <c r="N22" s="4" t="n">
-        <v>-1.585296579765604</v>
+        <v>-1.461599958737359</v>
       </c>
       <c r="O22" s="4" t="n">
-        <v>-2.427744730376318</v>
+        <v>-2.279055182598491</v>
       </c>
       <c r="P22" s="4" t="n">
-        <v>-2.202009080149786</v>
+        <v>-2.114469780042583</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>X &lt; -0.2245</t>
+          <t>X &lt; -0.2244</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>1316</v>
+        <v>1321</v>
       </c>
       <c r="C23" s="4" t="n">
-        <v>-0.362913004815745</v>
+        <v>-0.2970585615711485</v>
       </c>
       <c r="D23" s="4" t="n">
-        <v>-1.404744061523999</v>
+        <v>-1.390586207340142</v>
       </c>
       <c r="E23" s="4" t="n">
-        <v>-1.572414764976998</v>
+        <v>-1.519333434796316</v>
       </c>
       <c r="F23" s="4" t="n">
-        <v>-0.4172544253709134</v>
+        <v>-0.3721804511278251</v>
       </c>
       <c r="G23" s="4" t="n">
-        <v>-0.9555439784666078</v>
+        <v>-0.9712979424138197</v>
       </c>
       <c r="H23" s="4" t="n">
-        <v>-1.451240916277023</v>
+        <v>-1.410955876866218</v>
       </c>
       <c r="I23" s="4" t="n">
-        <v>-1.647372881786026</v>
+        <v>-1.657623533083076</v>
       </c>
       <c r="J23" s="4" t="n">
-        <v>-2.342059128000685</v>
+        <v>-2.309748420890685</v>
       </c>
       <c r="K23" s="4" t="n">
-        <v>-1.340825806526496</v>
+        <v>-1.325747183304465</v>
       </c>
       <c r="L23" s="4" t="n">
-        <v>-2.342489671141635</v>
+        <v>-2.3355188753319</v>
       </c>
       <c r="M23" s="4" t="n">
-        <v>-1.788465487975422</v>
+        <v>-1.743268258889529</v>
       </c>
       <c r="N23" s="4" t="n">
-        <v>-2.057577472190665</v>
+        <v>-2.022150107978895</v>
       </c>
       <c r="O23" s="4" t="n">
-        <v>-2.816245417851938</v>
+        <v>-2.830567141188411</v>
       </c>
       <c r="P23" s="4" t="n">
-        <v>-2.549602113913032</v>
+        <v>-2.657222506273726</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>X &lt; -0.2058</t>
+          <t>X &lt; -0.2057</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>1487</v>
+        <v>1496</v>
       </c>
       <c r="C24" s="4" t="n">
-        <v>-0.577108415303897</v>
+        <v>-0.5551747804867233</v>
       </c>
       <c r="D24" s="4" t="n">
-        <v>-0.6830112145072746</v>
+        <v>-0.645013047973876</v>
       </c>
       <c r="E24" s="4" t="n">
-        <v>-0.5069403979853249</v>
+        <v>-0.4724283582115589</v>
       </c>
       <c r="F24" s="4" t="n">
-        <v>0.3956943393850807</v>
+        <v>0.4237336368810389</v>
       </c>
       <c r="G24" s="4" t="n">
-        <v>-0.1729017490728708</v>
+        <v>-0.2284517987592309</v>
       </c>
       <c r="H24" s="4" t="n">
-        <v>-0.3080196523005299</v>
+        <v>-0.318287330339686</v>
       </c>
       <c r="I24" s="4" t="n">
-        <v>-0.8258020811603046</v>
+        <v>-0.9416477980422329</v>
       </c>
       <c r="J24" s="4" t="n">
-        <v>-1.323839535573676</v>
+        <v>-1.438311041268143</v>
       </c>
       <c r="K24" s="4" t="n">
-        <v>-0.6465666585394061</v>
+        <v>-0.7066881911860108</v>
       </c>
       <c r="L24" s="4" t="n">
-        <v>-1.295143172990066</v>
+        <v>-1.360896518836434</v>
       </c>
       <c r="M24" s="4" t="n">
-        <v>-0.8287033916529438</v>
+        <v>-0.9282124166727215</v>
       </c>
       <c r="N24" s="4" t="n">
-        <v>-1.361527226127208</v>
+        <v>-1.500728706978258</v>
       </c>
       <c r="O24" s="4" t="n">
-        <v>-1.677599423779398</v>
+        <v>-1.859409585097183</v>
       </c>
       <c r="P24" s="4" t="n">
-        <v>-1.414894628778434</v>
+        <v>-1.57383890852936</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>X &lt; -0.1871</t>
+          <t>X &lt; -0.187</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>1654</v>
+        <v>1665</v>
       </c>
       <c r="C25" s="4" t="n">
-        <v>-0.6512819573489921</v>
+        <v>-0.6030796437189281</v>
       </c>
       <c r="D25" s="4" t="n">
-        <v>-1.090901643406099</v>
+        <v>-1.081959154527034</v>
       </c>
       <c r="E25" s="4" t="n">
-        <v>-0.6730596945394041</v>
+        <v>-0.6684111465675642</v>
       </c>
       <c r="F25" s="4" t="n">
-        <v>0.1505631736966819</v>
+        <v>0.1503198294243049</v>
       </c>
       <c r="G25" s="4" t="n">
-        <v>-0.1144207801576087</v>
+        <v>-0.1868937902094743</v>
       </c>
       <c r="H25" s="4" t="n">
-        <v>-0.506107811209823</v>
+        <v>-0.5389382186661678</v>
       </c>
       <c r="I25" s="4" t="n">
-        <v>-1.100094837497657</v>
+        <v>-1.165363046970214</v>
       </c>
       <c r="J25" s="4" t="n">
-        <v>-0.9927163852542762</v>
+        <v>-1.060598021882861</v>
       </c>
       <c r="K25" s="4" t="n">
-        <v>-0.2374498217613663</v>
+        <v>-0.3466487763448001</v>
       </c>
       <c r="L25" s="4" t="n">
-        <v>-0.752644326640052</v>
+        <v>-0.8979845955290671</v>
       </c>
       <c r="M25" s="4" t="n">
-        <v>-0.3808170603272316</v>
+        <v>-0.5295453596579023</v>
       </c>
       <c r="N25" s="4" t="n">
-        <v>-0.8561707147701725</v>
+        <v>-1.037884026248179</v>
       </c>
       <c r="O25" s="4" t="n">
-        <v>-1.424131600630254</v>
+        <v>-1.640083377660297</v>
       </c>
       <c r="P25" s="4" t="n">
-        <v>-1.406844205480674</v>
+        <v>-1.658388698961502</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>X &lt; -0.1684</t>
+          <t>X &lt; -0.1683</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>1807</v>
+        <v>1819</v>
       </c>
       <c r="C26" s="4" t="n">
-        <v>-1.052344601962929</v>
+        <v>-0.9817275454110046</v>
       </c>
       <c r="D26" s="4" t="n">
-        <v>-1.315851436407421</v>
+        <v>-1.280618238278777</v>
       </c>
       <c r="E26" s="4" t="n">
-        <v>-1.131537974799862</v>
+        <v>-1.153693565024206</v>
       </c>
       <c r="F26" s="4" t="n">
-        <v>-0.5316621237081733</v>
+        <v>-0.5025775208935457</v>
       </c>
       <c r="G26" s="4" t="n">
-        <v>-0.6548498121336834</v>
+        <v>-0.7435473591451043</v>
       </c>
       <c r="H26" s="4" t="n">
-        <v>-1.209134136159349</v>
+        <v>-1.207432423446626</v>
       </c>
       <c r="I26" s="4" t="n">
-        <v>-1.815681083213789</v>
+        <v>-1.896036938709422</v>
       </c>
       <c r="J26" s="4" t="n">
-        <v>-1.591703619353389</v>
+        <v>-1.675437794638079</v>
       </c>
       <c r="K26" s="4" t="n">
-        <v>-0.9608769241808375</v>
+        <v>-1.080050394161802</v>
       </c>
       <c r="L26" s="4" t="n">
-        <v>-1.394313418951555</v>
+        <v>-1.545098383894029</v>
       </c>
       <c r="M26" s="4" t="n">
-        <v>-1.07157483664534</v>
+        <v>-1.225410182618411</v>
       </c>
       <c r="N26" s="4" t="n">
-        <v>-1.504198690831906</v>
+        <v>-1.631307351467818</v>
       </c>
       <c r="O26" s="4" t="n">
-        <v>-1.894080535207692</v>
+        <v>-2.051478705022014</v>
       </c>
       <c r="P26" s="4" t="n">
-        <v>-2.025424775867634</v>
+        <v>-2.212301600318042</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>X &lt; -0.1497</t>
+          <t>X &lt; -0.1496</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>1973</v>
+        <v>1984</v>
       </c>
       <c r="C27" s="4" t="n">
-        <v>-0.8192846105947709</v>
+        <v>-0.7825204378063688</v>
       </c>
       <c r="D27" s="4" t="n">
-        <v>-1.447265851557873</v>
+        <v>-1.437978288800345</v>
       </c>
       <c r="E27" s="4" t="n">
-        <v>-1.261067056740323</v>
+        <v>-1.25394419159062</v>
       </c>
       <c r="F27" s="4" t="n">
-        <v>-0.3475712089403586</v>
+        <v>-0.3451067488178836</v>
       </c>
       <c r="G27" s="4" t="n">
-        <v>-0.3036160207868903</v>
+        <v>-0.3556744868052704</v>
       </c>
       <c r="H27" s="4" t="n">
-        <v>-0.7358778710624208</v>
+        <v>-0.7583454350991445</v>
       </c>
       <c r="I27" s="4" t="n">
-        <v>-1.298435863653246</v>
+        <v>-1.34445844996791</v>
       </c>
       <c r="J27" s="4" t="n">
-        <v>-1.435345923112628</v>
+        <v>-1.482004876623357</v>
       </c>
       <c r="K27" s="4" t="n">
-        <v>-1.115279547295593</v>
+        <v>-1.190361050138094</v>
       </c>
       <c r="L27" s="4" t="n">
-        <v>-1.58376432971523</v>
+        <v>-1.685242595295193</v>
       </c>
       <c r="M27" s="4" t="n">
-        <v>-1.254823544901321</v>
+        <v>-1.358796402708712</v>
       </c>
       <c r="N27" s="4" t="n">
-        <v>-1.547022546238409</v>
+        <v>-1.675853109168756</v>
       </c>
       <c r="O27" s="4" t="n">
-        <v>-2.142105747928824</v>
+        <v>-2.295479037183547</v>
       </c>
       <c r="P27" s="4" t="n">
-        <v>-2.142164009534312</v>
+        <v>-2.321531680652868</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>X &lt; -0.131</t>
+          <t>X &lt; -0.1309</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>2135</v>
+        <v>2146</v>
       </c>
       <c r="C28" s="4" t="n">
-        <v>-1.270487725133982</v>
+        <v>-1.23637398329366</v>
       </c>
       <c r="D28" s="4" t="n">
-        <v>-1.274216702079784</v>
+        <v>-1.266597529134586</v>
       </c>
       <c r="E28" s="4" t="n">
-        <v>-1.08519596874465</v>
+        <v>-1.079516467203163</v>
       </c>
       <c r="F28" s="4" t="n">
-        <v>-0.5104945186110115</v>
+        <v>-0.5074211502782973</v>
       </c>
       <c r="G28" s="4" t="n">
-        <v>-0.2774006044277115</v>
+        <v>-0.322030049138867</v>
       </c>
       <c r="H28" s="4" t="n">
-        <v>-0.6078298704933189</v>
+        <v>-0.6274597754689779</v>
       </c>
       <c r="I28" s="4" t="n">
-        <v>-1.460985732085469</v>
+        <v>-1.499102326977855</v>
       </c>
       <c r="J28" s="4" t="n">
-        <v>-1.669660499872492</v>
+        <v>-1.707902020334473</v>
       </c>
       <c r="K28" s="4" t="n">
-        <v>-1.425278318829186</v>
+        <v>-1.487602573074916</v>
       </c>
       <c r="L28" s="4" t="n">
-        <v>-1.87604562066209</v>
+        <v>-1.960896518836435</v>
       </c>
       <c r="M28" s="4" t="n">
-        <v>-1.634449211932825</v>
+        <v>-1.721109558275735</v>
       </c>
       <c r="N28" s="4" t="n">
-        <v>-2.089247243110279</v>
+        <v>-2.196255703867969</v>
       </c>
       <c r="O28" s="4" t="n">
-        <v>-2.530867516083369</v>
+        <v>-2.65945712622819</v>
       </c>
       <c r="P28" s="4" t="n">
-        <v>-2.467136619867482</v>
+        <v>-2.618314141645563</v>
       </c>
     </row>
     <row r="29">
@@ -5048,309 +5048,309 @@
         </is>
       </c>
       <c r="B29" t="n">
-        <v>2310</v>
+        <v>2321</v>
       </c>
       <c r="C29" s="4" t="n">
-        <v>-0.9527197326436934</v>
+        <v>-0.9248504709881047</v>
       </c>
       <c r="D29" s="4" t="n">
-        <v>-1.335857506888445</v>
+        <v>-1.328608241375882</v>
       </c>
       <c r="E29" s="4" t="n">
-        <v>-1.190880401933569</v>
+        <v>-1.185140105904708</v>
       </c>
       <c r="F29" s="4" t="n">
-        <v>-0.5204414682131357</v>
+        <v>-0.5175890175890174</v>
       </c>
       <c r="G29" s="4" t="n">
-        <v>-0.2161970812930676</v>
+        <v>-0.2541173199831945</v>
       </c>
       <c r="H29" s="4" t="n">
-        <v>-0.4560625940063119</v>
+        <v>-0.4731341735652492</v>
       </c>
       <c r="I29" s="4" t="n">
-        <v>-1.510068809425164</v>
+        <v>-1.541479063346671</v>
       </c>
       <c r="J29" s="4" t="n">
-        <v>-1.651933564853501</v>
+        <v>-1.683679342636268</v>
       </c>
       <c r="K29" s="4" t="n">
-        <v>-1.344234335058175</v>
+        <v>-1.396741196834867</v>
       </c>
       <c r="L29" s="4" t="n">
-        <v>-1.781937880431784</v>
+        <v>-1.85336963711601</v>
       </c>
       <c r="M29" s="4" t="n">
-        <v>-1.314663982071266</v>
+        <v>-1.388789117835515</v>
       </c>
       <c r="N29" s="4" t="n">
-        <v>-1.775549548997809</v>
+        <v>-1.866663599649044</v>
       </c>
       <c r="O29" s="4" t="n">
-        <v>-2.172137002354049</v>
+        <v>-2.281528586234678</v>
       </c>
       <c r="P29" s="4" t="n">
-        <v>-1.879527507668215</v>
+        <v>-2.009122888558245</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>X &lt; -0.09354</t>
+          <t>X &lt; -0.09351</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>2549</v>
+        <v>2561</v>
       </c>
       <c r="C30" s="4" t="n">
-        <v>-0.4902837120331824</v>
+        <v>-0.4510597658349269</v>
       </c>
       <c r="D30" s="4" t="n">
-        <v>-0.8316569849804551</v>
+        <v>-0.8091847514730688</v>
       </c>
       <c r="E30" s="4" t="n">
-        <v>-0.8149985083532201</v>
+        <v>-0.7934032591662543</v>
       </c>
       <c r="F30" s="4" t="n">
-        <v>-0.7810328899700139</v>
+        <v>-0.7593209979441014</v>
       </c>
       <c r="G30" s="4" t="n">
-        <v>-0.3601451109801772</v>
+        <v>-0.3716838268885567</v>
       </c>
       <c r="H30" s="4" t="n">
-        <v>-0.3934184052375898</v>
+        <v>-0.3890988887737095</v>
       </c>
       <c r="I30" s="4" t="n">
-        <v>-1.082900225582407</v>
+        <v>-1.090648861336206</v>
       </c>
       <c r="J30" s="4" t="n">
-        <v>-1.137601208303813</v>
+        <v>-1.146063384981268</v>
       </c>
       <c r="K30" s="4" t="n">
-        <v>-0.7467385168692786</v>
+        <v>-0.7722978678733554</v>
       </c>
       <c r="L30" s="4" t="n">
-        <v>-1.06611928478906</v>
+        <v>-1.107095349245789</v>
       </c>
       <c r="M30" s="4" t="n">
-        <v>-0.5831268205730211</v>
+        <v>-0.6268154375113753</v>
       </c>
       <c r="N30" s="4" t="n">
-        <v>-0.9973249841009562</v>
+        <v>-1.054197579768456</v>
       </c>
       <c r="O30" s="4" t="n">
-        <v>-1.238952997466939</v>
+        <v>-1.310771324970368</v>
       </c>
       <c r="P30" s="4" t="n">
-        <v>-0.9914787184817229</v>
+        <v>-1.079223043653712</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>X &lt; -0.07483</t>
+          <t>X &lt; -0.07481</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>2774</v>
+        <v>2785</v>
       </c>
       <c r="C31" s="4" t="n">
-        <v>-1.13538319953328</v>
+        <v>-1.116259072921302</v>
       </c>
       <c r="D31" s="4" t="n">
-        <v>-1.184708010173914</v>
+        <v>-1.179452656914485</v>
       </c>
       <c r="E31" s="4" t="n">
-        <v>-1.057789127742808</v>
+        <v>-1.053550503507751</v>
       </c>
       <c r="F31" s="4" t="n">
-        <v>-1.1238897440752</v>
+        <v>-1.119217991311018</v>
       </c>
       <c r="G31" s="4" t="n">
-        <v>-0.4213482664052819</v>
+        <v>-0.4441013753317193</v>
       </c>
       <c r="H31" s="4" t="n">
-        <v>-0.6435739529271274</v>
+        <v>-0.653090904624932</v>
       </c>
       <c r="I31" s="4" t="n">
-        <v>-1.176341129908032</v>
+        <v>-1.19586715302853</v>
       </c>
       <c r="J31" s="4" t="n">
-        <v>-1.264450804947437</v>
+        <v>-1.284258711184904</v>
       </c>
       <c r="K31" s="4" t="n">
-        <v>-1.018169596199854</v>
+        <v>-1.051046432645109</v>
       </c>
       <c r="L31" s="4" t="n">
-        <v>-1.272626853490259</v>
+        <v>-1.317655213709145</v>
       </c>
       <c r="M31" s="4" t="n">
-        <v>-0.9534577859706062</v>
+        <v>-1.000044139973674</v>
       </c>
       <c r="N31" s="4" t="n">
-        <v>-1.151316129574788</v>
+        <v>-1.209130724163707</v>
       </c>
       <c r="O31" s="4" t="n">
-        <v>-1.299366351997932</v>
+        <v>-1.369221263970601</v>
       </c>
       <c r="P31" s="4" t="n">
-        <v>-1.125775131709631</v>
+        <v>-1.208099990144966</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>X &lt; -0.05612</t>
+          <t>X &lt; -0.05611</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>2995</v>
+        <v>3006</v>
       </c>
       <c r="C32" s="4" t="n">
-        <v>-1.117884115640734</v>
+        <v>-1.102360913989344</v>
       </c>
       <c r="D32" s="4" t="n">
-        <v>-1.182225169823653</v>
+        <v>-1.17745060653057</v>
       </c>
       <c r="E32" s="4" t="n">
-        <v>-1.160193534966659</v>
+        <v>-1.155903265609773</v>
       </c>
       <c r="F32" s="4" t="n">
-        <v>-0.8791109271608661</v>
+        <v>-0.8757104964001527</v>
       </c>
       <c r="G32" s="4" t="n">
-        <v>-0.6006636169284647</v>
+        <v>-0.6175362767017489</v>
       </c>
       <c r="H32" s="4" t="n">
-        <v>-0.884610175271753</v>
+        <v>-0.8907929424477175</v>
       </c>
       <c r="I32" s="4" t="n">
-        <v>-1.384472781802089</v>
+        <v>-1.398285137369548</v>
       </c>
       <c r="J32" s="4" t="n">
-        <v>-1.533881378449315</v>
+        <v>-1.547638489575228</v>
       </c>
       <c r="K32" s="4" t="n">
-        <v>-1.443658381134483</v>
+        <v>-1.467190820784658</v>
       </c>
       <c r="L32" s="4" t="n">
-        <v>-1.508726671740213</v>
+        <v>-1.54229186767364</v>
       </c>
       <c r="M32" s="4" t="n">
-        <v>-1.361676156493935</v>
+        <v>-1.396010711802909</v>
       </c>
       <c r="N32" s="4" t="n">
-        <v>-1.60927889541459</v>
+        <v>-1.652082994965077</v>
       </c>
       <c r="O32" s="4" t="n">
-        <v>-1.710797810158361</v>
+        <v>-1.763085687995805</v>
       </c>
       <c r="P32" s="4" t="n">
-        <v>-1.633663188348123</v>
+        <v>-1.695431730016509</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>X &lt; -0.03742</t>
+          <t>X &lt; -0.03741</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>3227</v>
+        <v>3238</v>
       </c>
       <c r="C33" s="4" t="n">
-        <v>-0.8451135613985485</v>
+        <v>-0.8337045655821598</v>
       </c>
       <c r="D33" s="4" t="n">
-        <v>-0.9584188880316518</v>
+        <v>-0.9548273715813025</v>
       </c>
       <c r="E33" s="4" t="n">
-        <v>-1.089714768390287</v>
+        <v>-1.085980422518823</v>
       </c>
       <c r="F33" s="4" t="n">
-        <v>-1.097457756176652</v>
+        <v>-1.093596059113302</v>
       </c>
       <c r="G33" s="4" t="n">
-        <v>-0.9085349512350831</v>
+        <v>-0.9196904274141602</v>
       </c>
       <c r="H33" s="4" t="n">
-        <v>-1.150886917591777</v>
+        <v>-1.154013133619664</v>
       </c>
       <c r="I33" s="4" t="n">
-        <v>-1.559206838709933</v>
+        <v>-1.568006790381126</v>
       </c>
       <c r="J33" s="4" t="n">
-        <v>-1.484016568977104</v>
+        <v>-1.493436882522133</v>
       </c>
       <c r="K33" s="4" t="n">
-        <v>-1.373691384434807</v>
+        <v>-1.390536948197216</v>
       </c>
       <c r="L33" s="4" t="n">
-        <v>-1.495093735805412</v>
+        <v>-1.519193866152904</v>
       </c>
       <c r="M33" s="4" t="n">
-        <v>-1.280424878552189</v>
+        <v>-1.305425735271015</v>
       </c>
       <c r="N33" s="4" t="n">
-        <v>-1.662589147960936</v>
+        <v>-1.693289982094051</v>
       </c>
       <c r="O33" s="4" t="n">
-        <v>-1.725067145728467</v>
+        <v>-1.762911144148184</v>
       </c>
       <c r="P33" s="4" t="n">
-        <v>-1.823184718136694</v>
+        <v>-1.86756019287666</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>X &lt; -0.01871</t>
+          <t>X &lt; -0.0187</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>3452</v>
+        <v>3463</v>
       </c>
       <c r="C34" s="4" t="n">
-        <v>-0.27312382274215</v>
+        <v>-0.2661532518144796</v>
       </c>
       <c r="D34" s="4" t="n">
-        <v>-0.4835570889561538</v>
+        <v>-0.4817781186759262</v>
       </c>
       <c r="E34" s="4" t="n">
-        <v>-0.8050947038484537</v>
+        <v>-0.8025133692844193</v>
       </c>
       <c r="F34" s="4" t="n">
-        <v>-0.6015934831935041</v>
+        <v>-0.5995845502036161</v>
       </c>
       <c r="G34" s="4" t="n">
-        <v>-0.6042704807036614</v>
+        <v>-0.6125210303528448</v>
       </c>
       <c r="H34" s="4" t="n">
-        <v>-0.7247315182832708</v>
+        <v>-0.7274526331220059</v>
       </c>
       <c r="I34" s="4" t="n">
-        <v>-0.7938671934297616</v>
+        <v>-0.8014095425647128</v>
       </c>
       <c r="J34" s="4" t="n">
-        <v>-0.7826569456450514</v>
+        <v>-0.7904960207266853</v>
       </c>
       <c r="K34" s="4" t="n">
-        <v>-0.8279125514170005</v>
+        <v>-0.8406434858876537</v>
       </c>
       <c r="L34" s="4" t="n">
-        <v>-0.9387160663532299</v>
+        <v>-0.9565700117698128</v>
       </c>
       <c r="M34" s="4" t="n">
-        <v>-0.7511968113636982</v>
+        <v>-0.7697686455416033</v>
       </c>
       <c r="N34" s="4" t="n">
-        <v>-1.106073508982028</v>
+        <v>-1.128515250652654</v>
       </c>
       <c r="O34" s="4" t="n">
-        <v>-1.162736237956878</v>
+        <v>-1.190249864578384</v>
       </c>
       <c r="P34" s="4" t="n">
-        <v>-1.15267614350514</v>
+        <v>-1.185123056767182</v>
       </c>
     </row>
     <row r="35">
@@ -5360,49 +5360,49 @@
         </is>
       </c>
       <c r="B35" t="n">
-        <v>3732</v>
+        <v>3743</v>
       </c>
       <c r="C35" s="4" t="n">
-        <v>-0.1444674324035162</v>
+        <v>-0.1405697588593</v>
       </c>
       <c r="D35" s="4" t="n">
-        <v>-0.3527858842819427</v>
+        <v>-0.3516111470601473</v>
       </c>
       <c r="E35" s="4" t="n">
-        <v>-0.3858849964643625</v>
+        <v>-0.3847360086399121</v>
       </c>
       <c r="F35" s="4" t="n">
-        <v>-0.4015441424238588</v>
+        <v>-0.4003083247687655</v>
       </c>
       <c r="G35" s="4" t="n">
-        <v>-0.3373329993895595</v>
+        <v>-0.3421276057706848</v>
       </c>
       <c r="H35" s="4" t="n">
-        <v>-0.4264408935730586</v>
+        <v>-0.4280452955914953</v>
       </c>
       <c r="I35" s="4" t="n">
-        <v>-0.3361924074274469</v>
+        <v>-0.3409292351679767</v>
       </c>
       <c r="J35" s="4" t="n">
-        <v>-0.4944472251467502</v>
+        <v>-0.4988683350196297</v>
       </c>
       <c r="K35" s="4" t="n">
-        <v>-0.3267285800462716</v>
+        <v>-0.3345065719595581</v>
       </c>
       <c r="L35" s="4" t="n">
-        <v>-0.5730918098697657</v>
+        <v>-0.5832610771497571</v>
       </c>
       <c r="M35" s="4" t="n">
-        <v>-0.3613305445598698</v>
+        <v>-0.3721912642903078</v>
       </c>
       <c r="N35" s="4" t="n">
-        <v>-0.4994474070792663</v>
+        <v>-0.5127447283400741</v>
       </c>
       <c r="O35" s="4" t="n">
-        <v>-0.4760592517018267</v>
+        <v>-0.4924127709560722</v>
       </c>
       <c r="P35" s="4" t="n">
-        <v>-0.5032242824903932</v>
+        <v>-0.5222859919263882</v>
       </c>
     </row>
   </sheetData>
